--- a/outputs/NSW_historical_prices.xlsx
+++ b/outputs/NSW_historical_prices.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly Data" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Monthly Data" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Heatmap" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/outputs/NSW_historical_prices.xlsx
+++ b/outputs/NSW_historical_prices.xlsx
@@ -528,16 +528,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>100.02</v>
+        <v>96.7</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>120.42</v>
+        <v>116.51</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>101.14</v>
+        <v>97.61</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>121.93</v>
+        <v>117.8</v>
       </c>
     </row>
     <row r="6">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>115.48</v>
+        <v>114.41</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>145.2</v>
+        <v>144.12</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>118.56</v>
+        <v>117.31</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>149.25</v>
+        <v>148</v>
       </c>
     </row>
     <row r="7">
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>107.9</v>
+        <v>106.61</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>132.05</v>
+        <v>130.5</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>112.14</v>
+        <v>110.58</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>137.24</v>
+        <v>135.4</v>
       </c>
     </row>
     <row r="8">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>118.8</v>
+        <v>118.94</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>141</v>
+        <v>140.86</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>129.63</v>
+        <v>129.57</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>153.81</v>
+        <v>153.42</v>
       </c>
     </row>
     <row r="9">
@@ -604,22 +604,22 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>97.47</v>
+        <v>97.45999999999999</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>115.39</v>
+        <v>115.24</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>113.49</v>
+        <v>113.29</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>134.31</v>
+        <v>133.95</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Data through: Mar 2026</t>
+          <t>Data through: Apr 2026</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F274"/>
+  <dimension ref="A1:F275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6233,6 +6233,26 @@
       </c>
       <c r="F274" s="7" t="inlineStr"/>
     </row>
+    <row r="275">
+      <c r="A275" s="4" t="inlineStr">
+        <is>
+          <t>Apr 2026</t>
+        </is>
+      </c>
+      <c r="B275" s="5" t="n">
+        <v>64.27</v>
+      </c>
+      <c r="C275" s="5" t="n">
+        <v>60.42</v>
+      </c>
+      <c r="D275" s="5" t="n">
+        <v>64.27</v>
+      </c>
+      <c r="E275" s="5" t="n">
+        <v>60.42</v>
+      </c>
+      <c r="F275" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6244,7 +6264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E274"/>
+  <dimension ref="A1:E275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11468,8 +11488,27 @@
         <v>74.36</v>
       </c>
     </row>
+    <row r="275">
+      <c r="A275" s="4" t="inlineStr">
+        <is>
+          <t>Apr 2026</t>
+        </is>
+      </c>
+      <c r="B275" s="5" t="n">
+        <v>64.27</v>
+      </c>
+      <c r="C275" s="5" t="n">
+        <v>60.42</v>
+      </c>
+      <c r="D275" s="5" t="n">
+        <v>64.27</v>
+      </c>
+      <c r="E275" s="5" t="n">
+        <v>60.42</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B274">
+  <conditionalFormatting sqref="B2:B275">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -11481,7 +11520,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C274">
+  <conditionalFormatting sqref="C2:C275">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -11493,7 +11532,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D274">
+  <conditionalFormatting sqref="D2:D275">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -11505,7 +11544,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E274">
+  <conditionalFormatting sqref="E2:E275">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>

--- a/outputs/NSW_historical_prices.xlsx
+++ b/outputs/NSW_historical_prices.xlsx
@@ -528,16 +528,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>96.7</v>
+        <v>91.93000000000001</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>116.51</v>
+        <v>108.26</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>97.61</v>
+        <v>93.56999999999999</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>117.8</v>
+        <v>110.44</v>
       </c>
     </row>
     <row r="6">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>114.41</v>
+        <v>105.75</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>144.12</v>
+        <v>128.84</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>117.31</v>
+        <v>109.48</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>148</v>
+        <v>133.58</v>
       </c>
     </row>
     <row r="7">
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>106.61</v>
+        <v>103.05</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>130.5</v>
+        <v>125.85</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>110.58</v>
+        <v>107.93</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>135.4</v>
+        <v>131.91</v>
       </c>
     </row>
     <row r="8">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>118.94</v>
+        <v>118.07</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>140.86</v>
+        <v>138.86</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>129.57</v>
+        <v>129.98</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>153.42</v>
+        <v>152.75</v>
       </c>
     </row>
     <row r="9">
@@ -604,22 +604,22 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>97.45999999999999</v>
+        <v>97.45</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>115.24</v>
+        <v>115.09</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>113.29</v>
+        <v>114.63</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>133.95</v>
+        <v>135.38</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Data through: Apr 2026</t>
+          <t>Data through: May 2026</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F275"/>
+  <dimension ref="A1:F276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -690,10 +690,10 @@
         <v>75.81999999999999</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>85.73999999999999</v>
+        <v>86.92</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>138.99</v>
+        <v>140.91</v>
       </c>
       <c r="F2" s="7" t="inlineStr"/>
     </row>
@@ -710,10 +710,10 @@
         <v>22.06</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>35.88</v>
+        <v>36.38</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>40.36</v>
+        <v>40.92</v>
       </c>
       <c r="F3" s="7" t="inlineStr"/>
     </row>
@@ -730,10 +730,10 @@
         <v>26.29</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>38.44</v>
+        <v>38.97</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>48.01</v>
+        <v>48.67</v>
       </c>
       <c r="F4" s="7" t="inlineStr"/>
     </row>
@@ -750,10 +750,10 @@
         <v>19.41</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>31.9</v>
+        <v>32.34</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>35.39</v>
+        <v>35.87</v>
       </c>
       <c r="F5" s="7" t="inlineStr"/>
     </row>
@@ -770,10 +770,10 @@
         <v>20.74</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>33.43</v>
+        <v>33.89</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>37.75</v>
+        <v>38.26</v>
       </c>
       <c r="F6" s="7" t="inlineStr"/>
     </row>
@@ -790,10 +790,10 @@
         <v>29.68</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>42.48</v>
+        <v>43.06</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>53.92</v>
+        <v>54.66</v>
       </c>
       <c r="F7" s="7" t="inlineStr"/>
     </row>
@@ -810,10 +810,10 @@
         <v>31.61</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>48.47</v>
+        <v>49.14</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>57.26</v>
+        <v>58.05</v>
       </c>
       <c r="F8" s="7" t="inlineStr"/>
     </row>
@@ -830,10 +830,10 @@
         <v>49.01</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>105.65</v>
+        <v>107.11</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>88.51000000000001</v>
+        <v>89.73</v>
       </c>
       <c r="F9" s="7" t="inlineStr"/>
     </row>
@@ -850,10 +850,10 @@
         <v>116.77</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>114.76</v>
+        <v>116.34</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>210.27</v>
+        <v>213.17</v>
       </c>
       <c r="F10" s="7" t="inlineStr"/>
     </row>
@@ -870,10 +870,10 @@
         <v>37.43</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>54.42</v>
+        <v>55.17</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>67.3</v>
+        <v>68.22</v>
       </c>
       <c r="F11" s="7" t="inlineStr"/>
     </row>
@@ -890,10 +890,10 @@
         <v>37.85</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>57.66</v>
+        <v>58.45</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>67.95</v>
+        <v>68.88</v>
       </c>
       <c r="F12" s="7" t="inlineStr"/>
     </row>
@@ -910,10 +910,10 @@
         <v>33.72</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>55.89</v>
+        <v>56.66</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>60.44</v>
+        <v>61.27</v>
       </c>
       <c r="F13" s="7" t="inlineStr"/>
     </row>
@@ -930,10 +930,10 @@
         <v>43.57</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>63.78</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>77.98999999999999</v>
+        <v>79.06</v>
       </c>
       <c r="F14" s="7" t="inlineStr"/>
     </row>
@@ -950,10 +950,10 @@
         <v>26.2</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>42.2</v>
+        <v>42.78</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>46.83</v>
+        <v>47.48</v>
       </c>
       <c r="F15" s="7" t="inlineStr"/>
     </row>
@@ -970,10 +970,10 @@
         <v>32.32</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>50.3</v>
+        <v>50.99</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>57.69</v>
+        <v>58.49</v>
       </c>
       <c r="F16" s="7" t="inlineStr"/>
     </row>
@@ -990,10 +990,10 @@
         <v>125.43</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>123.92</v>
+        <v>125.63</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>223.33</v>
+        <v>226.4</v>
       </c>
       <c r="F17" s="7" t="inlineStr"/>
     </row>
@@ -1010,10 +1010,10 @@
         <v>131.39</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>137.99</v>
+        <v>139.89</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>233.35</v>
+        <v>236.56</v>
       </c>
       <c r="F18" s="7" t="inlineStr"/>
     </row>
@@ -1030,10 +1030,10 @@
         <v>110.88</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>114.95</v>
+        <v>116.53</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>196.42</v>
+        <v>199.13</v>
       </c>
       <c r="F19" s="7" t="inlineStr"/>
     </row>
@@ -1050,10 +1050,10 @@
         <v>65.59999999999999</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>70.53</v>
+        <v>71.5</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>115.95</v>
+        <v>117.55</v>
       </c>
       <c r="F20" s="7" t="inlineStr"/>
     </row>
@@ -1070,10 +1070,10 @@
         <v>50.64</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>57.95</v>
+        <v>58.75</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>89.31</v>
+        <v>90.54000000000001</v>
       </c>
       <c r="F21" s="7" t="inlineStr"/>
     </row>
@@ -1090,10 +1090,10 @@
         <v>19.92</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>32.47</v>
+        <v>32.91</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>35.05</v>
+        <v>35.54</v>
       </c>
       <c r="F22" s="7" t="inlineStr"/>
     </row>
@@ -1110,10 +1110,10 @@
         <v>36.49</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>52.51</v>
+        <v>53.23</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>64.08</v>
+        <v>64.97</v>
       </c>
       <c r="F23" s="7" t="inlineStr"/>
     </row>
@@ -1130,10 +1130,10 @@
         <v>27.74</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>42.77</v>
+        <v>43.35</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>48.62</v>
+        <v>49.29</v>
       </c>
       <c r="F24" s="7" t="inlineStr"/>
     </row>
@@ -1150,10 +1150,10 @@
         <v>32.42</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>46.09</v>
+        <v>46.73</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>56.71</v>
+        <v>57.49</v>
       </c>
       <c r="F25" s="7" t="inlineStr"/>
     </row>
@@ -1170,10 +1170,10 @@
         <v>27.73</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>42.37</v>
+        <v>42.95</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>48.35</v>
+        <v>49.01</v>
       </c>
       <c r="F26" s="7" t="inlineStr"/>
     </row>
@@ -1190,10 +1190,10 @@
         <v>36.96</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>49.47</v>
+        <v>50.15</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>64.23</v>
+        <v>65.11</v>
       </c>
       <c r="F27" s="7" t="inlineStr"/>
     </row>
@@ -1210,10 +1210,10 @@
         <v>36.19</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>49.59</v>
+        <v>50.27</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>62.68</v>
+        <v>63.54</v>
       </c>
       <c r="F28" s="7" t="inlineStr"/>
     </row>
@@ -1230,10 +1230,10 @@
         <v>86.17</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>81.94</v>
+        <v>83.06999999999999</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>148.99</v>
+        <v>151.04</v>
       </c>
       <c r="F29" s="7" t="inlineStr"/>
     </row>
@@ -1250,10 +1250,10 @@
         <v>104.05</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>99.23</v>
+        <v>100.6</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>179.6</v>
+        <v>182.07</v>
       </c>
       <c r="F30" s="7" t="inlineStr"/>
     </row>
@@ -1270,10 +1270,10 @@
         <v>127.53</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>123.29</v>
+        <v>124.99</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>219.75</v>
+        <v>222.77</v>
       </c>
       <c r="F31" s="7" t="inlineStr"/>
     </row>
@@ -1290,10 +1290,10 @@
         <v>33.82</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>46.12</v>
+        <v>46.75</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>58.11</v>
+        <v>58.91</v>
       </c>
       <c r="F32" s="7" t="inlineStr"/>
     </row>
@@ -1310,10 +1310,10 @@
         <v>122.66</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>110.42</v>
+        <v>111.94</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>210.15</v>
+        <v>213.05</v>
       </c>
       <c r="F33" s="7" t="inlineStr"/>
     </row>
@@ -1330,10 +1330,10 @@
         <v>27.46</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>38.58</v>
+        <v>39.11</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>46.91</v>
+        <v>47.56</v>
       </c>
       <c r="F34" s="7" t="inlineStr"/>
     </row>
@@ -1350,10 +1350,10 @@
         <v>23.63</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>35.03</v>
+        <v>35.51</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>40.16</v>
+        <v>40.71</v>
       </c>
       <c r="F35" s="7" t="inlineStr"/>
     </row>
@@ -1370,10 +1370,10 @@
         <v>32.23</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>43.03</v>
+        <v>43.62</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>54.49</v>
+        <v>55.24</v>
       </c>
       <c r="F36" s="7" t="inlineStr"/>
     </row>
@@ -1390,10 +1390,10 @@
         <v>38.39</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>52.93</v>
+        <v>53.65</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>64.56</v>
+        <v>65.45</v>
       </c>
       <c r="F37" s="7" t="inlineStr"/>
     </row>
@@ -1410,10 +1410,10 @@
         <v>73.48999999999999</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>80</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>123.23</v>
+        <v>124.93</v>
       </c>
       <c r="F38" s="7" t="inlineStr"/>
     </row>
@@ -1430,10 +1430,10 @@
         <v>35.43</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>49.81</v>
+        <v>50.49</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>59.24</v>
+        <v>60.05</v>
       </c>
       <c r="F39" s="7" t="inlineStr"/>
     </row>
@@ -1450,10 +1450,10 @@
         <v>34.69</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>47.09</v>
+        <v>47.74</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>57.83</v>
+        <v>58.62</v>
       </c>
       <c r="F40" s="7" t="inlineStr"/>
     </row>
@@ -1470,10 +1470,10 @@
         <v>30.95</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>42.24</v>
+        <v>42.82</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>51.61</v>
+        <v>52.32</v>
       </c>
       <c r="F41" s="7" t="inlineStr"/>
     </row>
@@ -1490,10 +1490,10 @@
         <v>41.15</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>52.5</v>
+        <v>53.22</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>68.65000000000001</v>
+        <v>69.59</v>
       </c>
       <c r="F42" s="7" t="inlineStr"/>
     </row>
@@ -1510,10 +1510,10 @@
         <v>25.26</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>35.05</v>
+        <v>35.53</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>42.16</v>
+        <v>42.74</v>
       </c>
       <c r="F43" s="7" t="inlineStr"/>
     </row>
@@ -1530,10 +1530,10 @@
         <v>89.47</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>93.28</v>
+        <v>94.56999999999999</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>149.28</v>
+        <v>151.33</v>
       </c>
       <c r="F44" s="7" t="inlineStr"/>
     </row>
@@ -1550,10 +1550,10 @@
         <v>62.98</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>74.66</v>
+        <v>75.69</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>105.05</v>
+        <v>106.5</v>
       </c>
       <c r="F45" s="7" t="inlineStr"/>
     </row>
@@ -1570,10 +1570,10 @@
         <v>63.16</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>85.51000000000001</v>
+        <v>86.69</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>105.32</v>
+        <v>106.77</v>
       </c>
       <c r="F46" s="7" t="inlineStr"/>
     </row>
@@ -1590,10 +1590,10 @@
         <v>102.26</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>129.89</v>
+        <v>131.67</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>169.83</v>
+        <v>172.16</v>
       </c>
       <c r="F47" s="7" t="inlineStr"/>
     </row>
@@ -1610,10 +1610,10 @@
         <v>75.83</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>104.66</v>
+        <v>106.1</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>125.42</v>
+        <v>127.15</v>
       </c>
       <c r="F48" s="7" t="inlineStr"/>
     </row>
@@ -1630,10 +1630,10 @@
         <v>397.05</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>379.96</v>
+        <v>385.19</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>654.0599999999999</v>
+        <v>663.05</v>
       </c>
       <c r="F49" s="7" t="inlineStr"/>
     </row>
@@ -1650,10 +1650,10 @@
         <v>105.7</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>127.98</v>
+        <v>129.74</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>173.72</v>
+        <v>176.11</v>
       </c>
       <c r="F50" s="7" t="inlineStr"/>
     </row>
@@ -1670,10 +1670,10 @@
         <v>47.17</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>65.48999999999999</v>
+        <v>66.39</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>77.34999999999999</v>
+        <v>78.41</v>
       </c>
       <c r="F51" s="7" t="inlineStr"/>
     </row>
@@ -1690,10 +1690,10 @@
         <v>60.36</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>78.45</v>
+        <v>79.53</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>98.75</v>
+        <v>100.11</v>
       </c>
       <c r="F52" s="7" t="inlineStr"/>
     </row>
@@ -1710,10 +1710,10 @@
         <v>55.78</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>66.41</v>
+        <v>67.33</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>90.97</v>
+        <v>92.23</v>
       </c>
       <c r="F53" s="7" t="inlineStr"/>
     </row>
@@ -1730,10 +1730,10 @@
         <v>48.17</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>58.55</v>
+        <v>59.36</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>78.31999999999999</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="F54" s="7" t="inlineStr"/>
     </row>
@@ -1750,10 +1750,10 @@
         <v>55.55</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>65.09999999999999</v>
+        <v>65.98999999999999</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>90.04000000000001</v>
+        <v>91.28</v>
       </c>
       <c r="F55" s="7" t="inlineStr"/>
     </row>
@@ -1770,10 +1770,10 @@
         <v>43.73</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>55</v>
+        <v>55.75</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>70.56999999999999</v>
+        <v>71.54000000000001</v>
       </c>
       <c r="F56" s="7" t="inlineStr"/>
     </row>
@@ -1790,10 +1790,10 @@
         <v>32.22</v>
       </c>
       <c r="D57" s="5" t="n">
-        <v>43.68</v>
+        <v>44.28</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>51.76</v>
+        <v>52.48</v>
       </c>
       <c r="F57" s="7" t="inlineStr"/>
     </row>
@@ -1810,10 +1810,10 @@
         <v>47.31</v>
       </c>
       <c r="D58" s="5" t="n">
-        <v>55.29</v>
+        <v>56.05</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>75.67</v>
+        <v>76.70999999999999</v>
       </c>
       <c r="F58" s="7" t="inlineStr"/>
     </row>
@@ -1830,10 +1830,10 @@
         <v>40.08</v>
       </c>
       <c r="D59" s="5" t="n">
-        <v>52.93</v>
+        <v>53.66</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>63.8</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="F59" s="7" t="inlineStr"/>
     </row>
@@ -1850,10 +1850,10 @@
         <v>53.21</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>71.59999999999999</v>
+        <v>72.59</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>84.29000000000001</v>
+        <v>85.45</v>
       </c>
       <c r="F60" s="7" t="inlineStr"/>
     </row>
@@ -1870,10 +1870,10 @@
         <v>51.05</v>
       </c>
       <c r="D61" s="5" t="n">
-        <v>65.93000000000001</v>
+        <v>66.84</v>
       </c>
       <c r="E61" s="5" t="n">
-        <v>80.48999999999999</v>
+        <v>81.59</v>
       </c>
       <c r="F61" s="7" t="inlineStr"/>
     </row>
@@ -1890,10 +1890,10 @@
         <v>55.38</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>63.56</v>
+        <v>64.43000000000001</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>86.98</v>
+        <v>88.17</v>
       </c>
       <c r="F62" s="7" t="inlineStr"/>
     </row>
@@ -1910,10 +1910,10 @@
         <v>48.73</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>62.45</v>
+        <v>63.31</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>76.23999999999999</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="F63" s="7" t="inlineStr"/>
     </row>
@@ -1930,10 +1930,10 @@
         <v>45.62</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>55.4</v>
+        <v>56.17</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>71.09999999999999</v>
+        <v>72.08</v>
       </c>
       <c r="F64" s="7" t="inlineStr"/>
     </row>
@@ -1950,10 +1950,10 @@
         <v>143.1</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>127.28</v>
+        <v>129.03</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>223.26</v>
+        <v>226.33</v>
       </c>
       <c r="F65" s="7" t="inlineStr"/>
     </row>
@@ -1970,10 +1970,10 @@
         <v>38.45</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>48.18</v>
+        <v>48.85</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>60.05</v>
+        <v>60.88</v>
       </c>
       <c r="F66" s="7" t="inlineStr"/>
     </row>
@@ -1990,10 +1990,10 @@
         <v>27.84</v>
       </c>
       <c r="D67" s="5" t="n">
-        <v>37.39</v>
+        <v>37.9</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>43.53</v>
+        <v>44.13</v>
       </c>
       <c r="F67" s="7" t="inlineStr"/>
     </row>
@@ -2010,10 +2010,10 @@
         <v>72.97</v>
       </c>
       <c r="D68" s="5" t="n">
-        <v>73.62</v>
+        <v>74.63</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>114.05</v>
+        <v>115.62</v>
       </c>
       <c r="F68" s="7" t="inlineStr"/>
     </row>
@@ -2030,10 +2030,10 @@
         <v>39.35</v>
       </c>
       <c r="D69" s="5" t="n">
-        <v>64.73</v>
+        <v>65.62</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>61.48</v>
+        <v>62.33</v>
       </c>
       <c r="F69" s="7" t="inlineStr"/>
     </row>
@@ -2050,10 +2050,10 @@
         <v>29.61</v>
       </c>
       <c r="D70" s="5" t="n">
-        <v>38.5</v>
+        <v>39.03</v>
       </c>
       <c r="E70" s="5" t="n">
-        <v>46.25</v>
+        <v>46.88</v>
       </c>
       <c r="F70" s="7" t="inlineStr"/>
     </row>
@@ -2070,10 +2070,10 @@
         <v>47.45</v>
       </c>
       <c r="D71" s="5" t="n">
-        <v>56.15</v>
+        <v>56.92</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>73.98999999999999</v>
+        <v>75.01000000000001</v>
       </c>
       <c r="F71" s="7" t="inlineStr"/>
     </row>
@@ -2090,10 +2090,10 @@
         <v>35.75</v>
       </c>
       <c r="D72" s="5" t="n">
-        <v>47.14</v>
+        <v>47.79</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>55.65</v>
+        <v>56.42</v>
       </c>
       <c r="F72" s="7" t="inlineStr"/>
     </row>
@@ -2110,10 +2110,10 @@
         <v>45.82</v>
       </c>
       <c r="D73" s="5" t="n">
-        <v>53.07</v>
+        <v>53.8</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>71.20999999999999</v>
+        <v>72.19</v>
       </c>
       <c r="F73" s="7" t="inlineStr"/>
     </row>
@@ -2130,10 +2130,10 @@
         <v>40.23</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>48.76</v>
+        <v>49.43</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>62.33</v>
+        <v>63.18</v>
       </c>
       <c r="F74" s="7" t="inlineStr"/>
     </row>
@@ -2150,10 +2150,10 @@
         <v>27.9</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>37.53</v>
+        <v>38.05</v>
       </c>
       <c r="E75" s="5" t="n">
-        <v>43.09</v>
+        <v>43.68</v>
       </c>
       <c r="F75" s="7" t="inlineStr"/>
     </row>
@@ -2170,10 +2170,10 @@
         <v>28.56</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>39.44</v>
+        <v>39.99</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>43.97</v>
+        <v>44.58</v>
       </c>
       <c r="F76" s="7" t="inlineStr"/>
     </row>
@@ -2190,10 +2190,10 @@
         <v>32.65</v>
       </c>
       <c r="D77" s="5" t="n">
-        <v>42.32</v>
+        <v>42.91</v>
       </c>
       <c r="E77" s="5" t="n">
-        <v>50.18</v>
+        <v>50.87</v>
       </c>
       <c r="F77" s="7" t="inlineStr"/>
     </row>
@@ -2210,10 +2210,10 @@
         <v>209.33</v>
       </c>
       <c r="D78" s="5" t="n">
-        <v>165.31</v>
+        <v>167.59</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>321.13</v>
+        <v>325.55</v>
       </c>
       <c r="F78" s="7" t="inlineStr"/>
     </row>
@@ -2230,10 +2230,10 @@
         <v>186.31</v>
       </c>
       <c r="D79" s="5" t="n">
-        <v>149.12</v>
+        <v>151.18</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>285.31</v>
+        <v>289.23</v>
       </c>
       <c r="F79" s="7" t="inlineStr"/>
     </row>
@@ -2250,10 +2250,10 @@
         <v>78.56</v>
       </c>
       <c r="D80" s="5" t="n">
-        <v>76.97</v>
+        <v>78.03</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>119.93</v>
+        <v>121.58</v>
       </c>
       <c r="F80" s="7" t="inlineStr"/>
     </row>
@@ -2270,10 +2270,10 @@
         <v>96.8</v>
       </c>
       <c r="D81" s="5" t="n">
-        <v>84.83</v>
+        <v>86</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>147.32</v>
+        <v>149.35</v>
       </c>
       <c r="F81" s="7" t="inlineStr"/>
     </row>
@@ -2290,10 +2290,10 @@
         <v>30.88</v>
       </c>
       <c r="D82" s="5" t="n">
-        <v>39.24</v>
+        <v>39.78</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>46.85</v>
+        <v>47.5</v>
       </c>
       <c r="F82" s="7" t="inlineStr"/>
     </row>
@@ -2310,10 +2310,10 @@
         <v>28.33</v>
       </c>
       <c r="D83" s="5" t="n">
-        <v>37.48</v>
+        <v>37.99</v>
       </c>
       <c r="E83" s="5" t="n">
-        <v>42.9</v>
+        <v>43.49</v>
       </c>
       <c r="F83" s="7" t="inlineStr"/>
     </row>
@@ -2330,10 +2330,10 @@
         <v>31.21</v>
       </c>
       <c r="D84" s="5" t="n">
-        <v>41.96</v>
+        <v>42.54</v>
       </c>
       <c r="E84" s="5" t="n">
-        <v>47.16</v>
+        <v>47.81</v>
       </c>
       <c r="F84" s="7" t="inlineStr"/>
     </row>
@@ -2350,10 +2350,10 @@
         <v>38.94</v>
       </c>
       <c r="D85" s="5" t="n">
-        <v>50.21</v>
+        <v>50.9</v>
       </c>
       <c r="E85" s="5" t="n">
-        <v>58.73</v>
+        <v>59.53</v>
       </c>
       <c r="F85" s="7" t="inlineStr"/>
     </row>
@@ -2370,10 +2370,10 @@
         <v>29.46</v>
       </c>
       <c r="D86" s="5" t="n">
-        <v>41.21</v>
+        <v>41.78</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>44.32</v>
+        <v>44.93</v>
       </c>
       <c r="F86" s="7" t="inlineStr"/>
     </row>
@@ -2390,10 +2390,10 @@
         <v>46.72</v>
       </c>
       <c r="D87" s="5" t="n">
-        <v>52.47</v>
+        <v>53.19</v>
       </c>
       <c r="E87" s="5" t="n">
-        <v>70.12</v>
+        <v>71.09</v>
       </c>
       <c r="F87" s="7" t="inlineStr"/>
     </row>
@@ -2410,10 +2410,10 @@
         <v>25.76</v>
       </c>
       <c r="D88" s="5" t="n">
-        <v>36.19</v>
+        <v>36.69</v>
       </c>
       <c r="E88" s="5" t="n">
-        <v>38.57</v>
+        <v>39.1</v>
       </c>
       <c r="F88" s="7" t="inlineStr"/>
     </row>
@@ -2430,10 +2430,10 @@
         <v>24.27</v>
       </c>
       <c r="D89" s="5" t="n">
-        <v>33.87</v>
+        <v>34.34</v>
       </c>
       <c r="E89" s="5" t="n">
-        <v>36.29</v>
+        <v>36.79</v>
       </c>
       <c r="F89" s="7" t="inlineStr"/>
     </row>
@@ -2450,10 +2450,10 @@
         <v>24.35</v>
       </c>
       <c r="D90" s="5" t="n">
-        <v>34.47</v>
+        <v>34.94</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>36.37</v>
+        <v>36.87</v>
       </c>
       <c r="F90" s="7" t="inlineStr"/>
     </row>
@@ -2470,10 +2470,10 @@
         <v>24.87</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>33.51</v>
+        <v>33.98</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>37.09</v>
+        <v>37.6</v>
       </c>
       <c r="F91" s="7" t="inlineStr"/>
     </row>
@@ -2490,10 +2490,10 @@
         <v>78.09</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>71.76000000000001</v>
+        <v>72.75</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>115.88</v>
+        <v>117.47</v>
       </c>
       <c r="F92" s="7" t="inlineStr"/>
     </row>
@@ -2510,10 +2510,10 @@
         <v>259.43</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>201.91</v>
+        <v>204.69</v>
       </c>
       <c r="E93" s="5" t="n">
-        <v>383</v>
+        <v>388.27</v>
       </c>
       <c r="F93" s="7" t="inlineStr"/>
     </row>
@@ -2530,10 +2530,10 @@
         <v>29.29</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>38.69</v>
+        <v>39.22</v>
       </c>
       <c r="E94" s="5" t="n">
-        <v>43.02</v>
+        <v>43.61</v>
       </c>
       <c r="F94" s="7" t="inlineStr"/>
     </row>
@@ -2550,10 +2550,10 @@
         <v>27.22</v>
       </c>
       <c r="D95" s="5" t="n">
-        <v>38.7</v>
+        <v>39.23</v>
       </c>
       <c r="E95" s="5" t="n">
-        <v>39.86</v>
+        <v>40.41</v>
       </c>
       <c r="F95" s="7" t="inlineStr"/>
     </row>
@@ -2570,10 +2570,10 @@
         <v>30.41</v>
       </c>
       <c r="D96" s="5" t="n">
-        <v>42.5</v>
+        <v>43.08</v>
       </c>
       <c r="E96" s="5" t="n">
-        <v>44.39</v>
+        <v>45</v>
       </c>
       <c r="F96" s="7" t="inlineStr"/>
     </row>
@@ -2590,10 +2590,10 @@
         <v>29.83</v>
       </c>
       <c r="D97" s="5" t="n">
-        <v>39.88</v>
+        <v>40.43</v>
       </c>
       <c r="E97" s="5" t="n">
-        <v>43.41</v>
+        <v>44.01</v>
       </c>
       <c r="F97" s="7" t="inlineStr"/>
     </row>
@@ -2610,10 +2610,10 @@
         <v>35.14</v>
       </c>
       <c r="D98" s="5" t="n">
-        <v>44.49</v>
+        <v>45.1</v>
       </c>
       <c r="E98" s="5" t="n">
-        <v>51.04</v>
+        <v>51.74</v>
       </c>
       <c r="F98" s="7" t="inlineStr"/>
     </row>
@@ -2630,10 +2630,10 @@
         <v>33.09</v>
       </c>
       <c r="D99" s="5" t="n">
-        <v>43.71</v>
+        <v>44.31</v>
       </c>
       <c r="E99" s="5" t="n">
-        <v>47.97</v>
+        <v>48.63</v>
       </c>
       <c r="F99" s="7" t="inlineStr"/>
     </row>
@@ -2650,10 +2650,10 @@
         <v>31.1</v>
       </c>
       <c r="D100" s="5" t="n">
-        <v>41.32</v>
+        <v>41.89</v>
       </c>
       <c r="E100" s="5" t="n">
-        <v>44.99</v>
+        <v>45.61</v>
       </c>
       <c r="F100" s="7" t="inlineStr"/>
     </row>
@@ -2670,10 +2670,10 @@
         <v>30.68</v>
       </c>
       <c r="D101" s="5" t="n">
-        <v>41.26</v>
+        <v>41.83</v>
       </c>
       <c r="E101" s="5" t="n">
-        <v>44.39</v>
+        <v>45</v>
       </c>
       <c r="F101" s="7" t="inlineStr"/>
     </row>
@@ -2690,10 +2690,10 @@
         <v>47.76</v>
       </c>
       <c r="D102" s="5" t="n">
-        <v>53.7</v>
+        <v>54.44</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>69.09999999999999</v>
+        <v>70.05</v>
       </c>
       <c r="F102" s="7" t="inlineStr"/>
     </row>
@@ -2710,10 +2710,10 @@
         <v>27.5</v>
       </c>
       <c r="D103" s="5" t="n">
-        <v>37.3</v>
+        <v>37.81</v>
       </c>
       <c r="E103" s="5" t="n">
-        <v>39.79</v>
+        <v>40.33</v>
       </c>
       <c r="F103" s="7" t="inlineStr"/>
     </row>
@@ -2730,10 +2730,10 @@
         <v>28.43</v>
       </c>
       <c r="D104" s="5" t="n">
-        <v>36.26</v>
+        <v>36.76</v>
       </c>
       <c r="E104" s="5" t="n">
-        <v>41.12</v>
+        <v>41.69</v>
       </c>
       <c r="F104" s="7" t="inlineStr"/>
     </row>
@@ -2750,10 +2750,10 @@
         <v>29.48</v>
       </c>
       <c r="D105" s="5" t="n">
-        <v>38.89</v>
+        <v>39.42</v>
       </c>
       <c r="E105" s="5" t="n">
-        <v>42.63</v>
+        <v>43.22</v>
       </c>
       <c r="F105" s="7" t="inlineStr"/>
     </row>
@@ -2770,10 +2770,10 @@
         <v>28.13</v>
       </c>
       <c r="D106" s="5" t="n">
-        <v>36.81</v>
+        <v>37.32</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>40.67</v>
+        <v>41.23</v>
       </c>
       <c r="F106" s="7" t="inlineStr"/>
     </row>
@@ -2790,10 +2790,10 @@
         <v>36.78</v>
       </c>
       <c r="D107" s="5" t="n">
-        <v>48.38</v>
+        <v>49.05</v>
       </c>
       <c r="E107" s="5" t="n">
-        <v>53.09</v>
+        <v>53.82</v>
       </c>
       <c r="F107" s="7" t="inlineStr"/>
     </row>
@@ -2810,10 +2810,10 @@
         <v>30.61</v>
       </c>
       <c r="D108" s="5" t="n">
-        <v>41.37</v>
+        <v>41.94</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>44.11</v>
+        <v>44.71</v>
       </c>
       <c r="F108" s="7" t="inlineStr"/>
     </row>
@@ -2830,10 +2830,10 @@
         <v>40.68</v>
       </c>
       <c r="D109" s="5" t="n">
-        <v>51.8</v>
+        <v>52.51</v>
       </c>
       <c r="E109" s="5" t="n">
-        <v>58.52</v>
+        <v>59.32</v>
       </c>
       <c r="F109" s="7" t="inlineStr"/>
     </row>
@@ -2850,10 +2850,10 @@
         <v>74.02</v>
       </c>
       <c r="D110" s="9" t="n">
-        <v>94.84</v>
+        <v>96.14</v>
       </c>
       <c r="E110" s="9" t="n">
-        <v>106</v>
+        <v>107.45</v>
       </c>
       <c r="F110" s="10" t="inlineStr">
         <is>
@@ -2874,10 +2874,10 @@
         <v>59.12</v>
       </c>
       <c r="D111" s="9" t="n">
-        <v>81.83</v>
+        <v>82.95</v>
       </c>
       <c r="E111" s="9" t="n">
-        <v>84.28</v>
+        <v>85.44</v>
       </c>
       <c r="F111" s="10" t="inlineStr">
         <is>
@@ -2898,10 +2898,10 @@
         <v>54.32</v>
       </c>
       <c r="D112" s="9" t="n">
-        <v>74.86</v>
+        <v>75.89</v>
       </c>
       <c r="E112" s="9" t="n">
-        <v>77.09</v>
+        <v>78.15000000000001</v>
       </c>
       <c r="F112" s="10" t="inlineStr">
         <is>
@@ -2922,10 +2922,10 @@
         <v>60.96</v>
       </c>
       <c r="D113" s="9" t="n">
-        <v>80.92</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="E113" s="9" t="n">
-        <v>86.44</v>
+        <v>87.63</v>
       </c>
       <c r="F113" s="10" t="inlineStr">
         <is>
@@ -2946,10 +2946,10 @@
         <v>62.23</v>
       </c>
       <c r="D114" s="9" t="n">
-        <v>80.58</v>
+        <v>81.69</v>
       </c>
       <c r="E114" s="9" t="n">
-        <v>88.16</v>
+        <v>89.38</v>
       </c>
       <c r="F114" s="10" t="inlineStr">
         <is>
@@ -2970,10 +2970,10 @@
         <v>50.48</v>
       </c>
       <c r="D115" s="9" t="n">
-        <v>70.51000000000001</v>
+        <v>71.48</v>
       </c>
       <c r="E115" s="9" t="n">
-        <v>71.45999999999999</v>
+        <v>72.44</v>
       </c>
       <c r="F115" s="10" t="inlineStr">
         <is>
@@ -2994,10 +2994,10 @@
         <v>53.13</v>
       </c>
       <c r="D116" s="9" t="n">
-        <v>71.48999999999999</v>
+        <v>72.47</v>
       </c>
       <c r="E116" s="9" t="n">
-        <v>75.12</v>
+        <v>76.16</v>
       </c>
       <c r="F116" s="10" t="inlineStr">
         <is>
@@ -3018,10 +3018,10 @@
         <v>54.42</v>
       </c>
       <c r="D117" s="9" t="n">
-        <v>73.61</v>
+        <v>74.62</v>
       </c>
       <c r="E117" s="9" t="n">
-        <v>76.86</v>
+        <v>77.92</v>
       </c>
       <c r="F117" s="10" t="inlineStr">
         <is>
@@ -3042,10 +3042,10 @@
         <v>54.87</v>
       </c>
       <c r="D118" s="9" t="n">
-        <v>74.08</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="E118" s="9" t="n">
-        <v>77.41</v>
+        <v>78.47</v>
       </c>
       <c r="F118" s="10" t="inlineStr">
         <is>
@@ -3066,10 +3066,10 @@
         <v>57.39</v>
       </c>
       <c r="D119" s="9" t="n">
-        <v>76.13</v>
+        <v>77.17</v>
       </c>
       <c r="E119" s="9" t="n">
-        <v>80.86</v>
+        <v>81.97</v>
       </c>
       <c r="F119" s="10" t="inlineStr">
         <is>
@@ -3090,10 +3090,10 @@
         <v>59.18</v>
       </c>
       <c r="D120" s="9" t="n">
-        <v>77.5</v>
+        <v>78.56</v>
       </c>
       <c r="E120" s="9" t="n">
-        <v>83.28</v>
+        <v>84.42</v>
       </c>
       <c r="F120" s="10" t="inlineStr">
         <is>
@@ -3114,10 +3114,10 @@
         <v>59.67</v>
       </c>
       <c r="D121" s="9" t="n">
-        <v>79.41</v>
+        <v>80.5</v>
       </c>
       <c r="E121" s="9" t="n">
-        <v>83.86</v>
+        <v>85.02</v>
       </c>
       <c r="F121" s="10" t="inlineStr">
         <is>
@@ -3138,10 +3138,10 @@
         <v>60.88</v>
       </c>
       <c r="D122" s="9" t="n">
-        <v>80.92</v>
+        <v>82.03</v>
       </c>
       <c r="E122" s="9" t="n">
-        <v>85.22</v>
+        <v>86.39</v>
       </c>
       <c r="F122" s="10" t="inlineStr">
         <is>
@@ -3162,10 +3162,10 @@
         <v>56.37</v>
       </c>
       <c r="D123" s="9" t="n">
-        <v>75.66</v>
+        <v>76.7</v>
       </c>
       <c r="E123" s="9" t="n">
-        <v>78.59</v>
+        <v>79.67</v>
       </c>
       <c r="F123" s="10" t="inlineStr">
         <is>
@@ -3186,10 +3186,10 @@
         <v>54.35</v>
       </c>
       <c r="D124" s="9" t="n">
-        <v>73.19</v>
+        <v>74.2</v>
       </c>
       <c r="E124" s="9" t="n">
-        <v>75.47</v>
+        <v>76.5</v>
       </c>
       <c r="F124" s="10" t="inlineStr">
         <is>
@@ -3210,10 +3210,10 @@
         <v>52.4</v>
       </c>
       <c r="D125" s="9" t="n">
-        <v>71.34</v>
+        <v>72.31999999999999</v>
       </c>
       <c r="E125" s="9" t="n">
-        <v>72.58</v>
+        <v>73.58</v>
       </c>
       <c r="F125" s="10" t="inlineStr">
         <is>
@@ -3234,10 +3234,10 @@
         <v>51.68</v>
       </c>
       <c r="D126" s="9" t="n">
-        <v>69.77</v>
+        <v>70.73</v>
       </c>
       <c r="E126" s="9" t="n">
-        <v>71.42</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="F126" s="10" t="inlineStr">
         <is>
@@ -3258,10 +3258,10 @@
         <v>70.8</v>
       </c>
       <c r="D127" s="9" t="n">
-        <v>81.38</v>
+        <v>82.5</v>
       </c>
       <c r="E127" s="9" t="n">
-        <v>97.59999999999999</v>
+        <v>98.95</v>
       </c>
       <c r="F127" s="10" t="inlineStr">
         <is>
@@ -3282,10 +3282,10 @@
         <v>56.72</v>
       </c>
       <c r="D128" s="9" t="n">
-        <v>71.7</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="E128" s="9" t="n">
-        <v>78.04000000000001</v>
+        <v>79.11</v>
       </c>
       <c r="F128" s="10" t="inlineStr">
         <is>
@@ -3306,10 +3306,10 @@
         <v>52.88</v>
       </c>
       <c r="D129" s="9" t="n">
-        <v>69.09999999999999</v>
+        <v>70.05</v>
       </c>
       <c r="E129" s="9" t="n">
-        <v>72.61</v>
+        <v>73.61</v>
       </c>
       <c r="F129" s="10" t="inlineStr">
         <is>
@@ -3330,10 +3330,10 @@
         <v>51.65</v>
       </c>
       <c r="D130" s="9" t="n">
-        <v>66.72</v>
+        <v>67.63</v>
       </c>
       <c r="E130" s="9" t="n">
-        <v>70.79000000000001</v>
+        <v>71.76000000000001</v>
       </c>
       <c r="F130" s="10" t="inlineStr">
         <is>
@@ -3354,10 +3354,10 @@
         <v>50.39</v>
       </c>
       <c r="D131" s="9" t="n">
-        <v>66.52</v>
+        <v>67.44</v>
       </c>
       <c r="E131" s="9" t="n">
-        <v>68.94</v>
+        <v>69.89</v>
       </c>
       <c r="F131" s="10" t="inlineStr">
         <is>
@@ -3378,10 +3378,10 @@
         <v>56.06</v>
       </c>
       <c r="D132" s="9" t="n">
-        <v>70.15000000000001</v>
+        <v>71.12</v>
       </c>
       <c r="E132" s="9" t="n">
-        <v>76.56999999999999</v>
+        <v>77.63</v>
       </c>
       <c r="F132" s="10" t="inlineStr">
         <is>
@@ -3402,10 +3402,10 @@
         <v>51.67</v>
       </c>
       <c r="D133" s="9" t="n">
-        <v>67.83</v>
+        <v>68.76000000000001</v>
       </c>
       <c r="E133" s="9" t="n">
-        <v>70.45999999999999</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="F133" s="10" t="inlineStr">
         <is>
@@ -3426,10 +3426,10 @@
         <v>44.55</v>
       </c>
       <c r="D134" s="5" t="n">
-        <v>56.13</v>
+        <v>56.9</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>60.66</v>
+        <v>61.5</v>
       </c>
       <c r="F134" s="7" t="inlineStr"/>
     </row>
@@ -3446,10 +3446,10 @@
         <v>40.13</v>
       </c>
       <c r="D135" s="5" t="n">
-        <v>49.07</v>
+        <v>49.75</v>
       </c>
       <c r="E135" s="5" t="n">
-        <v>54.57</v>
+        <v>55.32</v>
       </c>
       <c r="F135" s="7" t="inlineStr"/>
     </row>
@@ -3466,10 +3466,10 @@
         <v>44.84</v>
       </c>
       <c r="D136" s="5" t="n">
-        <v>54.27</v>
+        <v>55.02</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>60.89</v>
+        <v>61.72</v>
       </c>
       <c r="F136" s="7" t="inlineStr"/>
     </row>
@@ -3486,10 +3486,10 @@
         <v>34.1</v>
       </c>
       <c r="D137" s="5" t="n">
-        <v>42.9</v>
+        <v>43.49</v>
       </c>
       <c r="E137" s="5" t="n">
-        <v>46.27</v>
+        <v>46.91</v>
       </c>
       <c r="F137" s="7" t="inlineStr"/>
     </row>
@@ -3506,10 +3506,10 @@
         <v>41.02</v>
       </c>
       <c r="D138" s="5" t="n">
-        <v>45.72</v>
+        <v>46.35</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>55.63</v>
+        <v>56.4</v>
       </c>
       <c r="F138" s="7" t="inlineStr"/>
     </row>
@@ -3526,10 +3526,10 @@
         <v>35.12</v>
       </c>
       <c r="D139" s="5" t="n">
-        <v>41.54</v>
+        <v>42.11</v>
       </c>
       <c r="E139" s="5" t="n">
-        <v>47.6</v>
+        <v>48.25</v>
       </c>
       <c r="F139" s="7" t="inlineStr"/>
     </row>
@@ -3546,10 +3546,10 @@
         <v>47.17</v>
       </c>
       <c r="D140" s="5" t="n">
-        <v>50.05</v>
+        <v>50.74</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>63.89</v>
+        <v>64.77</v>
       </c>
       <c r="F140" s="7" t="inlineStr"/>
     </row>
@@ -3566,10 +3566,10 @@
         <v>38.88</v>
       </c>
       <c r="D141" s="5" t="n">
-        <v>45.29</v>
+        <v>45.91</v>
       </c>
       <c r="E141" s="5" t="n">
-        <v>52.63</v>
+        <v>53.35</v>
       </c>
       <c r="F141" s="7" t="inlineStr"/>
     </row>
@@ -3586,10 +3586,10 @@
         <v>35.83</v>
       </c>
       <c r="D142" s="5" t="n">
-        <v>41.65</v>
+        <v>42.22</v>
       </c>
       <c r="E142" s="5" t="n">
-        <v>48.47</v>
+        <v>49.14</v>
       </c>
       <c r="F142" s="7" t="inlineStr"/>
     </row>
@@ -3606,10 +3606,10 @@
         <v>42.98</v>
       </c>
       <c r="D143" s="5" t="n">
-        <v>48.37</v>
+        <v>49.03</v>
       </c>
       <c r="E143" s="5" t="n">
-        <v>58</v>
+        <v>58.8</v>
       </c>
       <c r="F143" s="7" t="inlineStr"/>
     </row>
@@ -3626,10 +3626,10 @@
         <v>41.54</v>
       </c>
       <c r="D144" s="5" t="n">
-        <v>48.05</v>
+        <v>48.71</v>
       </c>
       <c r="E144" s="5" t="n">
-        <v>55.93</v>
+        <v>56.7</v>
       </c>
       <c r="F144" s="7" t="inlineStr"/>
     </row>
@@ -3646,10 +3646,10 @@
         <v>40.75</v>
       </c>
       <c r="D145" s="5" t="n">
-        <v>48.47</v>
+        <v>49.14</v>
       </c>
       <c r="E145" s="5" t="n">
-        <v>54.73</v>
+        <v>55.49</v>
       </c>
       <c r="F145" s="7" t="inlineStr"/>
     </row>
@@ -3666,10 +3666,10 @@
         <v>43.87</v>
       </c>
       <c r="D146" s="5" t="n">
-        <v>52.52</v>
+        <v>53.24</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>58.85</v>
+        <v>59.66</v>
       </c>
       <c r="F146" s="7" t="inlineStr"/>
     </row>
@@ -3686,10 +3686,10 @@
         <v>40.45</v>
       </c>
       <c r="D147" s="5" t="n">
-        <v>49.23</v>
+        <v>49.91</v>
       </c>
       <c r="E147" s="5" t="n">
-        <v>54.19</v>
+        <v>54.94</v>
       </c>
       <c r="F147" s="7" t="inlineStr"/>
     </row>
@@ -3706,10 +3706,10 @@
         <v>76.97</v>
       </c>
       <c r="D148" s="5" t="n">
-        <v>77.59999999999999</v>
+        <v>78.67</v>
       </c>
       <c r="E148" s="5" t="n">
-        <v>102.98</v>
+        <v>104.4</v>
       </c>
       <c r="F148" s="7" t="inlineStr"/>
     </row>
@@ -3726,10 +3726,10 @@
         <v>41.94</v>
       </c>
       <c r="D149" s="5" t="n">
-        <v>49.09</v>
+        <v>49.77</v>
       </c>
       <c r="E149" s="5" t="n">
-        <v>56.04</v>
+        <v>56.81</v>
       </c>
       <c r="F149" s="7" t="inlineStr"/>
     </row>
@@ -3746,10 +3746,10 @@
         <v>62.06</v>
       </c>
       <c r="D150" s="5" t="n">
-        <v>61.28</v>
+        <v>62.12</v>
       </c>
       <c r="E150" s="5" t="n">
-        <v>82.81999999999999</v>
+        <v>83.95999999999999</v>
       </c>
       <c r="F150" s="7" t="inlineStr"/>
     </row>
@@ -3766,10 +3766,10 @@
         <v>50.61</v>
       </c>
       <c r="D151" s="5" t="n">
-        <v>59.39</v>
+        <v>60.21</v>
       </c>
       <c r="E151" s="5" t="n">
-        <v>67.45</v>
+        <v>68.38</v>
       </c>
       <c r="F151" s="7" t="inlineStr"/>
     </row>
@@ -3786,10 +3786,10 @@
         <v>60.64</v>
       </c>
       <c r="D152" s="5" t="n">
-        <v>60.3</v>
+        <v>61.13</v>
       </c>
       <c r="E152" s="5" t="n">
-        <v>80.87</v>
+        <v>81.98999999999999</v>
       </c>
       <c r="F152" s="7" t="inlineStr"/>
     </row>
@@ -3806,10 +3806,10 @@
         <v>45.94</v>
       </c>
       <c r="D153" s="5" t="n">
-        <v>51.79</v>
+        <v>52.51</v>
       </c>
       <c r="E153" s="5" t="n">
-        <v>61.31</v>
+        <v>62.15</v>
       </c>
       <c r="F153" s="7" t="inlineStr"/>
     </row>
@@ -3826,10 +3826,10 @@
         <v>49.96</v>
       </c>
       <c r="D154" s="5" t="n">
-        <v>59.64</v>
+        <v>60.46</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>66.72</v>
+        <v>67.64</v>
       </c>
       <c r="F154" s="7" t="inlineStr"/>
     </row>
@@ -3846,10 +3846,10 @@
         <v>78</v>
       </c>
       <c r="D155" s="5" t="n">
-        <v>88.05</v>
+        <v>89.26000000000001</v>
       </c>
       <c r="E155" s="5" t="n">
-        <v>104.01</v>
+        <v>105.44</v>
       </c>
       <c r="F155" s="7" t="inlineStr"/>
     </row>
@@ -3866,10 +3866,10 @@
         <v>81.53</v>
       </c>
       <c r="D156" s="5" t="n">
-        <v>89.02</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>108.56</v>
+        <v>110.06</v>
       </c>
       <c r="F156" s="7" t="inlineStr"/>
     </row>
@@ -3886,10 +3886,10 @@
         <v>121.82</v>
       </c>
       <c r="D157" s="5" t="n">
-        <v>129.89</v>
+        <v>131.68</v>
       </c>
       <c r="E157" s="5" t="n">
-        <v>161.97</v>
+        <v>164.2</v>
       </c>
       <c r="F157" s="7" t="inlineStr"/>
     </row>
@@ -3906,10 +3906,10 @@
         <v>86.11</v>
       </c>
       <c r="D158" s="5" t="n">
-        <v>87.66</v>
+        <v>88.86</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>114.23</v>
+        <v>115.8</v>
       </c>
       <c r="F158" s="7" t="inlineStr"/>
     </row>
@@ -3926,10 +3926,10 @@
         <v>58.75</v>
       </c>
       <c r="D159" s="5" t="n">
-        <v>63.66</v>
+        <v>64.53</v>
       </c>
       <c r="E159" s="5" t="n">
-        <v>77.75</v>
+        <v>78.81999999999999</v>
       </c>
       <c r="F159" s="7" t="inlineStr"/>
     </row>
@@ -3946,10 +3946,10 @@
         <v>50.15</v>
       </c>
       <c r="D160" s="5" t="n">
-        <v>59.26</v>
+        <v>60.07</v>
       </c>
       <c r="E160" s="5" t="n">
-        <v>66.22</v>
+        <v>67.13</v>
       </c>
       <c r="F160" s="7" t="inlineStr"/>
     </row>
@@ -3966,10 +3966,10 @@
         <v>60.61</v>
       </c>
       <c r="D161" s="5" t="n">
-        <v>72.8</v>
+        <v>73.8</v>
       </c>
       <c r="E161" s="5" t="n">
-        <v>79.89</v>
+        <v>80.98</v>
       </c>
       <c r="F161" s="7" t="inlineStr"/>
     </row>
@@ -3986,10 +3986,10 @@
         <v>114.97</v>
       </c>
       <c r="D162" s="5" t="n">
-        <v>109.38</v>
+        <v>110.88</v>
       </c>
       <c r="E162" s="5" t="n">
-        <v>151.27</v>
+        <v>153.35</v>
       </c>
       <c r="F162" s="7" t="inlineStr"/>
     </row>
@@ -4006,10 +4006,10 @@
         <v>59.62</v>
       </c>
       <c r="D163" s="5" t="n">
-        <v>67.68000000000001</v>
+        <v>68.61</v>
       </c>
       <c r="E163" s="5" t="n">
-        <v>78.31</v>
+        <v>79.38</v>
       </c>
       <c r="F163" s="7" t="inlineStr"/>
     </row>
@@ -4026,10 +4026,10 @@
         <v>106.24</v>
       </c>
       <c r="D164" s="5" t="n">
-        <v>108.44</v>
+        <v>109.93</v>
       </c>
       <c r="E164" s="5" t="n">
-        <v>139.33</v>
+        <v>141.24</v>
       </c>
       <c r="F164" s="7" t="inlineStr"/>
     </row>
@@ -4046,10 +4046,10 @@
         <v>279.63</v>
       </c>
       <c r="D165" s="5" t="n">
-        <v>233.85</v>
+        <v>237.07</v>
       </c>
       <c r="E165" s="5" t="n">
-        <v>366.16</v>
+        <v>371.19</v>
       </c>
       <c r="F165" s="7" t="inlineStr"/>
     </row>
@@ -4066,10 +4066,10 @@
         <v>110.22</v>
       </c>
       <c r="D166" s="5" t="n">
-        <v>121.21</v>
+        <v>122.88</v>
       </c>
       <c r="E166" s="5" t="n">
-        <v>144.11</v>
+        <v>146.09</v>
       </c>
       <c r="F166" s="7" t="inlineStr"/>
     </row>
@@ -4086,10 +4086,10 @@
         <v>115.63</v>
       </c>
       <c r="D167" s="5" t="n">
-        <v>139.1</v>
+        <v>141.01</v>
       </c>
       <c r="E167" s="5" t="n">
-        <v>151.08</v>
+        <v>153.16</v>
       </c>
       <c r="F167" s="7" t="inlineStr"/>
     </row>
@@ -4106,10 +4106,10 @@
         <v>96.5</v>
       </c>
       <c r="D168" s="5" t="n">
-        <v>117.09</v>
+        <v>118.7</v>
       </c>
       <c r="E168" s="5" t="n">
-        <v>126</v>
+        <v>127.74</v>
       </c>
       <c r="F168" s="7" t="inlineStr"/>
     </row>
@@ -4126,10 +4126,10 @@
         <v>90.03</v>
       </c>
       <c r="D169" s="5" t="n">
-        <v>110.73</v>
+        <v>112.26</v>
       </c>
       <c r="E169" s="5" t="n">
-        <v>117.48</v>
+        <v>119.1</v>
       </c>
       <c r="F169" s="7" t="inlineStr"/>
     </row>
@@ -4146,10 +4146,10 @@
         <v>102.1</v>
       </c>
       <c r="D170" s="5" t="n">
-        <v>118.67</v>
+        <v>120.31</v>
       </c>
       <c r="E170" s="5" t="n">
-        <v>132.96</v>
+        <v>134.79</v>
       </c>
       <c r="F170" s="7" t="inlineStr"/>
     </row>
@@ -4166,10 +4166,10 @@
         <v>112.14</v>
       </c>
       <c r="D171" s="5" t="n">
-        <v>132.75</v>
+        <v>134.58</v>
       </c>
       <c r="E171" s="5" t="n">
-        <v>145.74</v>
+        <v>147.74</v>
       </c>
       <c r="F171" s="7" t="inlineStr"/>
     </row>
@@ -4186,10 +4186,10 @@
         <v>91.84999999999999</v>
       </c>
       <c r="D172" s="5" t="n">
-        <v>113.15</v>
+        <v>114.7</v>
       </c>
       <c r="E172" s="5" t="n">
-        <v>119.13</v>
+        <v>120.76</v>
       </c>
       <c r="F172" s="7" t="inlineStr"/>
     </row>
@@ -4206,10 +4206,10 @@
         <v>90.03</v>
       </c>
       <c r="D173" s="5" t="n">
-        <v>106.35</v>
+        <v>107.81</v>
       </c>
       <c r="E173" s="5" t="n">
-        <v>116.5</v>
+        <v>118.11</v>
       </c>
       <c r="F173" s="7" t="inlineStr"/>
     </row>
@@ -4226,10 +4226,10 @@
         <v>87.13</v>
       </c>
       <c r="D174" s="5" t="n">
-        <v>101.72</v>
+        <v>103.12</v>
       </c>
       <c r="E174" s="5" t="n">
-        <v>112.5</v>
+        <v>114.05</v>
       </c>
       <c r="F174" s="7" t="inlineStr"/>
     </row>
@@ -4246,10 +4246,10 @@
         <v>87.25</v>
       </c>
       <c r="D175" s="5" t="n">
-        <v>98.63</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="E175" s="5" t="n">
-        <v>112.4</v>
+        <v>113.95</v>
       </c>
       <c r="F175" s="7" t="inlineStr"/>
     </row>
@@ -4266,10 +4266,10 @@
         <v>83.73999999999999</v>
       </c>
       <c r="D176" s="5" t="n">
-        <v>97.79000000000001</v>
+        <v>99.14</v>
       </c>
       <c r="E176" s="5" t="n">
-        <v>107.73</v>
+        <v>109.21</v>
       </c>
       <c r="F176" s="7" t="inlineStr"/>
     </row>
@@ -4286,10 +4286,10 @@
         <v>80.61</v>
       </c>
       <c r="D177" s="5" t="n">
-        <v>93.5</v>
+        <v>94.79000000000001</v>
       </c>
       <c r="E177" s="5" t="n">
-        <v>103.55</v>
+        <v>104.97</v>
       </c>
       <c r="F177" s="7" t="inlineStr"/>
     </row>
@@ -4306,10 +4306,10 @@
         <v>69.84999999999999</v>
       </c>
       <c r="D178" s="5" t="n">
-        <v>85.56999999999999</v>
+        <v>86.75</v>
       </c>
       <c r="E178" s="5" t="n">
-        <v>89.59999999999999</v>
+        <v>90.83</v>
       </c>
       <c r="F178" s="7" t="inlineStr"/>
     </row>
@@ -4326,10 +4326,10 @@
         <v>85.54000000000001</v>
       </c>
       <c r="D179" s="5" t="n">
-        <v>96.25</v>
+        <v>97.58</v>
       </c>
       <c r="E179" s="5" t="n">
-        <v>109.59</v>
+        <v>111.1</v>
       </c>
       <c r="F179" s="7" t="inlineStr"/>
     </row>
@@ -4346,10 +4346,10 @@
         <v>88.81999999999999</v>
       </c>
       <c r="D180" s="5" t="n">
-        <v>98.88</v>
+        <v>100.24</v>
       </c>
       <c r="E180" s="5" t="n">
-        <v>113.66</v>
+        <v>115.22</v>
       </c>
       <c r="F180" s="7" t="inlineStr"/>
     </row>
@@ -4366,10 +4366,10 @@
         <v>130.79</v>
       </c>
       <c r="D181" s="5" t="n">
-        <v>128.76</v>
+        <v>130.53</v>
       </c>
       <c r="E181" s="5" t="n">
-        <v>167.17</v>
+        <v>169.47</v>
       </c>
       <c r="F181" s="7" t="inlineStr"/>
     </row>
@@ -4386,10 +4386,10 @@
         <v>84.93000000000001</v>
       </c>
       <c r="D182" s="5" t="n">
-        <v>95.70999999999999</v>
+        <v>97.02</v>
       </c>
       <c r="E182" s="5" t="n">
-        <v>108.39</v>
+        <v>109.89</v>
       </c>
       <c r="F182" s="7" t="inlineStr"/>
     </row>
@@ -4406,10 +4406,10 @@
         <v>108.46</v>
       </c>
       <c r="D183" s="5" t="n">
-        <v>118.55</v>
+        <v>120.18</v>
       </c>
       <c r="E183" s="5" t="n">
-        <v>138.23</v>
+        <v>140.13</v>
       </c>
       <c r="F183" s="7" t="inlineStr"/>
     </row>
@@ -4426,10 +4426,10 @@
         <v>107.82</v>
       </c>
       <c r="D184" s="5" t="n">
-        <v>118.81</v>
+        <v>120.45</v>
       </c>
       <c r="E184" s="5" t="n">
-        <v>137.21</v>
+        <v>139.1</v>
       </c>
       <c r="F184" s="7" t="inlineStr"/>
     </row>
@@ -4446,10 +4446,10 @@
         <v>101.79</v>
       </c>
       <c r="D185" s="5" t="n">
-        <v>112.11</v>
+        <v>113.66</v>
       </c>
       <c r="E185" s="5" t="n">
-        <v>129.31</v>
+        <v>131.09</v>
       </c>
       <c r="F185" s="7" t="inlineStr"/>
     </row>
@@ -4466,10 +4466,10 @@
         <v>99.8</v>
       </c>
       <c r="D186" s="5" t="n">
-        <v>109.12</v>
+        <v>110.62</v>
       </c>
       <c r="E186" s="5" t="n">
-        <v>126.57</v>
+        <v>128.31</v>
       </c>
       <c r="F186" s="7" t="inlineStr"/>
     </row>
@@ -4486,10 +4486,10 @@
         <v>97.98</v>
       </c>
       <c r="D187" s="5" t="n">
-        <v>105.76</v>
+        <v>107.22</v>
       </c>
       <c r="E187" s="5" t="n">
-        <v>124.05</v>
+        <v>125.75</v>
       </c>
       <c r="F187" s="7" t="inlineStr"/>
     </row>
@@ -4506,10 +4506,10 @@
         <v>157.41</v>
       </c>
       <c r="D188" s="5" t="n">
-        <v>148.7</v>
+        <v>150.75</v>
       </c>
       <c r="E188" s="5" t="n">
-        <v>199.29</v>
+        <v>202.04</v>
       </c>
       <c r="F188" s="7" t="inlineStr"/>
     </row>
@@ -4526,10 +4526,10 @@
         <v>102.7</v>
       </c>
       <c r="D189" s="5" t="n">
-        <v>112.96</v>
+        <v>114.52</v>
       </c>
       <c r="E189" s="5" t="n">
-        <v>130.03</v>
+        <v>131.82</v>
       </c>
       <c r="F189" s="7" t="inlineStr"/>
     </row>
@@ -4546,10 +4546,10 @@
         <v>99.31</v>
       </c>
       <c r="D190" s="5" t="n">
-        <v>111.31</v>
+        <v>112.84</v>
       </c>
       <c r="E190" s="5" t="n">
-        <v>125.75</v>
+        <v>127.47</v>
       </c>
       <c r="F190" s="7" t="inlineStr"/>
     </row>
@@ -4566,10 +4566,10 @@
         <v>87.88</v>
       </c>
       <c r="D191" s="5" t="n">
-        <v>99.16</v>
+        <v>100.53</v>
       </c>
       <c r="E191" s="5" t="n">
-        <v>111.05</v>
+        <v>112.58</v>
       </c>
       <c r="F191" s="7" t="inlineStr"/>
     </row>
@@ -4586,10 +4586,10 @@
         <v>90.98</v>
       </c>
       <c r="D192" s="5" t="n">
-        <v>99.79000000000001</v>
+        <v>101.16</v>
       </c>
       <c r="E192" s="5" t="n">
-        <v>114.74</v>
+        <v>116.32</v>
       </c>
       <c r="F192" s="7" t="inlineStr"/>
     </row>
@@ -4606,10 +4606,10 @@
         <v>107.65</v>
       </c>
       <c r="D193" s="5" t="n">
-        <v>114.91</v>
+        <v>116.49</v>
       </c>
       <c r="E193" s="5" t="n">
-        <v>135.5</v>
+        <v>137.37</v>
       </c>
       <c r="F193" s="7" t="inlineStr"/>
     </row>
@@ -4626,10 +4626,10 @@
         <v>80.73999999999999</v>
       </c>
       <c r="D194" s="5" t="n">
-        <v>89.92</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="E194" s="5" t="n">
-        <v>101.44</v>
+        <v>102.83</v>
       </c>
       <c r="F194" s="7" t="inlineStr"/>
     </row>
@@ -4646,10 +4646,10 @@
         <v>98.62</v>
       </c>
       <c r="D195" s="5" t="n">
-        <v>105.39</v>
+        <v>106.84</v>
       </c>
       <c r="E195" s="5" t="n">
-        <v>123.67</v>
+        <v>125.37</v>
       </c>
       <c r="F195" s="7" t="inlineStr"/>
     </row>
@@ -4666,10 +4666,10 @@
         <v>110.15</v>
       </c>
       <c r="D196" s="5" t="n">
-        <v>119.68</v>
+        <v>121.33</v>
       </c>
       <c r="E196" s="5" t="n">
-        <v>137.87</v>
+        <v>139.77</v>
       </c>
       <c r="F196" s="7" t="inlineStr"/>
     </row>
@@ -4686,10 +4686,10 @@
         <v>111.43</v>
       </c>
       <c r="D197" s="5" t="n">
-        <v>127.09</v>
+        <v>128.84</v>
       </c>
       <c r="E197" s="5" t="n">
-        <v>139.15</v>
+        <v>141.07</v>
       </c>
       <c r="F197" s="7" t="inlineStr"/>
     </row>
@@ -4706,10 +4706,10 @@
         <v>72.06</v>
       </c>
       <c r="D198" s="5" t="n">
-        <v>87.09</v>
+        <v>88.29000000000001</v>
       </c>
       <c r="E198" s="5" t="n">
-        <v>89.78</v>
+        <v>91.02</v>
       </c>
       <c r="F198" s="7" t="inlineStr"/>
     </row>
@@ -4726,10 +4726,10 @@
         <v>54.5</v>
       </c>
       <c r="D199" s="5" t="n">
-        <v>64.75</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="E199" s="5" t="n">
-        <v>67.75</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="F199" s="7" t="inlineStr"/>
     </row>
@@ -4746,10 +4746,10 @@
         <v>185.41</v>
       </c>
       <c r="D200" s="5" t="n">
-        <v>189.09</v>
+        <v>191.69</v>
       </c>
       <c r="E200" s="5" t="n">
-        <v>230.2</v>
+        <v>233.37</v>
       </c>
       <c r="F200" s="7" t="inlineStr"/>
     </row>
@@ -4766,10 +4766,10 @@
         <v>59.42</v>
       </c>
       <c r="D201" s="5" t="n">
-        <v>71.3</v>
+        <v>72.28</v>
       </c>
       <c r="E201" s="5" t="n">
-        <v>73.68000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="F201" s="7" t="inlineStr"/>
     </row>
@@ -4786,10 +4786,10 @@
         <v>51.4</v>
       </c>
       <c r="D202" s="5" t="n">
-        <v>57.17</v>
+        <v>57.96</v>
       </c>
       <c r="E202" s="5" t="n">
-        <v>63.66</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="F202" s="7" t="inlineStr"/>
     </row>
@@ -4806,10 +4806,10 @@
         <v>45.3</v>
       </c>
       <c r="D203" s="5" t="n">
-        <v>50.32</v>
+        <v>51.01</v>
       </c>
       <c r="E203" s="5" t="n">
-        <v>56.47</v>
+        <v>57.24</v>
       </c>
       <c r="F203" s="7" t="inlineStr"/>
     </row>
@@ -4826,10 +4826,10 @@
         <v>48.48</v>
       </c>
       <c r="D204" s="5" t="n">
-        <v>52.63</v>
+        <v>53.36</v>
       </c>
       <c r="E204" s="5" t="n">
-        <v>60.82</v>
+        <v>61.66</v>
       </c>
       <c r="F204" s="7" t="inlineStr"/>
     </row>
@@ -4846,10 +4846,10 @@
         <v>60.43</v>
       </c>
       <c r="D205" s="5" t="n">
-        <v>60.73</v>
+        <v>61.57</v>
       </c>
       <c r="E205" s="5" t="n">
-        <v>76.31</v>
+        <v>77.36</v>
       </c>
       <c r="F205" s="7" t="inlineStr"/>
     </row>
@@ -4866,10 +4866,10 @@
         <v>56.33</v>
       </c>
       <c r="D206" s="5" t="n">
-        <v>60.28</v>
+        <v>61.11</v>
       </c>
       <c r="E206" s="5" t="n">
-        <v>70.77</v>
+        <v>71.73999999999999</v>
       </c>
       <c r="F206" s="7" t="inlineStr"/>
     </row>
@@ -4886,10 +4886,10 @@
         <v>60.22</v>
       </c>
       <c r="D207" s="5" t="n">
-        <v>62.32</v>
+        <v>63.18</v>
       </c>
       <c r="E207" s="5" t="n">
-        <v>75.27</v>
+        <v>76.31</v>
       </c>
       <c r="F207" s="7" t="inlineStr"/>
     </row>
@@ -4906,10 +4906,10 @@
         <v>44.24</v>
       </c>
       <c r="D208" s="5" t="n">
-        <v>50.97</v>
+        <v>51.68</v>
       </c>
       <c r="E208" s="5" t="n">
-        <v>55.02</v>
+        <v>55.77</v>
       </c>
       <c r="F208" s="7" t="inlineStr"/>
     </row>
@@ -4926,10 +4926,10 @@
         <v>71.72</v>
       </c>
       <c r="D209" s="5" t="n">
-        <v>71.75</v>
+        <v>72.73999999999999</v>
       </c>
       <c r="E209" s="5" t="n">
-        <v>88.92</v>
+        <v>90.14</v>
       </c>
       <c r="F209" s="7" t="inlineStr"/>
     </row>
@@ -4946,10 +4946,10 @@
         <v>82.45</v>
       </c>
       <c r="D210" s="5" t="n">
-        <v>77.25</v>
+        <v>78.31</v>
       </c>
       <c r="E210" s="5" t="n">
-        <v>101.92</v>
+        <v>103.32</v>
       </c>
       <c r="F210" s="7" t="inlineStr"/>
     </row>
@@ -4966,10 +4966,10 @@
         <v>106.96</v>
       </c>
       <c r="D211" s="5" t="n">
-        <v>87.97</v>
+        <v>89.18000000000001</v>
       </c>
       <c r="E211" s="5" t="n">
-        <v>131.82</v>
+        <v>133.63</v>
       </c>
       <c r="F211" s="7" t="inlineStr"/>
     </row>
@@ -4986,10 +4986,10 @@
         <v>42.87</v>
       </c>
       <c r="D212" s="5" t="n">
-        <v>47.78</v>
+        <v>48.43</v>
       </c>
       <c r="E212" s="5" t="n">
-        <v>52.73</v>
+        <v>53.46</v>
       </c>
       <c r="F212" s="7" t="inlineStr"/>
     </row>
@@ -5006,10 +5006,10 @@
         <v>36.12</v>
       </c>
       <c r="D213" s="5" t="n">
-        <v>43.13</v>
+        <v>43.72</v>
       </c>
       <c r="E213" s="5" t="n">
-        <v>44.34</v>
+        <v>44.95</v>
       </c>
       <c r="F213" s="7" t="inlineStr"/>
     </row>
@@ -5026,10 +5026,10 @@
         <v>40.97</v>
       </c>
       <c r="D214" s="5" t="n">
-        <v>47.75</v>
+        <v>48.41</v>
       </c>
       <c r="E214" s="5" t="n">
-        <v>50.2</v>
+        <v>50.89</v>
       </c>
       <c r="F214" s="7" t="inlineStr"/>
     </row>
@@ -5046,10 +5046,10 @@
         <v>68.79000000000001</v>
       </c>
       <c r="D215" s="5" t="n">
-        <v>68.09999999999999</v>
+        <v>69.04000000000001</v>
       </c>
       <c r="E215" s="5" t="n">
-        <v>84.09</v>
+        <v>85.23999999999999</v>
       </c>
       <c r="F215" s="7" t="inlineStr"/>
     </row>
@@ -5066,10 +5066,10 @@
         <v>183.33</v>
       </c>
       <c r="D216" s="5" t="n">
-        <v>143.39</v>
+        <v>145.36</v>
       </c>
       <c r="E216" s="5" t="n">
-        <v>223.55</v>
+        <v>226.63</v>
       </c>
       <c r="F216" s="7" t="inlineStr"/>
     </row>
@@ -5086,10 +5086,10 @@
         <v>255.16</v>
       </c>
       <c r="D217" s="5" t="n">
-        <v>194.68</v>
+        <v>197.36</v>
       </c>
       <c r="E217" s="5" t="n">
-        <v>310.39</v>
+        <v>314.66</v>
       </c>
       <c r="F217" s="7" t="inlineStr"/>
     </row>
@@ -5106,10 +5106,10 @@
         <v>173.79</v>
       </c>
       <c r="D218" s="5" t="n">
-        <v>150.43</v>
+        <v>152.49</v>
       </c>
       <c r="E218" s="5" t="n">
-        <v>210.81</v>
+        <v>213.71</v>
       </c>
       <c r="F218" s="7" t="inlineStr"/>
     </row>
@@ -5126,10 +5126,10 @@
         <v>66.06999999999999</v>
       </c>
       <c r="D219" s="5" t="n">
-        <v>72.76000000000001</v>
+        <v>73.76000000000001</v>
       </c>
       <c r="E219" s="5" t="n">
-        <v>79.92</v>
+        <v>81.02</v>
       </c>
       <c r="F219" s="7" t="inlineStr"/>
     </row>
@@ -5146,10 +5146,10 @@
         <v>47.75</v>
       </c>
       <c r="D220" s="5" t="n">
-        <v>58.98</v>
+        <v>59.79</v>
       </c>
       <c r="E220" s="5" t="n">
-        <v>57.6</v>
+        <v>58.39</v>
       </c>
       <c r="F220" s="7" t="inlineStr"/>
     </row>
@@ -5166,10 +5166,10 @@
         <v>59.06</v>
       </c>
       <c r="D221" s="5" t="n">
-        <v>68.61</v>
+        <v>69.55</v>
       </c>
       <c r="E221" s="5" t="n">
-        <v>70.94</v>
+        <v>71.91</v>
       </c>
       <c r="F221" s="7" t="inlineStr"/>
     </row>
@@ -5186,10 +5186,10 @@
         <v>72.52</v>
       </c>
       <c r="D222" s="5" t="n">
-        <v>77.06999999999999</v>
+        <v>78.13</v>
       </c>
       <c r="E222" s="5" t="n">
-        <v>86.73999999999999</v>
+        <v>87.93000000000001</v>
       </c>
       <c r="F222" s="7" t="inlineStr"/>
     </row>
@@ -5206,10 +5206,10 @@
         <v>69.08</v>
       </c>
       <c r="D223" s="5" t="n">
-        <v>80.94</v>
+        <v>82.06</v>
       </c>
       <c r="E223" s="5" t="n">
-        <v>82.28</v>
+        <v>83.41</v>
       </c>
       <c r="F223" s="7" t="inlineStr"/>
     </row>
@@ -5226,10 +5226,10 @@
         <v>81.23999999999999</v>
       </c>
       <c r="D224" s="5" t="n">
-        <v>91.25</v>
+        <v>92.51000000000001</v>
       </c>
       <c r="E224" s="5" t="n">
-        <v>96.06999999999999</v>
+        <v>97.39</v>
       </c>
       <c r="F224" s="7" t="inlineStr"/>
     </row>
@@ -5246,10 +5246,10 @@
         <v>92.36</v>
       </c>
       <c r="D225" s="5" t="n">
-        <v>97.48999999999999</v>
+        <v>98.83</v>
       </c>
       <c r="E225" s="5" t="n">
-        <v>108.44</v>
+        <v>109.93</v>
       </c>
       <c r="F225" s="7" t="inlineStr"/>
     </row>
@@ -5266,10 +5266,10 @@
         <v>104.67</v>
       </c>
       <c r="D226" s="5" t="n">
-        <v>117.38</v>
+        <v>118.99</v>
       </c>
       <c r="E226" s="5" t="n">
-        <v>122.03</v>
+        <v>123.71</v>
       </c>
       <c r="F226" s="7" t="inlineStr"/>
     </row>
@@ -5286,10 +5286,10 @@
         <v>204.07</v>
       </c>
       <c r="D227" s="5" t="n">
-        <v>216.57</v>
+        <v>219.55</v>
       </c>
       <c r="E227" s="5" t="n">
-        <v>236.5</v>
+        <v>239.75</v>
       </c>
       <c r="F227" s="7" t="inlineStr"/>
     </row>
@@ -5306,10 +5306,10 @@
         <v>385.21</v>
       </c>
       <c r="D228" s="5" t="n">
-        <v>369.22</v>
+        <v>374.3</v>
       </c>
       <c r="E228" s="5" t="n">
-        <v>443.8</v>
+        <v>449.9</v>
       </c>
       <c r="F228" s="7" t="inlineStr"/>
     </row>
@@ -5326,10 +5326,10 @@
         <v>441.06</v>
       </c>
       <c r="D229" s="5" t="n">
-        <v>455.89</v>
+        <v>462.16</v>
       </c>
       <c r="E229" s="5" t="n">
-        <v>505.16</v>
+        <v>512.11</v>
       </c>
       <c r="F229" s="7" t="inlineStr"/>
     </row>
@@ -5346,10 +5346,10 @@
         <v>425.89</v>
       </c>
       <c r="D230" s="5" t="n">
-        <v>422.53</v>
+        <v>428.34</v>
       </c>
       <c r="E230" s="5" t="n">
-        <v>484.82</v>
+        <v>491.49</v>
       </c>
       <c r="F230" s="7" t="inlineStr"/>
     </row>
@@ -5366,10 +5366,10 @@
         <v>156.59</v>
       </c>
       <c r="D231" s="5" t="n">
-        <v>167.82</v>
+        <v>170.13</v>
       </c>
       <c r="E231" s="5" t="n">
-        <v>177.18</v>
+        <v>179.61</v>
       </c>
       <c r="F231" s="7" t="inlineStr"/>
     </row>
@@ -5386,10 +5386,10 @@
         <v>157.38</v>
       </c>
       <c r="D232" s="5" t="n">
-        <v>173.05</v>
+        <v>175.43</v>
       </c>
       <c r="E232" s="5" t="n">
-        <v>177</v>
+        <v>179.43</v>
       </c>
       <c r="F232" s="7" t="inlineStr"/>
     </row>
@@ -5406,10 +5406,10 @@
         <v>155.91</v>
       </c>
       <c r="D233" s="5" t="n">
-        <v>169.51</v>
+        <v>171.84</v>
       </c>
       <c r="E233" s="5" t="n">
-        <v>174.27</v>
+        <v>176.67</v>
       </c>
       <c r="F233" s="7" t="inlineStr"/>
     </row>
@@ -5426,10 +5426,10 @@
         <v>106.68</v>
       </c>
       <c r="D234" s="5" t="n">
-        <v>125.43</v>
+        <v>127.15</v>
       </c>
       <c r="E234" s="5" t="n">
-        <v>118.52</v>
+        <v>120.15</v>
       </c>
       <c r="F234" s="7" t="inlineStr"/>
     </row>
@@ -5446,10 +5446,10 @@
         <v>72.58</v>
       </c>
       <c r="D235" s="5" t="n">
-        <v>91.25</v>
+        <v>92.51000000000001</v>
       </c>
       <c r="E235" s="5" t="n">
-        <v>80.15000000000001</v>
+        <v>81.25</v>
       </c>
       <c r="F235" s="7" t="inlineStr"/>
     </row>
@@ -5466,10 +5466,10 @@
         <v>95.95</v>
       </c>
       <c r="D236" s="5" t="n">
-        <v>103.76</v>
+        <v>105.19</v>
       </c>
       <c r="E236" s="5" t="n">
-        <v>105.48</v>
+        <v>106.93</v>
       </c>
       <c r="F236" s="7" t="inlineStr"/>
     </row>
@@ -5486,10 +5486,10 @@
         <v>96.16</v>
       </c>
       <c r="D237" s="5" t="n">
-        <v>98.63</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="E237" s="5" t="n">
-        <v>105.23</v>
+        <v>106.68</v>
       </c>
       <c r="F237" s="7" t="inlineStr"/>
     </row>
@@ -5506,10 +5506,10 @@
         <v>134.91</v>
       </c>
       <c r="D238" s="5" t="n">
-        <v>126.39</v>
+        <v>128.13</v>
       </c>
       <c r="E238" s="5" t="n">
-        <v>146.98</v>
+        <v>149</v>
       </c>
       <c r="F238" s="7" t="inlineStr"/>
     </row>
@@ -5526,10 +5526,10 @@
         <v>116.44</v>
       </c>
       <c r="D239" s="5" t="n">
-        <v>120.41</v>
+        <v>122.07</v>
       </c>
       <c r="E239" s="5" t="n">
-        <v>126.5</v>
+        <v>128.24</v>
       </c>
       <c r="F239" s="7" t="inlineStr"/>
     </row>
@@ -5546,10 +5546,10 @@
         <v>230.59</v>
       </c>
       <c r="D240" s="5" t="n">
-        <v>210.15</v>
+        <v>213.04</v>
       </c>
       <c r="E240" s="5" t="n">
-        <v>249.8</v>
+        <v>253.23</v>
       </c>
       <c r="F240" s="7" t="inlineStr"/>
     </row>
@@ -5566,10 +5566,10 @@
         <v>123.7</v>
       </c>
       <c r="D241" s="5" t="n">
-        <v>113.64</v>
+        <v>115.2</v>
       </c>
       <c r="E241" s="5" t="n">
-        <v>133.62</v>
+        <v>135.46</v>
       </c>
       <c r="F241" s="7" t="inlineStr"/>
     </row>
@@ -5586,10 +5586,10 @@
         <v>93.78</v>
       </c>
       <c r="D242" s="5" t="n">
-        <v>90.55</v>
+        <v>91.8</v>
       </c>
       <c r="E242" s="5" t="n">
-        <v>100.92</v>
+        <v>102.3</v>
       </c>
       <c r="F242" s="7" t="inlineStr"/>
     </row>
@@ -5606,10 +5606,10 @@
         <v>104.72</v>
       </c>
       <c r="D243" s="5" t="n">
-        <v>100.03</v>
+        <v>101.4</v>
       </c>
       <c r="E243" s="5" t="n">
-        <v>112.26</v>
+        <v>113.8</v>
       </c>
       <c r="F243" s="7" t="inlineStr"/>
     </row>
@@ -5626,10 +5626,10 @@
         <v>70.17</v>
       </c>
       <c r="D244" s="5" t="n">
-        <v>68.92</v>
+        <v>69.87</v>
       </c>
       <c r="E244" s="5" t="n">
-        <v>74.94</v>
+        <v>75.97</v>
       </c>
       <c r="F244" s="7" t="inlineStr"/>
     </row>
@@ -5646,10 +5646,10 @@
         <v>41.9</v>
       </c>
       <c r="D245" s="5" t="n">
-        <v>44.84</v>
+        <v>45.46</v>
       </c>
       <c r="E245" s="5" t="n">
-        <v>44.65</v>
+        <v>45.27</v>
       </c>
       <c r="F245" s="7" t="inlineStr"/>
     </row>
@@ -5666,10 +5666,10 @@
         <v>94.34999999999999</v>
       </c>
       <c r="D246" s="5" t="n">
-        <v>92.89</v>
+        <v>94.17</v>
       </c>
       <c r="E246" s="5" t="n">
-        <v>100.34</v>
+        <v>101.72</v>
       </c>
       <c r="F246" s="7" t="inlineStr"/>
     </row>
@@ -5686,10 +5686,10 @@
         <v>81.66</v>
       </c>
       <c r="D247" s="5" t="n">
-        <v>72.44</v>
+        <v>73.44</v>
       </c>
       <c r="E247" s="5" t="n">
-        <v>86.66</v>
+        <v>87.84999999999999</v>
       </c>
       <c r="F247" s="7" t="inlineStr"/>
     </row>
@@ -5706,10 +5706,10 @@
         <v>80.48</v>
       </c>
       <c r="D248" s="5" t="n">
-        <v>85.88</v>
+        <v>87.06</v>
       </c>
       <c r="E248" s="5" t="n">
-        <v>85.15000000000001</v>
+        <v>86.31999999999999</v>
       </c>
       <c r="F248" s="7" t="inlineStr"/>
     </row>
@@ -5726,10 +5726,10 @@
         <v>160.9</v>
       </c>
       <c r="D249" s="5" t="n">
-        <v>117.77</v>
+        <v>119.39</v>
       </c>
       <c r="E249" s="5" t="n">
-        <v>169.7</v>
+        <v>172.04</v>
       </c>
       <c r="F249" s="7" t="inlineStr"/>
     </row>
@@ -5746,10 +5746,10 @@
         <v>70.48999999999999</v>
       </c>
       <c r="D250" s="5" t="n">
-        <v>74.09999999999999</v>
+        <v>75.12</v>
       </c>
       <c r="E250" s="5" t="n">
-        <v>74.12</v>
+        <v>75.14</v>
       </c>
       <c r="F250" s="7" t="inlineStr"/>
     </row>
@@ -5766,10 +5766,10 @@
         <v>86.27</v>
       </c>
       <c r="D251" s="5" t="n">
-        <v>94.12</v>
+        <v>95.42</v>
       </c>
       <c r="E251" s="5" t="n">
-        <v>90.39</v>
+        <v>91.64</v>
       </c>
       <c r="F251" s="7" t="inlineStr"/>
     </row>
@@ -5786,10 +5786,10 @@
         <v>430.06</v>
       </c>
       <c r="D252" s="5" t="n">
-        <v>285.64</v>
+        <v>289.57</v>
       </c>
       <c r="E252" s="5" t="n">
-        <v>449.05</v>
+        <v>455.23</v>
       </c>
       <c r="F252" s="7" t="inlineStr"/>
     </row>
@@ -5806,10 +5806,10 @@
         <v>173.97</v>
       </c>
       <c r="D253" s="5" t="n">
-        <v>158.94</v>
+        <v>161.13</v>
       </c>
       <c r="E253" s="5" t="n">
-        <v>181.03</v>
+        <v>183.52</v>
       </c>
       <c r="F253" s="7" t="inlineStr"/>
     </row>
@@ -5826,10 +5826,10 @@
         <v>155.59</v>
       </c>
       <c r="D254" s="5" t="n">
-        <v>132.23</v>
+        <v>134.05</v>
       </c>
       <c r="E254" s="5" t="n">
-        <v>161.78</v>
+        <v>164.01</v>
       </c>
       <c r="F254" s="7" t="inlineStr"/>
     </row>
@@ -5846,10 +5846,10 @@
         <v>253.4</v>
       </c>
       <c r="D255" s="5" t="n">
-        <v>181.26</v>
+        <v>183.76</v>
       </c>
       <c r="E255" s="5" t="n">
-        <v>263.29</v>
+        <v>266.92</v>
       </c>
       <c r="F255" s="7" t="inlineStr"/>
     </row>
@@ -5866,10 +5866,10 @@
         <v>49.3</v>
       </c>
       <c r="D256" s="5" t="n">
-        <v>60.24</v>
+        <v>61.07</v>
       </c>
       <c r="E256" s="5" t="n">
-        <v>51.19</v>
+        <v>51.89</v>
       </c>
       <c r="F256" s="7" t="inlineStr"/>
     </row>
@@ -5886,10 +5886,10 @@
         <v>81.59</v>
       </c>
       <c r="D257" s="5" t="n">
-        <v>80.31999999999999</v>
+        <v>81.43000000000001</v>
       </c>
       <c r="E257" s="5" t="n">
-        <v>84.66</v>
+        <v>85.81999999999999</v>
       </c>
       <c r="F257" s="7" t="inlineStr"/>
     </row>
@@ -5906,10 +5906,10 @@
         <v>359.37</v>
       </c>
       <c r="D258" s="5" t="n">
-        <v>227.79</v>
+        <v>230.93</v>
       </c>
       <c r="E258" s="5" t="n">
-        <v>372.64</v>
+        <v>377.77</v>
       </c>
       <c r="F258" s="7" t="inlineStr"/>
     </row>
@@ -5926,10 +5926,10 @@
         <v>173.92</v>
       </c>
       <c r="D259" s="5" t="n">
-        <v>139.61</v>
+        <v>141.54</v>
       </c>
       <c r="E259" s="5" t="n">
-        <v>180.23</v>
+        <v>182.7</v>
       </c>
       <c r="F259" s="7" t="inlineStr"/>
     </row>
@@ -5946,10 +5946,10 @@
         <v>93.90000000000001</v>
       </c>
       <c r="D260" s="5" t="n">
-        <v>86.09999999999999</v>
+        <v>87.28</v>
       </c>
       <c r="E260" s="5" t="n">
-        <v>97.01000000000001</v>
+        <v>98.34</v>
       </c>
       <c r="F260" s="7" t="inlineStr"/>
     </row>
@@ -5966,10 +5966,10 @@
         <v>99.90000000000001</v>
       </c>
       <c r="D261" s="5" t="n">
-        <v>93.03</v>
+        <v>94.31</v>
       </c>
       <c r="E261" s="5" t="n">
-        <v>102.89</v>
+        <v>104.31</v>
       </c>
       <c r="F261" s="7" t="inlineStr"/>
     </row>
@@ -5986,10 +5986,10 @@
         <v>82.47</v>
       </c>
       <c r="D262" s="5" t="n">
-        <v>92.37</v>
+        <v>93.64</v>
       </c>
       <c r="E262" s="5" t="n">
-        <v>84.68000000000001</v>
+        <v>85.84999999999999</v>
       </c>
       <c r="F262" s="7" t="inlineStr"/>
     </row>
@@ -6006,10 +6006,10 @@
         <v>107.35</v>
       </c>
       <c r="D263" s="5" t="n">
-        <v>106.6</v>
+        <v>108.06</v>
       </c>
       <c r="E263" s="5" t="n">
-        <v>109.95</v>
+        <v>111.47</v>
       </c>
       <c r="F263" s="7" t="inlineStr"/>
     </row>
@@ -6026,10 +6026,10 @@
         <v>162.22</v>
       </c>
       <c r="D264" s="5" t="n">
-        <v>125.69</v>
+        <v>127.42</v>
       </c>
       <c r="E264" s="5" t="n">
-        <v>165.74</v>
+        <v>168.02</v>
       </c>
       <c r="F264" s="7" t="inlineStr"/>
     </row>
@@ -6046,10 +6046,10 @@
         <v>435.34</v>
       </c>
       <c r="D265" s="5" t="n">
-        <v>261.12</v>
+        <v>264.71</v>
       </c>
       <c r="E265" s="5" t="n">
-        <v>443.7</v>
+        <v>449.8</v>
       </c>
       <c r="F265" s="7" t="inlineStr"/>
     </row>
@@ -6066,10 +6066,10 @@
         <v>107.33</v>
       </c>
       <c r="D266" s="5" t="n">
-        <v>98.38</v>
+        <v>99.73</v>
       </c>
       <c r="E266" s="5" t="n">
-        <v>108.91</v>
+        <v>110.41</v>
       </c>
       <c r="F266" s="7" t="inlineStr"/>
     </row>
@@ -6086,10 +6086,10 @@
         <v>112.68</v>
       </c>
       <c r="D267" s="5" t="n">
-        <v>102.29</v>
+        <v>103.7</v>
       </c>
       <c r="E267" s="5" t="n">
-        <v>113.84</v>
+        <v>115.41</v>
       </c>
       <c r="F267" s="7" t="inlineStr"/>
     </row>
@@ -6106,10 +6106,10 @@
         <v>66.42</v>
       </c>
       <c r="D268" s="5" t="n">
-        <v>71.66</v>
+        <v>72.65000000000001</v>
       </c>
       <c r="E268" s="5" t="n">
-        <v>66.81</v>
+        <v>67.73</v>
       </c>
       <c r="F268" s="7" t="inlineStr"/>
     </row>
@@ -6126,10 +6126,10 @@
         <v>75.34999999999999</v>
       </c>
       <c r="D269" s="5" t="n">
-        <v>77.31999999999999</v>
+        <v>78.39</v>
       </c>
       <c r="E269" s="5" t="n">
-        <v>75.65000000000001</v>
+        <v>76.69</v>
       </c>
       <c r="F269" s="7" t="inlineStr"/>
     </row>
@@ -6146,10 +6146,10 @@
         <v>83.58</v>
       </c>
       <c r="D270" s="5" t="n">
-        <v>77.08</v>
+        <v>78.14</v>
       </c>
       <c r="E270" s="5" t="n">
-        <v>83.73999999999999</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="F270" s="7" t="inlineStr"/>
     </row>
@@ -6166,10 +6166,10 @@
         <v>77.75</v>
       </c>
       <c r="D271" s="5" t="n">
-        <v>71.36</v>
+        <v>72.34</v>
       </c>
       <c r="E271" s="5" t="n">
-        <v>77.75</v>
+        <v>78.81999999999999</v>
       </c>
       <c r="F271" s="7" t="inlineStr"/>
     </row>
@@ -6186,10 +6186,10 @@
         <v>45.49</v>
       </c>
       <c r="D272" s="5" t="n">
-        <v>67.22</v>
+        <v>67.83</v>
       </c>
       <c r="E272" s="5" t="n">
-        <v>45.49</v>
+        <v>45.91</v>
       </c>
       <c r="F272" s="7" t="inlineStr"/>
     </row>
@@ -6206,10 +6206,10 @@
         <v>97.18000000000001</v>
       </c>
       <c r="D273" s="5" t="n">
-        <v>83.76000000000001</v>
+        <v>84.14</v>
       </c>
       <c r="E273" s="5" t="n">
-        <v>97.18000000000001</v>
+        <v>97.62</v>
       </c>
       <c r="F273" s="7" t="inlineStr"/>
     </row>
@@ -6252,6 +6252,26 @@
         <v>60.42</v>
       </c>
       <c r="F275" s="7" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="4" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="B276" s="5" t="n">
+        <v>65.76000000000001</v>
+      </c>
+      <c r="C276" s="5" t="n">
+        <v>63.17</v>
+      </c>
+      <c r="D276" s="5" t="n">
+        <v>65.76000000000001</v>
+      </c>
+      <c r="E276" s="5" t="n">
+        <v>63.17</v>
+      </c>
+      <c r="F276" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6264,7 +6284,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E275"/>
+  <dimension ref="A1:E276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6314,10 +6334,10 @@
         <v>75.81999999999999</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>85.73999999999999</v>
+        <v>86.92</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>138.99</v>
+        <v>140.91</v>
       </c>
     </row>
     <row r="3">
@@ -6333,10 +6353,10 @@
         <v>22.06</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>35.88</v>
+        <v>36.38</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>40.36</v>
+        <v>40.92</v>
       </c>
     </row>
     <row r="4">
@@ -6352,10 +6372,10 @@
         <v>26.29</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>38.44</v>
+        <v>38.97</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>48.01</v>
+        <v>48.67</v>
       </c>
     </row>
     <row r="5">
@@ -6371,10 +6391,10 @@
         <v>19.41</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>31.9</v>
+        <v>32.34</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>35.39</v>
+        <v>35.87</v>
       </c>
     </row>
     <row r="6">
@@ -6390,10 +6410,10 @@
         <v>20.74</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>33.43</v>
+        <v>33.89</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>37.75</v>
+        <v>38.26</v>
       </c>
     </row>
     <row r="7">
@@ -6409,10 +6429,10 @@
         <v>29.68</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>42.48</v>
+        <v>43.06</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>53.92</v>
+        <v>54.66</v>
       </c>
     </row>
     <row r="8">
@@ -6428,10 +6448,10 @@
         <v>31.61</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>48.47</v>
+        <v>49.14</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>57.26</v>
+        <v>58.05</v>
       </c>
     </row>
     <row r="9">
@@ -6447,10 +6467,10 @@
         <v>49.01</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>105.65</v>
+        <v>107.11</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>88.51000000000001</v>
+        <v>89.73</v>
       </c>
     </row>
     <row r="10">
@@ -6466,10 +6486,10 @@
         <v>116.77</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>114.76</v>
+        <v>116.34</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>210.27</v>
+        <v>213.17</v>
       </c>
     </row>
     <row r="11">
@@ -6485,10 +6505,10 @@
         <v>37.43</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>54.42</v>
+        <v>55.17</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>67.3</v>
+        <v>68.22</v>
       </c>
     </row>
     <row r="12">
@@ -6504,10 +6524,10 @@
         <v>37.85</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>57.66</v>
+        <v>58.45</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>67.95</v>
+        <v>68.88</v>
       </c>
     </row>
     <row r="13">
@@ -6523,10 +6543,10 @@
         <v>33.72</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>55.89</v>
+        <v>56.66</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>60.44</v>
+        <v>61.27</v>
       </c>
     </row>
     <row r="14">
@@ -6542,10 +6562,10 @@
         <v>43.57</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>63.78</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>77.98999999999999</v>
+        <v>79.06</v>
       </c>
     </row>
     <row r="15">
@@ -6561,10 +6581,10 @@
         <v>26.2</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>42.2</v>
+        <v>42.78</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>46.83</v>
+        <v>47.48</v>
       </c>
     </row>
     <row r="16">
@@ -6580,10 +6600,10 @@
         <v>32.32</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>50.3</v>
+        <v>50.99</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>57.69</v>
+        <v>58.49</v>
       </c>
     </row>
     <row r="17">
@@ -6599,10 +6619,10 @@
         <v>125.43</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>123.92</v>
+        <v>125.63</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>223.33</v>
+        <v>226.4</v>
       </c>
     </row>
     <row r="18">
@@ -6618,10 +6638,10 @@
         <v>131.39</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>137.99</v>
+        <v>139.89</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>233.35</v>
+        <v>236.56</v>
       </c>
     </row>
     <row r="19">
@@ -6637,10 +6657,10 @@
         <v>110.88</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>114.95</v>
+        <v>116.53</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>196.42</v>
+        <v>199.13</v>
       </c>
     </row>
     <row r="20">
@@ -6656,10 +6676,10 @@
         <v>65.59999999999999</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>70.53</v>
+        <v>71.5</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>115.95</v>
+        <v>117.55</v>
       </c>
     </row>
     <row r="21">
@@ -6675,10 +6695,10 @@
         <v>50.64</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>57.95</v>
+        <v>58.75</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>89.31</v>
+        <v>90.54000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -6694,10 +6714,10 @@
         <v>19.92</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>32.47</v>
+        <v>32.91</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>35.05</v>
+        <v>35.54</v>
       </c>
     </row>
     <row r="23">
@@ -6713,10 +6733,10 @@
         <v>36.49</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>52.51</v>
+        <v>53.23</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>64.08</v>
+        <v>64.97</v>
       </c>
     </row>
     <row r="24">
@@ -6732,10 +6752,10 @@
         <v>27.74</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>42.77</v>
+        <v>43.35</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>48.62</v>
+        <v>49.29</v>
       </c>
     </row>
     <row r="25">
@@ -6751,10 +6771,10 @@
         <v>32.42</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>46.09</v>
+        <v>46.73</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>56.71</v>
+        <v>57.49</v>
       </c>
     </row>
     <row r="26">
@@ -6770,10 +6790,10 @@
         <v>27.73</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>42.37</v>
+        <v>42.95</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>48.35</v>
+        <v>49.01</v>
       </c>
     </row>
     <row r="27">
@@ -6789,10 +6809,10 @@
         <v>36.96</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>49.47</v>
+        <v>50.15</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>64.23</v>
+        <v>65.11</v>
       </c>
     </row>
     <row r="28">
@@ -6808,10 +6828,10 @@
         <v>36.19</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>49.59</v>
+        <v>50.27</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>62.68</v>
+        <v>63.54</v>
       </c>
     </row>
     <row r="29">
@@ -6827,10 +6847,10 @@
         <v>86.17</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>81.94</v>
+        <v>83.06999999999999</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>148.99</v>
+        <v>151.04</v>
       </c>
     </row>
     <row r="30">
@@ -6846,10 +6866,10 @@
         <v>104.05</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>99.23</v>
+        <v>100.6</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>179.6</v>
+        <v>182.07</v>
       </c>
     </row>
     <row r="31">
@@ -6865,10 +6885,10 @@
         <v>127.53</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>123.29</v>
+        <v>124.99</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>219.75</v>
+        <v>222.77</v>
       </c>
     </row>
     <row r="32">
@@ -6884,10 +6904,10 @@
         <v>33.82</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>46.12</v>
+        <v>46.75</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>58.11</v>
+        <v>58.91</v>
       </c>
     </row>
     <row r="33">
@@ -6903,10 +6923,10 @@
         <v>122.66</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>110.42</v>
+        <v>111.94</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>210.15</v>
+        <v>213.05</v>
       </c>
     </row>
     <row r="34">
@@ -6922,10 +6942,10 @@
         <v>27.46</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>38.58</v>
+        <v>39.11</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>46.91</v>
+        <v>47.56</v>
       </c>
     </row>
     <row r="35">
@@ -6941,10 +6961,10 @@
         <v>23.63</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>35.03</v>
+        <v>35.51</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>40.16</v>
+        <v>40.71</v>
       </c>
     </row>
     <row r="36">
@@ -6960,10 +6980,10 @@
         <v>32.23</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>43.03</v>
+        <v>43.62</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>54.49</v>
+        <v>55.24</v>
       </c>
     </row>
     <row r="37">
@@ -6979,10 +6999,10 @@
         <v>38.39</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>52.93</v>
+        <v>53.65</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>64.56</v>
+        <v>65.45</v>
       </c>
     </row>
     <row r="38">
@@ -6998,10 +7018,10 @@
         <v>73.48999999999999</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>80</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>123.23</v>
+        <v>124.93</v>
       </c>
     </row>
     <row r="39">
@@ -7017,10 +7037,10 @@
         <v>35.43</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>49.81</v>
+        <v>50.49</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>59.24</v>
+        <v>60.05</v>
       </c>
     </row>
     <row r="40">
@@ -7036,10 +7056,10 @@
         <v>34.69</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>47.09</v>
+        <v>47.74</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>57.83</v>
+        <v>58.62</v>
       </c>
     </row>
     <row r="41">
@@ -7055,10 +7075,10 @@
         <v>30.95</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>42.24</v>
+        <v>42.82</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>51.61</v>
+        <v>52.32</v>
       </c>
     </row>
     <row r="42">
@@ -7074,10 +7094,10 @@
         <v>41.15</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>52.5</v>
+        <v>53.22</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>68.65000000000001</v>
+        <v>69.59</v>
       </c>
     </row>
     <row r="43">
@@ -7093,10 +7113,10 @@
         <v>25.26</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>35.05</v>
+        <v>35.53</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>42.16</v>
+        <v>42.74</v>
       </c>
     </row>
     <row r="44">
@@ -7112,10 +7132,10 @@
         <v>89.47</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>93.28</v>
+        <v>94.56999999999999</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>149.28</v>
+        <v>151.33</v>
       </c>
     </row>
     <row r="45">
@@ -7131,10 +7151,10 @@
         <v>62.98</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>74.66</v>
+        <v>75.69</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>105.05</v>
+        <v>106.5</v>
       </c>
     </row>
     <row r="46">
@@ -7150,10 +7170,10 @@
         <v>63.16</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>85.51000000000001</v>
+        <v>86.69</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>105.32</v>
+        <v>106.77</v>
       </c>
     </row>
     <row r="47">
@@ -7169,10 +7189,10 @@
         <v>102.26</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>129.89</v>
+        <v>131.67</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>169.83</v>
+        <v>172.16</v>
       </c>
     </row>
     <row r="48">
@@ -7188,10 +7208,10 @@
         <v>75.83</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>104.66</v>
+        <v>106.1</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>125.42</v>
+        <v>127.15</v>
       </c>
     </row>
     <row r="49">
@@ -7207,10 +7227,10 @@
         <v>397.05</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>379.96</v>
+        <v>385.19</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>654.0599999999999</v>
+        <v>663.05</v>
       </c>
     </row>
     <row r="50">
@@ -7226,10 +7246,10 @@
         <v>105.7</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>127.98</v>
+        <v>129.74</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>173.72</v>
+        <v>176.11</v>
       </c>
     </row>
     <row r="51">
@@ -7245,10 +7265,10 @@
         <v>47.17</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>65.48999999999999</v>
+        <v>66.39</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>77.34999999999999</v>
+        <v>78.41</v>
       </c>
     </row>
     <row r="52">
@@ -7264,10 +7284,10 @@
         <v>60.36</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>78.45</v>
+        <v>79.53</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>98.75</v>
+        <v>100.11</v>
       </c>
     </row>
     <row r="53">
@@ -7283,10 +7303,10 @@
         <v>55.78</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>66.41</v>
+        <v>67.33</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>90.97</v>
+        <v>92.23</v>
       </c>
     </row>
     <row r="54">
@@ -7302,10 +7322,10 @@
         <v>48.17</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>58.55</v>
+        <v>59.36</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>78.31999999999999</v>
+        <v>79.40000000000001</v>
       </c>
     </row>
     <row r="55">
@@ -7321,10 +7341,10 @@
         <v>55.55</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>65.09999999999999</v>
+        <v>65.98999999999999</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>90.04000000000001</v>
+        <v>91.28</v>
       </c>
     </row>
     <row r="56">
@@ -7340,10 +7360,10 @@
         <v>43.73</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>55</v>
+        <v>55.75</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>70.56999999999999</v>
+        <v>71.54000000000001</v>
       </c>
     </row>
     <row r="57">
@@ -7359,10 +7379,10 @@
         <v>32.22</v>
       </c>
       <c r="D57" s="5" t="n">
-        <v>43.68</v>
+        <v>44.28</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>51.76</v>
+        <v>52.48</v>
       </c>
     </row>
     <row r="58">
@@ -7378,10 +7398,10 @@
         <v>47.31</v>
       </c>
       <c r="D58" s="5" t="n">
-        <v>55.29</v>
+        <v>56.05</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>75.67</v>
+        <v>76.70999999999999</v>
       </c>
     </row>
     <row r="59">
@@ -7397,10 +7417,10 @@
         <v>40.08</v>
       </c>
       <c r="D59" s="5" t="n">
-        <v>52.93</v>
+        <v>53.66</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>63.8</v>
+        <v>64.68000000000001</v>
       </c>
     </row>
     <row r="60">
@@ -7416,10 +7436,10 @@
         <v>53.21</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>71.59999999999999</v>
+        <v>72.59</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>84.29000000000001</v>
+        <v>85.45</v>
       </c>
     </row>
     <row r="61">
@@ -7435,10 +7455,10 @@
         <v>51.05</v>
       </c>
       <c r="D61" s="5" t="n">
-        <v>65.93000000000001</v>
+        <v>66.84</v>
       </c>
       <c r="E61" s="5" t="n">
-        <v>80.48999999999999</v>
+        <v>81.59</v>
       </c>
     </row>
     <row r="62">
@@ -7454,10 +7474,10 @@
         <v>55.38</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>63.56</v>
+        <v>64.43000000000001</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>86.98</v>
+        <v>88.17</v>
       </c>
     </row>
     <row r="63">
@@ -7473,10 +7493,10 @@
         <v>48.73</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>62.45</v>
+        <v>63.31</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>76.23999999999999</v>
+        <v>77.29000000000001</v>
       </c>
     </row>
     <row r="64">
@@ -7492,10 +7512,10 @@
         <v>45.62</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>55.4</v>
+        <v>56.17</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>71.09999999999999</v>
+        <v>72.08</v>
       </c>
     </row>
     <row r="65">
@@ -7511,10 +7531,10 @@
         <v>143.1</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>127.28</v>
+        <v>129.03</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>223.26</v>
+        <v>226.33</v>
       </c>
     </row>
     <row r="66">
@@ -7530,10 +7550,10 @@
         <v>38.45</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>48.18</v>
+        <v>48.85</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>60.05</v>
+        <v>60.88</v>
       </c>
     </row>
     <row r="67">
@@ -7549,10 +7569,10 @@
         <v>27.84</v>
       </c>
       <c r="D67" s="5" t="n">
-        <v>37.39</v>
+        <v>37.9</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>43.53</v>
+        <v>44.13</v>
       </c>
     </row>
     <row r="68">
@@ -7568,10 +7588,10 @@
         <v>72.97</v>
       </c>
       <c r="D68" s="5" t="n">
-        <v>73.62</v>
+        <v>74.63</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>114.05</v>
+        <v>115.62</v>
       </c>
     </row>
     <row r="69">
@@ -7587,10 +7607,10 @@
         <v>39.35</v>
       </c>
       <c r="D69" s="5" t="n">
-        <v>64.73</v>
+        <v>65.62</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>61.48</v>
+        <v>62.33</v>
       </c>
     </row>
     <row r="70">
@@ -7606,10 +7626,10 @@
         <v>29.61</v>
       </c>
       <c r="D70" s="5" t="n">
-        <v>38.5</v>
+        <v>39.03</v>
       </c>
       <c r="E70" s="5" t="n">
-        <v>46.25</v>
+        <v>46.88</v>
       </c>
     </row>
     <row r="71">
@@ -7625,10 +7645,10 @@
         <v>47.45</v>
       </c>
       <c r="D71" s="5" t="n">
-        <v>56.15</v>
+        <v>56.92</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>73.98999999999999</v>
+        <v>75.01000000000001</v>
       </c>
     </row>
     <row r="72">
@@ -7644,10 +7664,10 @@
         <v>35.75</v>
       </c>
       <c r="D72" s="5" t="n">
-        <v>47.14</v>
+        <v>47.79</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>55.65</v>
+        <v>56.42</v>
       </c>
     </row>
     <row r="73">
@@ -7663,10 +7683,10 @@
         <v>45.82</v>
       </c>
       <c r="D73" s="5" t="n">
-        <v>53.07</v>
+        <v>53.8</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>71.20999999999999</v>
+        <v>72.19</v>
       </c>
     </row>
     <row r="74">
@@ -7682,10 +7702,10 @@
         <v>40.23</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>48.76</v>
+        <v>49.43</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>62.33</v>
+        <v>63.18</v>
       </c>
     </row>
     <row r="75">
@@ -7701,10 +7721,10 @@
         <v>27.9</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>37.53</v>
+        <v>38.05</v>
       </c>
       <c r="E75" s="5" t="n">
-        <v>43.09</v>
+        <v>43.68</v>
       </c>
     </row>
     <row r="76">
@@ -7720,10 +7740,10 @@
         <v>28.56</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>39.44</v>
+        <v>39.99</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>43.97</v>
+        <v>44.58</v>
       </c>
     </row>
     <row r="77">
@@ -7739,10 +7759,10 @@
         <v>32.65</v>
       </c>
       <c r="D77" s="5" t="n">
-        <v>42.32</v>
+        <v>42.91</v>
       </c>
       <c r="E77" s="5" t="n">
-        <v>50.18</v>
+        <v>50.87</v>
       </c>
     </row>
     <row r="78">
@@ -7758,10 +7778,10 @@
         <v>209.33</v>
       </c>
       <c r="D78" s="5" t="n">
-        <v>165.31</v>
+        <v>167.59</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>321.13</v>
+        <v>325.55</v>
       </c>
     </row>
     <row r="79">
@@ -7777,10 +7797,10 @@
         <v>186.31</v>
       </c>
       <c r="D79" s="5" t="n">
-        <v>149.12</v>
+        <v>151.18</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>285.31</v>
+        <v>289.23</v>
       </c>
     </row>
     <row r="80">
@@ -7796,10 +7816,10 @@
         <v>78.56</v>
       </c>
       <c r="D80" s="5" t="n">
-        <v>76.97</v>
+        <v>78.03</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>119.93</v>
+        <v>121.58</v>
       </c>
     </row>
     <row r="81">
@@ -7815,10 +7835,10 @@
         <v>96.8</v>
       </c>
       <c r="D81" s="5" t="n">
-        <v>84.83</v>
+        <v>86</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>147.32</v>
+        <v>149.35</v>
       </c>
     </row>
     <row r="82">
@@ -7834,10 +7854,10 @@
         <v>30.88</v>
       </c>
       <c r="D82" s="5" t="n">
-        <v>39.24</v>
+        <v>39.78</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>46.85</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="83">
@@ -7853,10 +7873,10 @@
         <v>28.33</v>
       </c>
       <c r="D83" s="5" t="n">
-        <v>37.48</v>
+        <v>37.99</v>
       </c>
       <c r="E83" s="5" t="n">
-        <v>42.9</v>
+        <v>43.49</v>
       </c>
     </row>
     <row r="84">
@@ -7872,10 +7892,10 @@
         <v>31.21</v>
       </c>
       <c r="D84" s="5" t="n">
-        <v>41.96</v>
+        <v>42.54</v>
       </c>
       <c r="E84" s="5" t="n">
-        <v>47.16</v>
+        <v>47.81</v>
       </c>
     </row>
     <row r="85">
@@ -7891,10 +7911,10 @@
         <v>38.94</v>
       </c>
       <c r="D85" s="5" t="n">
-        <v>50.21</v>
+        <v>50.9</v>
       </c>
       <c r="E85" s="5" t="n">
-        <v>58.73</v>
+        <v>59.53</v>
       </c>
     </row>
     <row r="86">
@@ -7910,10 +7930,10 @@
         <v>29.46</v>
       </c>
       <c r="D86" s="5" t="n">
-        <v>41.21</v>
+        <v>41.78</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>44.32</v>
+        <v>44.93</v>
       </c>
     </row>
     <row r="87">
@@ -7929,10 +7949,10 @@
         <v>46.72</v>
       </c>
       <c r="D87" s="5" t="n">
-        <v>52.47</v>
+        <v>53.19</v>
       </c>
       <c r="E87" s="5" t="n">
-        <v>70.12</v>
+        <v>71.09</v>
       </c>
     </row>
     <row r="88">
@@ -7948,10 +7968,10 @@
         <v>25.76</v>
       </c>
       <c r="D88" s="5" t="n">
-        <v>36.19</v>
+        <v>36.69</v>
       </c>
       <c r="E88" s="5" t="n">
-        <v>38.57</v>
+        <v>39.1</v>
       </c>
     </row>
     <row r="89">
@@ -7967,10 +7987,10 @@
         <v>24.27</v>
       </c>
       <c r="D89" s="5" t="n">
-        <v>33.87</v>
+        <v>34.34</v>
       </c>
       <c r="E89" s="5" t="n">
-        <v>36.29</v>
+        <v>36.79</v>
       </c>
     </row>
     <row r="90">
@@ -7986,10 +8006,10 @@
         <v>24.35</v>
       </c>
       <c r="D90" s="5" t="n">
-        <v>34.47</v>
+        <v>34.94</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>36.37</v>
+        <v>36.87</v>
       </c>
     </row>
     <row r="91">
@@ -8005,10 +8025,10 @@
         <v>24.87</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>33.51</v>
+        <v>33.98</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>37.09</v>
+        <v>37.6</v>
       </c>
     </row>
     <row r="92">
@@ -8024,10 +8044,10 @@
         <v>78.09</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>71.76000000000001</v>
+        <v>72.75</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>115.88</v>
+        <v>117.47</v>
       </c>
     </row>
     <row r="93">
@@ -8043,10 +8063,10 @@
         <v>259.43</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>201.91</v>
+        <v>204.69</v>
       </c>
       <c r="E93" s="5" t="n">
-        <v>383</v>
+        <v>388.27</v>
       </c>
     </row>
     <row r="94">
@@ -8062,10 +8082,10 @@
         <v>29.29</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>38.69</v>
+        <v>39.22</v>
       </c>
       <c r="E94" s="5" t="n">
-        <v>43.02</v>
+        <v>43.61</v>
       </c>
     </row>
     <row r="95">
@@ -8081,10 +8101,10 @@
         <v>27.22</v>
       </c>
       <c r="D95" s="5" t="n">
-        <v>38.7</v>
+        <v>39.23</v>
       </c>
       <c r="E95" s="5" t="n">
-        <v>39.86</v>
+        <v>40.41</v>
       </c>
     </row>
     <row r="96">
@@ -8100,10 +8120,10 @@
         <v>30.41</v>
       </c>
       <c r="D96" s="5" t="n">
-        <v>42.5</v>
+        <v>43.08</v>
       </c>
       <c r="E96" s="5" t="n">
-        <v>44.39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="97">
@@ -8119,10 +8139,10 @@
         <v>29.83</v>
       </c>
       <c r="D97" s="5" t="n">
-        <v>39.88</v>
+        <v>40.43</v>
       </c>
       <c r="E97" s="5" t="n">
-        <v>43.41</v>
+        <v>44.01</v>
       </c>
     </row>
     <row r="98">
@@ -8138,10 +8158,10 @@
         <v>35.14</v>
       </c>
       <c r="D98" s="5" t="n">
-        <v>44.49</v>
+        <v>45.1</v>
       </c>
       <c r="E98" s="5" t="n">
-        <v>51.04</v>
+        <v>51.74</v>
       </c>
     </row>
     <row r="99">
@@ -8157,10 +8177,10 @@
         <v>33.09</v>
       </c>
       <c r="D99" s="5" t="n">
-        <v>43.71</v>
+        <v>44.31</v>
       </c>
       <c r="E99" s="5" t="n">
-        <v>47.97</v>
+        <v>48.63</v>
       </c>
     </row>
     <row r="100">
@@ -8176,10 +8196,10 @@
         <v>31.1</v>
       </c>
       <c r="D100" s="5" t="n">
-        <v>41.32</v>
+        <v>41.89</v>
       </c>
       <c r="E100" s="5" t="n">
-        <v>44.99</v>
+        <v>45.61</v>
       </c>
     </row>
     <row r="101">
@@ -8195,10 +8215,10 @@
         <v>30.68</v>
       </c>
       <c r="D101" s="5" t="n">
-        <v>41.26</v>
+        <v>41.83</v>
       </c>
       <c r="E101" s="5" t="n">
-        <v>44.39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="102">
@@ -8214,10 +8234,10 @@
         <v>47.76</v>
       </c>
       <c r="D102" s="5" t="n">
-        <v>53.7</v>
+        <v>54.44</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>69.09999999999999</v>
+        <v>70.05</v>
       </c>
     </row>
     <row r="103">
@@ -8233,10 +8253,10 @@
         <v>27.5</v>
       </c>
       <c r="D103" s="5" t="n">
-        <v>37.3</v>
+        <v>37.81</v>
       </c>
       <c r="E103" s="5" t="n">
-        <v>39.79</v>
+        <v>40.33</v>
       </c>
     </row>
     <row r="104">
@@ -8252,10 +8272,10 @@
         <v>28.43</v>
       </c>
       <c r="D104" s="5" t="n">
-        <v>36.26</v>
+        <v>36.76</v>
       </c>
       <c r="E104" s="5" t="n">
-        <v>41.12</v>
+        <v>41.69</v>
       </c>
     </row>
     <row r="105">
@@ -8271,10 +8291,10 @@
         <v>29.48</v>
       </c>
       <c r="D105" s="5" t="n">
-        <v>38.89</v>
+        <v>39.42</v>
       </c>
       <c r="E105" s="5" t="n">
-        <v>42.63</v>
+        <v>43.22</v>
       </c>
     </row>
     <row r="106">
@@ -8290,10 +8310,10 @@
         <v>28.13</v>
       </c>
       <c r="D106" s="5" t="n">
-        <v>36.81</v>
+        <v>37.32</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>40.67</v>
+        <v>41.23</v>
       </c>
     </row>
     <row r="107">
@@ -8309,10 +8329,10 @@
         <v>36.78</v>
       </c>
       <c r="D107" s="5" t="n">
-        <v>48.38</v>
+        <v>49.05</v>
       </c>
       <c r="E107" s="5" t="n">
-        <v>53.09</v>
+        <v>53.82</v>
       </c>
     </row>
     <row r="108">
@@ -8328,10 +8348,10 @@
         <v>30.61</v>
       </c>
       <c r="D108" s="5" t="n">
-        <v>41.37</v>
+        <v>41.94</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>44.11</v>
+        <v>44.71</v>
       </c>
     </row>
     <row r="109">
@@ -8347,10 +8367,10 @@
         <v>40.68</v>
       </c>
       <c r="D109" s="5" t="n">
-        <v>51.8</v>
+        <v>52.51</v>
       </c>
       <c r="E109" s="5" t="n">
-        <v>58.52</v>
+        <v>59.32</v>
       </c>
     </row>
     <row r="110">
@@ -8366,10 +8386,10 @@
         <v>74.02</v>
       </c>
       <c r="D110" s="5" t="n">
-        <v>94.84</v>
+        <v>96.14</v>
       </c>
       <c r="E110" s="5" t="n">
-        <v>106</v>
+        <v>107.45</v>
       </c>
     </row>
     <row r="111">
@@ -8385,10 +8405,10 @@
         <v>59.12</v>
       </c>
       <c r="D111" s="5" t="n">
-        <v>81.83</v>
+        <v>82.95</v>
       </c>
       <c r="E111" s="5" t="n">
-        <v>84.28</v>
+        <v>85.44</v>
       </c>
     </row>
     <row r="112">
@@ -8404,10 +8424,10 @@
         <v>54.32</v>
       </c>
       <c r="D112" s="5" t="n">
-        <v>74.86</v>
+        <v>75.89</v>
       </c>
       <c r="E112" s="5" t="n">
-        <v>77.09</v>
+        <v>78.15000000000001</v>
       </c>
     </row>
     <row r="113">
@@ -8423,10 +8443,10 @@
         <v>60.96</v>
       </c>
       <c r="D113" s="5" t="n">
-        <v>80.92</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="E113" s="5" t="n">
-        <v>86.44</v>
+        <v>87.63</v>
       </c>
     </row>
     <row r="114">
@@ -8442,10 +8462,10 @@
         <v>62.23</v>
       </c>
       <c r="D114" s="5" t="n">
-        <v>80.58</v>
+        <v>81.69</v>
       </c>
       <c r="E114" s="5" t="n">
-        <v>88.16</v>
+        <v>89.38</v>
       </c>
     </row>
     <row r="115">
@@ -8461,10 +8481,10 @@
         <v>50.48</v>
       </c>
       <c r="D115" s="5" t="n">
-        <v>70.51000000000001</v>
+        <v>71.48</v>
       </c>
       <c r="E115" s="5" t="n">
-        <v>71.45999999999999</v>
+        <v>72.44</v>
       </c>
     </row>
     <row r="116">
@@ -8480,10 +8500,10 @@
         <v>53.13</v>
       </c>
       <c r="D116" s="5" t="n">
-        <v>71.48999999999999</v>
+        <v>72.47</v>
       </c>
       <c r="E116" s="5" t="n">
-        <v>75.12</v>
+        <v>76.16</v>
       </c>
     </row>
     <row r="117">
@@ -8499,10 +8519,10 @@
         <v>54.42</v>
       </c>
       <c r="D117" s="5" t="n">
-        <v>73.61</v>
+        <v>74.62</v>
       </c>
       <c r="E117" s="5" t="n">
-        <v>76.86</v>
+        <v>77.92</v>
       </c>
     </row>
     <row r="118">
@@ -8518,10 +8538,10 @@
         <v>54.87</v>
       </c>
       <c r="D118" s="5" t="n">
-        <v>74.08</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="E118" s="5" t="n">
-        <v>77.41</v>
+        <v>78.47</v>
       </c>
     </row>
     <row r="119">
@@ -8537,10 +8557,10 @@
         <v>57.39</v>
       </c>
       <c r="D119" s="5" t="n">
-        <v>76.13</v>
+        <v>77.17</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>80.86</v>
+        <v>81.97</v>
       </c>
     </row>
     <row r="120">
@@ -8556,10 +8576,10 @@
         <v>59.18</v>
       </c>
       <c r="D120" s="5" t="n">
-        <v>77.5</v>
+        <v>78.56</v>
       </c>
       <c r="E120" s="5" t="n">
-        <v>83.28</v>
+        <v>84.42</v>
       </c>
     </row>
     <row r="121">
@@ -8575,10 +8595,10 @@
         <v>59.67</v>
       </c>
       <c r="D121" s="5" t="n">
-        <v>79.41</v>
+        <v>80.5</v>
       </c>
       <c r="E121" s="5" t="n">
-        <v>83.86</v>
+        <v>85.02</v>
       </c>
     </row>
     <row r="122">
@@ -8594,10 +8614,10 @@
         <v>60.88</v>
       </c>
       <c r="D122" s="5" t="n">
-        <v>80.92</v>
+        <v>82.03</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>85.22</v>
+        <v>86.39</v>
       </c>
     </row>
     <row r="123">
@@ -8613,10 +8633,10 @@
         <v>56.37</v>
       </c>
       <c r="D123" s="5" t="n">
-        <v>75.66</v>
+        <v>76.7</v>
       </c>
       <c r="E123" s="5" t="n">
-        <v>78.59</v>
+        <v>79.67</v>
       </c>
     </row>
     <row r="124">
@@ -8632,10 +8652,10 @@
         <v>54.35</v>
       </c>
       <c r="D124" s="5" t="n">
-        <v>73.19</v>
+        <v>74.2</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>75.47</v>
+        <v>76.5</v>
       </c>
     </row>
     <row r="125">
@@ -8651,10 +8671,10 @@
         <v>52.4</v>
       </c>
       <c r="D125" s="5" t="n">
-        <v>71.34</v>
+        <v>72.31999999999999</v>
       </c>
       <c r="E125" s="5" t="n">
-        <v>72.58</v>
+        <v>73.58</v>
       </c>
     </row>
     <row r="126">
@@ -8670,10 +8690,10 @@
         <v>51.68</v>
       </c>
       <c r="D126" s="5" t="n">
-        <v>69.77</v>
+        <v>70.73</v>
       </c>
       <c r="E126" s="5" t="n">
-        <v>71.42</v>
+        <v>72.40000000000001</v>
       </c>
     </row>
     <row r="127">
@@ -8689,10 +8709,10 @@
         <v>70.8</v>
       </c>
       <c r="D127" s="5" t="n">
-        <v>81.38</v>
+        <v>82.5</v>
       </c>
       <c r="E127" s="5" t="n">
-        <v>97.59999999999999</v>
+        <v>98.95</v>
       </c>
     </row>
     <row r="128">
@@ -8708,10 +8728,10 @@
         <v>56.72</v>
       </c>
       <c r="D128" s="5" t="n">
-        <v>71.7</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="E128" s="5" t="n">
-        <v>78.04000000000001</v>
+        <v>79.11</v>
       </c>
     </row>
     <row r="129">
@@ -8727,10 +8747,10 @@
         <v>52.88</v>
       </c>
       <c r="D129" s="5" t="n">
-        <v>69.09999999999999</v>
+        <v>70.05</v>
       </c>
       <c r="E129" s="5" t="n">
-        <v>72.61</v>
+        <v>73.61</v>
       </c>
     </row>
     <row r="130">
@@ -8746,10 +8766,10 @@
         <v>51.65</v>
       </c>
       <c r="D130" s="5" t="n">
-        <v>66.72</v>
+        <v>67.63</v>
       </c>
       <c r="E130" s="5" t="n">
-        <v>70.79000000000001</v>
+        <v>71.76000000000001</v>
       </c>
     </row>
     <row r="131">
@@ -8765,10 +8785,10 @@
         <v>50.39</v>
       </c>
       <c r="D131" s="5" t="n">
-        <v>66.52</v>
+        <v>67.44</v>
       </c>
       <c r="E131" s="5" t="n">
-        <v>68.94</v>
+        <v>69.89</v>
       </c>
     </row>
     <row r="132">
@@ -8784,10 +8804,10 @@
         <v>56.06</v>
       </c>
       <c r="D132" s="5" t="n">
-        <v>70.15000000000001</v>
+        <v>71.12</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>76.56999999999999</v>
+        <v>77.63</v>
       </c>
     </row>
     <row r="133">
@@ -8803,10 +8823,10 @@
         <v>51.67</v>
       </c>
       <c r="D133" s="5" t="n">
-        <v>67.83</v>
+        <v>68.76000000000001</v>
       </c>
       <c r="E133" s="5" t="n">
-        <v>70.45999999999999</v>
+        <v>71.43000000000001</v>
       </c>
     </row>
     <row r="134">
@@ -8822,10 +8842,10 @@
         <v>44.55</v>
       </c>
       <c r="D134" s="5" t="n">
-        <v>56.13</v>
+        <v>56.9</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>60.66</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="135">
@@ -8841,10 +8861,10 @@
         <v>40.13</v>
       </c>
       <c r="D135" s="5" t="n">
-        <v>49.07</v>
+        <v>49.75</v>
       </c>
       <c r="E135" s="5" t="n">
-        <v>54.57</v>
+        <v>55.32</v>
       </c>
     </row>
     <row r="136">
@@ -8860,10 +8880,10 @@
         <v>44.84</v>
       </c>
       <c r="D136" s="5" t="n">
-        <v>54.27</v>
+        <v>55.02</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>60.89</v>
+        <v>61.72</v>
       </c>
     </row>
     <row r="137">
@@ -8879,10 +8899,10 @@
         <v>34.1</v>
       </c>
       <c r="D137" s="5" t="n">
-        <v>42.9</v>
+        <v>43.49</v>
       </c>
       <c r="E137" s="5" t="n">
-        <v>46.27</v>
+        <v>46.91</v>
       </c>
     </row>
     <row r="138">
@@ -8898,10 +8918,10 @@
         <v>41.02</v>
       </c>
       <c r="D138" s="5" t="n">
-        <v>45.72</v>
+        <v>46.35</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>55.63</v>
+        <v>56.4</v>
       </c>
     </row>
     <row r="139">
@@ -8917,10 +8937,10 @@
         <v>35.12</v>
       </c>
       <c r="D139" s="5" t="n">
-        <v>41.54</v>
+        <v>42.11</v>
       </c>
       <c r="E139" s="5" t="n">
-        <v>47.6</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="140">
@@ -8936,10 +8956,10 @@
         <v>47.17</v>
       </c>
       <c r="D140" s="5" t="n">
-        <v>50.05</v>
+        <v>50.74</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>63.89</v>
+        <v>64.77</v>
       </c>
     </row>
     <row r="141">
@@ -8955,10 +8975,10 @@
         <v>38.88</v>
       </c>
       <c r="D141" s="5" t="n">
-        <v>45.29</v>
+        <v>45.91</v>
       </c>
       <c r="E141" s="5" t="n">
-        <v>52.63</v>
+        <v>53.35</v>
       </c>
     </row>
     <row r="142">
@@ -8974,10 +8994,10 @@
         <v>35.83</v>
       </c>
       <c r="D142" s="5" t="n">
-        <v>41.65</v>
+        <v>42.22</v>
       </c>
       <c r="E142" s="5" t="n">
-        <v>48.47</v>
+        <v>49.14</v>
       </c>
     </row>
     <row r="143">
@@ -8993,10 +9013,10 @@
         <v>42.98</v>
       </c>
       <c r="D143" s="5" t="n">
-        <v>48.37</v>
+        <v>49.03</v>
       </c>
       <c r="E143" s="5" t="n">
-        <v>58</v>
+        <v>58.8</v>
       </c>
     </row>
     <row r="144">
@@ -9012,10 +9032,10 @@
         <v>41.54</v>
       </c>
       <c r="D144" s="5" t="n">
-        <v>48.05</v>
+        <v>48.71</v>
       </c>
       <c r="E144" s="5" t="n">
-        <v>55.93</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="145">
@@ -9031,10 +9051,10 @@
         <v>40.75</v>
       </c>
       <c r="D145" s="5" t="n">
-        <v>48.47</v>
+        <v>49.14</v>
       </c>
       <c r="E145" s="5" t="n">
-        <v>54.73</v>
+        <v>55.49</v>
       </c>
     </row>
     <row r="146">
@@ -9050,10 +9070,10 @@
         <v>43.87</v>
       </c>
       <c r="D146" s="5" t="n">
-        <v>52.52</v>
+        <v>53.24</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>58.85</v>
+        <v>59.66</v>
       </c>
     </row>
     <row r="147">
@@ -9069,10 +9089,10 @@
         <v>40.45</v>
       </c>
       <c r="D147" s="5" t="n">
-        <v>49.23</v>
+        <v>49.91</v>
       </c>
       <c r="E147" s="5" t="n">
-        <v>54.19</v>
+        <v>54.94</v>
       </c>
     </row>
     <row r="148">
@@ -9088,10 +9108,10 @@
         <v>76.97</v>
       </c>
       <c r="D148" s="5" t="n">
-        <v>77.59999999999999</v>
+        <v>78.67</v>
       </c>
       <c r="E148" s="5" t="n">
-        <v>102.98</v>
+        <v>104.4</v>
       </c>
     </row>
     <row r="149">
@@ -9107,10 +9127,10 @@
         <v>41.94</v>
       </c>
       <c r="D149" s="5" t="n">
-        <v>49.09</v>
+        <v>49.77</v>
       </c>
       <c r="E149" s="5" t="n">
-        <v>56.04</v>
+        <v>56.81</v>
       </c>
     </row>
     <row r="150">
@@ -9126,10 +9146,10 @@
         <v>62.06</v>
       </c>
       <c r="D150" s="5" t="n">
-        <v>61.28</v>
+        <v>62.12</v>
       </c>
       <c r="E150" s="5" t="n">
-        <v>82.81999999999999</v>
+        <v>83.95999999999999</v>
       </c>
     </row>
     <row r="151">
@@ -9145,10 +9165,10 @@
         <v>50.61</v>
       </c>
       <c r="D151" s="5" t="n">
-        <v>59.39</v>
+        <v>60.21</v>
       </c>
       <c r="E151" s="5" t="n">
-        <v>67.45</v>
+        <v>68.38</v>
       </c>
     </row>
     <row r="152">
@@ -9164,10 +9184,10 @@
         <v>60.64</v>
       </c>
       <c r="D152" s="5" t="n">
-        <v>60.3</v>
+        <v>61.13</v>
       </c>
       <c r="E152" s="5" t="n">
-        <v>80.87</v>
+        <v>81.98999999999999</v>
       </c>
     </row>
     <row r="153">
@@ -9183,10 +9203,10 @@
         <v>45.94</v>
       </c>
       <c r="D153" s="5" t="n">
-        <v>51.79</v>
+        <v>52.51</v>
       </c>
       <c r="E153" s="5" t="n">
-        <v>61.31</v>
+        <v>62.15</v>
       </c>
     </row>
     <row r="154">
@@ -9202,10 +9222,10 @@
         <v>49.96</v>
       </c>
       <c r="D154" s="5" t="n">
-        <v>59.64</v>
+        <v>60.46</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>66.72</v>
+        <v>67.64</v>
       </c>
     </row>
     <row r="155">
@@ -9221,10 +9241,10 @@
         <v>78</v>
       </c>
       <c r="D155" s="5" t="n">
-        <v>88.05</v>
+        <v>89.26000000000001</v>
       </c>
       <c r="E155" s="5" t="n">
-        <v>104.01</v>
+        <v>105.44</v>
       </c>
     </row>
     <row r="156">
@@ -9240,10 +9260,10 @@
         <v>81.53</v>
       </c>
       <c r="D156" s="5" t="n">
-        <v>89.02</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>108.56</v>
+        <v>110.06</v>
       </c>
     </row>
     <row r="157">
@@ -9259,10 +9279,10 @@
         <v>121.82</v>
       </c>
       <c r="D157" s="5" t="n">
-        <v>129.89</v>
+        <v>131.68</v>
       </c>
       <c r="E157" s="5" t="n">
-        <v>161.97</v>
+        <v>164.2</v>
       </c>
     </row>
     <row r="158">
@@ -9278,10 +9298,10 @@
         <v>86.11</v>
       </c>
       <c r="D158" s="5" t="n">
-        <v>87.66</v>
+        <v>88.86</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>114.23</v>
+        <v>115.8</v>
       </c>
     </row>
     <row r="159">
@@ -9297,10 +9317,10 @@
         <v>58.75</v>
       </c>
       <c r="D159" s="5" t="n">
-        <v>63.66</v>
+        <v>64.53</v>
       </c>
       <c r="E159" s="5" t="n">
-        <v>77.75</v>
+        <v>78.81999999999999</v>
       </c>
     </row>
     <row r="160">
@@ -9316,10 +9336,10 @@
         <v>50.15</v>
       </c>
       <c r="D160" s="5" t="n">
-        <v>59.26</v>
+        <v>60.07</v>
       </c>
       <c r="E160" s="5" t="n">
-        <v>66.22</v>
+        <v>67.13</v>
       </c>
     </row>
     <row r="161">
@@ -9335,10 +9355,10 @@
         <v>60.61</v>
       </c>
       <c r="D161" s="5" t="n">
-        <v>72.8</v>
+        <v>73.8</v>
       </c>
       <c r="E161" s="5" t="n">
-        <v>79.89</v>
+        <v>80.98</v>
       </c>
     </row>
     <row r="162">
@@ -9354,10 +9374,10 @@
         <v>114.97</v>
       </c>
       <c r="D162" s="5" t="n">
-        <v>109.38</v>
+        <v>110.88</v>
       </c>
       <c r="E162" s="5" t="n">
-        <v>151.27</v>
+        <v>153.35</v>
       </c>
     </row>
     <row r="163">
@@ -9373,10 +9393,10 @@
         <v>59.62</v>
       </c>
       <c r="D163" s="5" t="n">
-        <v>67.68000000000001</v>
+        <v>68.61</v>
       </c>
       <c r="E163" s="5" t="n">
-        <v>78.31</v>
+        <v>79.38</v>
       </c>
     </row>
     <row r="164">
@@ -9392,10 +9412,10 @@
         <v>106.24</v>
       </c>
       <c r="D164" s="5" t="n">
-        <v>108.44</v>
+        <v>109.93</v>
       </c>
       <c r="E164" s="5" t="n">
-        <v>139.33</v>
+        <v>141.24</v>
       </c>
     </row>
     <row r="165">
@@ -9411,10 +9431,10 @@
         <v>279.63</v>
       </c>
       <c r="D165" s="5" t="n">
-        <v>233.85</v>
+        <v>237.07</v>
       </c>
       <c r="E165" s="5" t="n">
-        <v>366.16</v>
+        <v>371.19</v>
       </c>
     </row>
     <row r="166">
@@ -9430,10 +9450,10 @@
         <v>110.22</v>
       </c>
       <c r="D166" s="5" t="n">
-        <v>121.21</v>
+        <v>122.88</v>
       </c>
       <c r="E166" s="5" t="n">
-        <v>144.11</v>
+        <v>146.09</v>
       </c>
     </row>
     <row r="167">
@@ -9449,10 +9469,10 @@
         <v>115.63</v>
       </c>
       <c r="D167" s="5" t="n">
-        <v>139.1</v>
+        <v>141.01</v>
       </c>
       <c r="E167" s="5" t="n">
-        <v>151.08</v>
+        <v>153.16</v>
       </c>
     </row>
     <row r="168">
@@ -9468,10 +9488,10 @@
         <v>96.5</v>
       </c>
       <c r="D168" s="5" t="n">
-        <v>117.09</v>
+        <v>118.7</v>
       </c>
       <c r="E168" s="5" t="n">
-        <v>126</v>
+        <v>127.74</v>
       </c>
     </row>
     <row r="169">
@@ -9487,10 +9507,10 @@
         <v>90.03</v>
       </c>
       <c r="D169" s="5" t="n">
-        <v>110.73</v>
+        <v>112.26</v>
       </c>
       <c r="E169" s="5" t="n">
-        <v>117.48</v>
+        <v>119.1</v>
       </c>
     </row>
     <row r="170">
@@ -9506,10 +9526,10 @@
         <v>102.1</v>
       </c>
       <c r="D170" s="5" t="n">
-        <v>118.67</v>
+        <v>120.31</v>
       </c>
       <c r="E170" s="5" t="n">
-        <v>132.96</v>
+        <v>134.79</v>
       </c>
     </row>
     <row r="171">
@@ -9525,10 +9545,10 @@
         <v>112.14</v>
       </c>
       <c r="D171" s="5" t="n">
-        <v>132.75</v>
+        <v>134.58</v>
       </c>
       <c r="E171" s="5" t="n">
-        <v>145.74</v>
+        <v>147.74</v>
       </c>
     </row>
     <row r="172">
@@ -9544,10 +9564,10 @@
         <v>91.84999999999999</v>
       </c>
       <c r="D172" s="5" t="n">
-        <v>113.15</v>
+        <v>114.7</v>
       </c>
       <c r="E172" s="5" t="n">
-        <v>119.13</v>
+        <v>120.76</v>
       </c>
     </row>
     <row r="173">
@@ -9563,10 +9583,10 @@
         <v>90.03</v>
       </c>
       <c r="D173" s="5" t="n">
-        <v>106.35</v>
+        <v>107.81</v>
       </c>
       <c r="E173" s="5" t="n">
-        <v>116.5</v>
+        <v>118.11</v>
       </c>
     </row>
     <row r="174">
@@ -9582,10 +9602,10 @@
         <v>87.13</v>
       </c>
       <c r="D174" s="5" t="n">
-        <v>101.72</v>
+        <v>103.12</v>
       </c>
       <c r="E174" s="5" t="n">
-        <v>112.5</v>
+        <v>114.05</v>
       </c>
     </row>
     <row r="175">
@@ -9601,10 +9621,10 @@
         <v>87.25</v>
       </c>
       <c r="D175" s="5" t="n">
-        <v>98.63</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="E175" s="5" t="n">
-        <v>112.4</v>
+        <v>113.95</v>
       </c>
     </row>
     <row r="176">
@@ -9620,10 +9640,10 @@
         <v>83.73999999999999</v>
       </c>
       <c r="D176" s="5" t="n">
-        <v>97.79000000000001</v>
+        <v>99.14</v>
       </c>
       <c r="E176" s="5" t="n">
-        <v>107.73</v>
+        <v>109.21</v>
       </c>
     </row>
     <row r="177">
@@ -9639,10 +9659,10 @@
         <v>80.61</v>
       </c>
       <c r="D177" s="5" t="n">
-        <v>93.5</v>
+        <v>94.79000000000001</v>
       </c>
       <c r="E177" s="5" t="n">
-        <v>103.55</v>
+        <v>104.97</v>
       </c>
     </row>
     <row r="178">
@@ -9658,10 +9678,10 @@
         <v>69.84999999999999</v>
       </c>
       <c r="D178" s="5" t="n">
-        <v>85.56999999999999</v>
+        <v>86.75</v>
       </c>
       <c r="E178" s="5" t="n">
-        <v>89.59999999999999</v>
+        <v>90.83</v>
       </c>
     </row>
     <row r="179">
@@ -9677,10 +9697,10 @@
         <v>85.54000000000001</v>
       </c>
       <c r="D179" s="5" t="n">
-        <v>96.25</v>
+        <v>97.58</v>
       </c>
       <c r="E179" s="5" t="n">
-        <v>109.59</v>
+        <v>111.1</v>
       </c>
     </row>
     <row r="180">
@@ -9696,10 +9716,10 @@
         <v>88.81999999999999</v>
       </c>
       <c r="D180" s="5" t="n">
-        <v>98.88</v>
+        <v>100.24</v>
       </c>
       <c r="E180" s="5" t="n">
-        <v>113.66</v>
+        <v>115.22</v>
       </c>
     </row>
     <row r="181">
@@ -9715,10 +9735,10 @@
         <v>130.79</v>
       </c>
       <c r="D181" s="5" t="n">
-        <v>128.76</v>
+        <v>130.53</v>
       </c>
       <c r="E181" s="5" t="n">
-        <v>167.17</v>
+        <v>169.47</v>
       </c>
     </row>
     <row r="182">
@@ -9734,10 +9754,10 @@
         <v>84.93000000000001</v>
       </c>
       <c r="D182" s="5" t="n">
-        <v>95.70999999999999</v>
+        <v>97.02</v>
       </c>
       <c r="E182" s="5" t="n">
-        <v>108.39</v>
+        <v>109.89</v>
       </c>
     </row>
     <row r="183">
@@ -9753,10 +9773,10 @@
         <v>108.46</v>
       </c>
       <c r="D183" s="5" t="n">
-        <v>118.55</v>
+        <v>120.18</v>
       </c>
       <c r="E183" s="5" t="n">
-        <v>138.23</v>
+        <v>140.13</v>
       </c>
     </row>
     <row r="184">
@@ -9772,10 +9792,10 @@
         <v>107.82</v>
       </c>
       <c r="D184" s="5" t="n">
-        <v>118.81</v>
+        <v>120.45</v>
       </c>
       <c r="E184" s="5" t="n">
-        <v>137.21</v>
+        <v>139.1</v>
       </c>
     </row>
     <row r="185">
@@ -9791,10 +9811,10 @@
         <v>101.79</v>
       </c>
       <c r="D185" s="5" t="n">
-        <v>112.11</v>
+        <v>113.66</v>
       </c>
       <c r="E185" s="5" t="n">
-        <v>129.31</v>
+        <v>131.09</v>
       </c>
     </row>
     <row r="186">
@@ -9810,10 +9830,10 @@
         <v>99.8</v>
       </c>
       <c r="D186" s="5" t="n">
-        <v>109.12</v>
+        <v>110.62</v>
       </c>
       <c r="E186" s="5" t="n">
-        <v>126.57</v>
+        <v>128.31</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9849,10 @@
         <v>97.98</v>
       </c>
       <c r="D187" s="5" t="n">
-        <v>105.76</v>
+        <v>107.22</v>
       </c>
       <c r="E187" s="5" t="n">
-        <v>124.05</v>
+        <v>125.75</v>
       </c>
     </row>
     <row r="188">
@@ -9848,10 +9868,10 @@
         <v>157.41</v>
       </c>
       <c r="D188" s="5" t="n">
-        <v>148.7</v>
+        <v>150.75</v>
       </c>
       <c r="E188" s="5" t="n">
-        <v>199.29</v>
+        <v>202.04</v>
       </c>
     </row>
     <row r="189">
@@ -9867,10 +9887,10 @@
         <v>102.7</v>
       </c>
       <c r="D189" s="5" t="n">
-        <v>112.96</v>
+        <v>114.52</v>
       </c>
       <c r="E189" s="5" t="n">
-        <v>130.03</v>
+        <v>131.82</v>
       </c>
     </row>
     <row r="190">
@@ -9886,10 +9906,10 @@
         <v>99.31</v>
       </c>
       <c r="D190" s="5" t="n">
-        <v>111.31</v>
+        <v>112.84</v>
       </c>
       <c r="E190" s="5" t="n">
-        <v>125.75</v>
+        <v>127.47</v>
       </c>
     </row>
     <row r="191">
@@ -9905,10 +9925,10 @@
         <v>87.88</v>
       </c>
       <c r="D191" s="5" t="n">
-        <v>99.16</v>
+        <v>100.53</v>
       </c>
       <c r="E191" s="5" t="n">
-        <v>111.05</v>
+        <v>112.58</v>
       </c>
     </row>
     <row r="192">
@@ -9924,10 +9944,10 @@
         <v>90.98</v>
       </c>
       <c r="D192" s="5" t="n">
-        <v>99.79000000000001</v>
+        <v>101.16</v>
       </c>
       <c r="E192" s="5" t="n">
-        <v>114.74</v>
+        <v>116.32</v>
       </c>
     </row>
     <row r="193">
@@ -9943,10 +9963,10 @@
         <v>107.65</v>
       </c>
       <c r="D193" s="5" t="n">
-        <v>114.91</v>
+        <v>116.49</v>
       </c>
       <c r="E193" s="5" t="n">
-        <v>135.5</v>
+        <v>137.37</v>
       </c>
     </row>
     <row r="194">
@@ -9962,10 +9982,10 @@
         <v>80.73999999999999</v>
       </c>
       <c r="D194" s="5" t="n">
-        <v>89.92</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="E194" s="5" t="n">
-        <v>101.44</v>
+        <v>102.83</v>
       </c>
     </row>
     <row r="195">
@@ -9981,10 +10001,10 @@
         <v>98.62</v>
       </c>
       <c r="D195" s="5" t="n">
-        <v>105.39</v>
+        <v>106.84</v>
       </c>
       <c r="E195" s="5" t="n">
-        <v>123.67</v>
+        <v>125.37</v>
       </c>
     </row>
     <row r="196">
@@ -10000,10 +10020,10 @@
         <v>110.15</v>
       </c>
       <c r="D196" s="5" t="n">
-        <v>119.68</v>
+        <v>121.33</v>
       </c>
       <c r="E196" s="5" t="n">
-        <v>137.87</v>
+        <v>139.77</v>
       </c>
     </row>
     <row r="197">
@@ -10019,10 +10039,10 @@
         <v>111.43</v>
       </c>
       <c r="D197" s="5" t="n">
-        <v>127.09</v>
+        <v>128.84</v>
       </c>
       <c r="E197" s="5" t="n">
-        <v>139.15</v>
+        <v>141.07</v>
       </c>
     </row>
     <row r="198">
@@ -10038,10 +10058,10 @@
         <v>72.06</v>
       </c>
       <c r="D198" s="5" t="n">
-        <v>87.09</v>
+        <v>88.29000000000001</v>
       </c>
       <c r="E198" s="5" t="n">
-        <v>89.78</v>
+        <v>91.02</v>
       </c>
     </row>
     <row r="199">
@@ -10057,10 +10077,10 @@
         <v>54.5</v>
       </c>
       <c r="D199" s="5" t="n">
-        <v>64.75</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="E199" s="5" t="n">
-        <v>67.75</v>
+        <v>68.68000000000001</v>
       </c>
     </row>
     <row r="200">
@@ -10076,10 +10096,10 @@
         <v>185.41</v>
       </c>
       <c r="D200" s="5" t="n">
-        <v>189.09</v>
+        <v>191.69</v>
       </c>
       <c r="E200" s="5" t="n">
-        <v>230.2</v>
+        <v>233.37</v>
       </c>
     </row>
     <row r="201">
@@ -10095,10 +10115,10 @@
         <v>59.42</v>
       </c>
       <c r="D201" s="5" t="n">
-        <v>71.3</v>
+        <v>72.28</v>
       </c>
       <c r="E201" s="5" t="n">
-        <v>73.68000000000001</v>
+        <v>74.7</v>
       </c>
     </row>
     <row r="202">
@@ -10114,10 +10134,10 @@
         <v>51.4</v>
       </c>
       <c r="D202" s="5" t="n">
-        <v>57.17</v>
+        <v>57.96</v>
       </c>
       <c r="E202" s="5" t="n">
-        <v>63.66</v>
+        <v>64.54000000000001</v>
       </c>
     </row>
     <row r="203">
@@ -10133,10 +10153,10 @@
         <v>45.3</v>
       </c>
       <c r="D203" s="5" t="n">
-        <v>50.32</v>
+        <v>51.01</v>
       </c>
       <c r="E203" s="5" t="n">
-        <v>56.47</v>
+        <v>57.24</v>
       </c>
     </row>
     <row r="204">
@@ -10152,10 +10172,10 @@
         <v>48.48</v>
       </c>
       <c r="D204" s="5" t="n">
-        <v>52.63</v>
+        <v>53.36</v>
       </c>
       <c r="E204" s="5" t="n">
-        <v>60.82</v>
+        <v>61.66</v>
       </c>
     </row>
     <row r="205">
@@ -10171,10 +10191,10 @@
         <v>60.43</v>
       </c>
       <c r="D205" s="5" t="n">
-        <v>60.73</v>
+        <v>61.57</v>
       </c>
       <c r="E205" s="5" t="n">
-        <v>76.31</v>
+        <v>77.36</v>
       </c>
     </row>
     <row r="206">
@@ -10190,10 +10210,10 @@
         <v>56.33</v>
       </c>
       <c r="D206" s="5" t="n">
-        <v>60.28</v>
+        <v>61.11</v>
       </c>
       <c r="E206" s="5" t="n">
-        <v>70.77</v>
+        <v>71.73999999999999</v>
       </c>
     </row>
     <row r="207">
@@ -10209,10 +10229,10 @@
         <v>60.22</v>
       </c>
       <c r="D207" s="5" t="n">
-        <v>62.32</v>
+        <v>63.18</v>
       </c>
       <c r="E207" s="5" t="n">
-        <v>75.27</v>
+        <v>76.31</v>
       </c>
     </row>
     <row r="208">
@@ -10228,10 +10248,10 @@
         <v>44.24</v>
       </c>
       <c r="D208" s="5" t="n">
-        <v>50.97</v>
+        <v>51.68</v>
       </c>
       <c r="E208" s="5" t="n">
-        <v>55.02</v>
+        <v>55.77</v>
       </c>
     </row>
     <row r="209">
@@ -10247,10 +10267,10 @@
         <v>71.72</v>
       </c>
       <c r="D209" s="5" t="n">
-        <v>71.75</v>
+        <v>72.73999999999999</v>
       </c>
       <c r="E209" s="5" t="n">
-        <v>88.92</v>
+        <v>90.14</v>
       </c>
     </row>
     <row r="210">
@@ -10266,10 +10286,10 @@
         <v>82.45</v>
       </c>
       <c r="D210" s="5" t="n">
-        <v>77.25</v>
+        <v>78.31</v>
       </c>
       <c r="E210" s="5" t="n">
-        <v>101.92</v>
+        <v>103.32</v>
       </c>
     </row>
     <row r="211">
@@ -10285,10 +10305,10 @@
         <v>106.96</v>
       </c>
       <c r="D211" s="5" t="n">
-        <v>87.97</v>
+        <v>89.18000000000001</v>
       </c>
       <c r="E211" s="5" t="n">
-        <v>131.82</v>
+        <v>133.63</v>
       </c>
     </row>
     <row r="212">
@@ -10304,10 +10324,10 @@
         <v>42.87</v>
       </c>
       <c r="D212" s="5" t="n">
-        <v>47.78</v>
+        <v>48.43</v>
       </c>
       <c r="E212" s="5" t="n">
-        <v>52.73</v>
+        <v>53.46</v>
       </c>
     </row>
     <row r="213">
@@ -10323,10 +10343,10 @@
         <v>36.12</v>
       </c>
       <c r="D213" s="5" t="n">
-        <v>43.13</v>
+        <v>43.72</v>
       </c>
       <c r="E213" s="5" t="n">
-        <v>44.34</v>
+        <v>44.95</v>
       </c>
     </row>
     <row r="214">
@@ -10342,10 +10362,10 @@
         <v>40.97</v>
       </c>
       <c r="D214" s="5" t="n">
-        <v>47.75</v>
+        <v>48.41</v>
       </c>
       <c r="E214" s="5" t="n">
-        <v>50.2</v>
+        <v>50.89</v>
       </c>
     </row>
     <row r="215">
@@ -10361,10 +10381,10 @@
         <v>68.79000000000001</v>
       </c>
       <c r="D215" s="5" t="n">
-        <v>68.09999999999999</v>
+        <v>69.04000000000001</v>
       </c>
       <c r="E215" s="5" t="n">
-        <v>84.09</v>
+        <v>85.23999999999999</v>
       </c>
     </row>
     <row r="216">
@@ -10380,10 +10400,10 @@
         <v>183.33</v>
       </c>
       <c r="D216" s="5" t="n">
-        <v>143.39</v>
+        <v>145.36</v>
       </c>
       <c r="E216" s="5" t="n">
-        <v>223.55</v>
+        <v>226.63</v>
       </c>
     </row>
     <row r="217">
@@ -10399,10 +10419,10 @@
         <v>255.16</v>
       </c>
       <c r="D217" s="5" t="n">
-        <v>194.68</v>
+        <v>197.36</v>
       </c>
       <c r="E217" s="5" t="n">
-        <v>310.39</v>
+        <v>314.66</v>
       </c>
     </row>
     <row r="218">
@@ -10418,10 +10438,10 @@
         <v>173.79</v>
       </c>
       <c r="D218" s="5" t="n">
-        <v>150.43</v>
+        <v>152.49</v>
       </c>
       <c r="E218" s="5" t="n">
-        <v>210.81</v>
+        <v>213.71</v>
       </c>
     </row>
     <row r="219">
@@ -10437,10 +10457,10 @@
         <v>66.06999999999999</v>
       </c>
       <c r="D219" s="5" t="n">
-        <v>72.76000000000001</v>
+        <v>73.76000000000001</v>
       </c>
       <c r="E219" s="5" t="n">
-        <v>79.92</v>
+        <v>81.02</v>
       </c>
     </row>
     <row r="220">
@@ -10456,10 +10476,10 @@
         <v>47.75</v>
       </c>
       <c r="D220" s="5" t="n">
-        <v>58.98</v>
+        <v>59.79</v>
       </c>
       <c r="E220" s="5" t="n">
-        <v>57.6</v>
+        <v>58.39</v>
       </c>
     </row>
     <row r="221">
@@ -10475,10 +10495,10 @@
         <v>59.06</v>
       </c>
       <c r="D221" s="5" t="n">
-        <v>68.61</v>
+        <v>69.55</v>
       </c>
       <c r="E221" s="5" t="n">
-        <v>70.94</v>
+        <v>71.91</v>
       </c>
     </row>
     <row r="222">
@@ -10494,10 +10514,10 @@
         <v>72.52</v>
       </c>
       <c r="D222" s="5" t="n">
-        <v>77.06999999999999</v>
+        <v>78.13</v>
       </c>
       <c r="E222" s="5" t="n">
-        <v>86.73999999999999</v>
+        <v>87.93000000000001</v>
       </c>
     </row>
     <row r="223">
@@ -10513,10 +10533,10 @@
         <v>69.08</v>
       </c>
       <c r="D223" s="5" t="n">
-        <v>80.94</v>
+        <v>82.06</v>
       </c>
       <c r="E223" s="5" t="n">
-        <v>82.28</v>
+        <v>83.41</v>
       </c>
     </row>
     <row r="224">
@@ -10532,10 +10552,10 @@
         <v>81.23999999999999</v>
       </c>
       <c r="D224" s="5" t="n">
-        <v>91.25</v>
+        <v>92.51000000000001</v>
       </c>
       <c r="E224" s="5" t="n">
-        <v>96.06999999999999</v>
+        <v>97.39</v>
       </c>
     </row>
     <row r="225">
@@ -10551,10 +10571,10 @@
         <v>92.36</v>
       </c>
       <c r="D225" s="5" t="n">
-        <v>97.48999999999999</v>
+        <v>98.83</v>
       </c>
       <c r="E225" s="5" t="n">
-        <v>108.44</v>
+        <v>109.93</v>
       </c>
     </row>
     <row r="226">
@@ -10570,10 +10590,10 @@
         <v>104.67</v>
       </c>
       <c r="D226" s="5" t="n">
-        <v>117.38</v>
+        <v>118.99</v>
       </c>
       <c r="E226" s="5" t="n">
-        <v>122.03</v>
+        <v>123.71</v>
       </c>
     </row>
     <row r="227">
@@ -10589,10 +10609,10 @@
         <v>204.07</v>
       </c>
       <c r="D227" s="5" t="n">
-        <v>216.57</v>
+        <v>219.55</v>
       </c>
       <c r="E227" s="5" t="n">
-        <v>236.5</v>
+        <v>239.75</v>
       </c>
     </row>
     <row r="228">
@@ -10608,10 +10628,10 @@
         <v>385.21</v>
       </c>
       <c r="D228" s="5" t="n">
-        <v>369.22</v>
+        <v>374.3</v>
       </c>
       <c r="E228" s="5" t="n">
-        <v>443.8</v>
+        <v>449.9</v>
       </c>
     </row>
     <row r="229">
@@ -10627,10 +10647,10 @@
         <v>441.06</v>
       </c>
       <c r="D229" s="5" t="n">
-        <v>455.89</v>
+        <v>462.16</v>
       </c>
       <c r="E229" s="5" t="n">
-        <v>505.16</v>
+        <v>512.11</v>
       </c>
     </row>
     <row r="230">
@@ -10646,10 +10666,10 @@
         <v>425.89</v>
       </c>
       <c r="D230" s="5" t="n">
-        <v>422.53</v>
+        <v>428.34</v>
       </c>
       <c r="E230" s="5" t="n">
-        <v>484.82</v>
+        <v>491.49</v>
       </c>
     </row>
     <row r="231">
@@ -10665,10 +10685,10 @@
         <v>156.59</v>
       </c>
       <c r="D231" s="5" t="n">
-        <v>167.82</v>
+        <v>170.13</v>
       </c>
       <c r="E231" s="5" t="n">
-        <v>177.18</v>
+        <v>179.61</v>
       </c>
     </row>
     <row r="232">
@@ -10684,10 +10704,10 @@
         <v>157.38</v>
       </c>
       <c r="D232" s="5" t="n">
-        <v>173.05</v>
+        <v>175.43</v>
       </c>
       <c r="E232" s="5" t="n">
-        <v>177</v>
+        <v>179.43</v>
       </c>
     </row>
     <row r="233">
@@ -10703,10 +10723,10 @@
         <v>155.91</v>
       </c>
       <c r="D233" s="5" t="n">
-        <v>169.51</v>
+        <v>171.84</v>
       </c>
       <c r="E233" s="5" t="n">
-        <v>174.27</v>
+        <v>176.67</v>
       </c>
     </row>
     <row r="234">
@@ -10722,10 +10742,10 @@
         <v>106.68</v>
       </c>
       <c r="D234" s="5" t="n">
-        <v>125.43</v>
+        <v>127.15</v>
       </c>
       <c r="E234" s="5" t="n">
-        <v>118.52</v>
+        <v>120.15</v>
       </c>
     </row>
     <row r="235">
@@ -10741,10 +10761,10 @@
         <v>72.58</v>
       </c>
       <c r="D235" s="5" t="n">
-        <v>91.25</v>
+        <v>92.51000000000001</v>
       </c>
       <c r="E235" s="5" t="n">
-        <v>80.15000000000001</v>
+        <v>81.25</v>
       </c>
     </row>
     <row r="236">
@@ -10760,10 +10780,10 @@
         <v>95.95</v>
       </c>
       <c r="D236" s="5" t="n">
-        <v>103.76</v>
+        <v>105.19</v>
       </c>
       <c r="E236" s="5" t="n">
-        <v>105.48</v>
+        <v>106.93</v>
       </c>
     </row>
     <row r="237">
@@ -10779,10 +10799,10 @@
         <v>96.16</v>
       </c>
       <c r="D237" s="5" t="n">
-        <v>98.63</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="E237" s="5" t="n">
-        <v>105.23</v>
+        <v>106.68</v>
       </c>
     </row>
     <row r="238">
@@ -10798,10 +10818,10 @@
         <v>134.91</v>
       </c>
       <c r="D238" s="5" t="n">
-        <v>126.39</v>
+        <v>128.13</v>
       </c>
       <c r="E238" s="5" t="n">
-        <v>146.98</v>
+        <v>149</v>
       </c>
     </row>
     <row r="239">
@@ -10817,10 +10837,10 @@
         <v>116.44</v>
       </c>
       <c r="D239" s="5" t="n">
-        <v>120.41</v>
+        <v>122.07</v>
       </c>
       <c r="E239" s="5" t="n">
-        <v>126.5</v>
+        <v>128.24</v>
       </c>
     </row>
     <row r="240">
@@ -10836,10 +10856,10 @@
         <v>230.59</v>
       </c>
       <c r="D240" s="5" t="n">
-        <v>210.15</v>
+        <v>213.04</v>
       </c>
       <c r="E240" s="5" t="n">
-        <v>249.8</v>
+        <v>253.23</v>
       </c>
     </row>
     <row r="241">
@@ -10855,10 +10875,10 @@
         <v>123.7</v>
       </c>
       <c r="D241" s="5" t="n">
-        <v>113.64</v>
+        <v>115.2</v>
       </c>
       <c r="E241" s="5" t="n">
-        <v>133.62</v>
+        <v>135.46</v>
       </c>
     </row>
     <row r="242">
@@ -10874,10 +10894,10 @@
         <v>93.78</v>
       </c>
       <c r="D242" s="5" t="n">
-        <v>90.55</v>
+        <v>91.8</v>
       </c>
       <c r="E242" s="5" t="n">
-        <v>100.92</v>
+        <v>102.3</v>
       </c>
     </row>
     <row r="243">
@@ -10893,10 +10913,10 @@
         <v>104.72</v>
       </c>
       <c r="D243" s="5" t="n">
-        <v>100.03</v>
+        <v>101.4</v>
       </c>
       <c r="E243" s="5" t="n">
-        <v>112.26</v>
+        <v>113.8</v>
       </c>
     </row>
     <row r="244">
@@ -10912,10 +10932,10 @@
         <v>70.17</v>
       </c>
       <c r="D244" s="5" t="n">
-        <v>68.92</v>
+        <v>69.87</v>
       </c>
       <c r="E244" s="5" t="n">
-        <v>74.94</v>
+        <v>75.97</v>
       </c>
     </row>
     <row r="245">
@@ -10931,10 +10951,10 @@
         <v>41.9</v>
       </c>
       <c r="D245" s="5" t="n">
-        <v>44.84</v>
+        <v>45.46</v>
       </c>
       <c r="E245" s="5" t="n">
-        <v>44.65</v>
+        <v>45.27</v>
       </c>
     </row>
     <row r="246">
@@ -10950,10 +10970,10 @@
         <v>94.34999999999999</v>
       </c>
       <c r="D246" s="5" t="n">
-        <v>92.89</v>
+        <v>94.17</v>
       </c>
       <c r="E246" s="5" t="n">
-        <v>100.34</v>
+        <v>101.72</v>
       </c>
     </row>
     <row r="247">
@@ -10969,10 +10989,10 @@
         <v>81.66</v>
       </c>
       <c r="D247" s="5" t="n">
-        <v>72.44</v>
+        <v>73.44</v>
       </c>
       <c r="E247" s="5" t="n">
-        <v>86.66</v>
+        <v>87.84999999999999</v>
       </c>
     </row>
     <row r="248">
@@ -10988,10 +11008,10 @@
         <v>80.48</v>
       </c>
       <c r="D248" s="5" t="n">
-        <v>85.88</v>
+        <v>87.06</v>
       </c>
       <c r="E248" s="5" t="n">
-        <v>85.15000000000001</v>
+        <v>86.31999999999999</v>
       </c>
     </row>
     <row r="249">
@@ -11007,10 +11027,10 @@
         <v>160.9</v>
       </c>
       <c r="D249" s="5" t="n">
-        <v>117.77</v>
+        <v>119.39</v>
       </c>
       <c r="E249" s="5" t="n">
-        <v>169.7</v>
+        <v>172.04</v>
       </c>
     </row>
     <row r="250">
@@ -11026,10 +11046,10 @@
         <v>70.48999999999999</v>
       </c>
       <c r="D250" s="5" t="n">
-        <v>74.09999999999999</v>
+        <v>75.12</v>
       </c>
       <c r="E250" s="5" t="n">
-        <v>74.12</v>
+        <v>75.14</v>
       </c>
     </row>
     <row r="251">
@@ -11045,10 +11065,10 @@
         <v>86.27</v>
       </c>
       <c r="D251" s="5" t="n">
-        <v>94.12</v>
+        <v>95.42</v>
       </c>
       <c r="E251" s="5" t="n">
-        <v>90.39</v>
+        <v>91.64</v>
       </c>
     </row>
     <row r="252">
@@ -11064,10 +11084,10 @@
         <v>430.06</v>
       </c>
       <c r="D252" s="5" t="n">
-        <v>285.64</v>
+        <v>289.57</v>
       </c>
       <c r="E252" s="5" t="n">
-        <v>449.05</v>
+        <v>455.23</v>
       </c>
     </row>
     <row r="253">
@@ -11083,10 +11103,10 @@
         <v>173.97</v>
       </c>
       <c r="D253" s="5" t="n">
-        <v>158.94</v>
+        <v>161.13</v>
       </c>
       <c r="E253" s="5" t="n">
-        <v>181.03</v>
+        <v>183.52</v>
       </c>
     </row>
     <row r="254">
@@ -11102,10 +11122,10 @@
         <v>155.59</v>
       </c>
       <c r="D254" s="5" t="n">
-        <v>132.23</v>
+        <v>134.05</v>
       </c>
       <c r="E254" s="5" t="n">
-        <v>161.78</v>
+        <v>164.01</v>
       </c>
     </row>
     <row r="255">
@@ -11121,10 +11141,10 @@
         <v>253.4</v>
       </c>
       <c r="D255" s="5" t="n">
-        <v>181.26</v>
+        <v>183.76</v>
       </c>
       <c r="E255" s="5" t="n">
-        <v>263.29</v>
+        <v>266.92</v>
       </c>
     </row>
     <row r="256">
@@ -11140,10 +11160,10 @@
         <v>49.3</v>
       </c>
       <c r="D256" s="5" t="n">
-        <v>60.24</v>
+        <v>61.07</v>
       </c>
       <c r="E256" s="5" t="n">
-        <v>51.19</v>
+        <v>51.89</v>
       </c>
     </row>
     <row r="257">
@@ -11159,10 +11179,10 @@
         <v>81.59</v>
       </c>
       <c r="D257" s="5" t="n">
-        <v>80.31999999999999</v>
+        <v>81.43000000000001</v>
       </c>
       <c r="E257" s="5" t="n">
-        <v>84.66</v>
+        <v>85.81999999999999</v>
       </c>
     </row>
     <row r="258">
@@ -11178,10 +11198,10 @@
         <v>359.37</v>
       </c>
       <c r="D258" s="5" t="n">
-        <v>227.79</v>
+        <v>230.93</v>
       </c>
       <c r="E258" s="5" t="n">
-        <v>372.64</v>
+        <v>377.77</v>
       </c>
     </row>
     <row r="259">
@@ -11197,10 +11217,10 @@
         <v>173.92</v>
       </c>
       <c r="D259" s="5" t="n">
-        <v>139.61</v>
+        <v>141.54</v>
       </c>
       <c r="E259" s="5" t="n">
-        <v>180.23</v>
+        <v>182.7</v>
       </c>
     </row>
     <row r="260">
@@ -11216,10 +11236,10 @@
         <v>93.90000000000001</v>
       </c>
       <c r="D260" s="5" t="n">
-        <v>86.09999999999999</v>
+        <v>87.28</v>
       </c>
       <c r="E260" s="5" t="n">
-        <v>97.01000000000001</v>
+        <v>98.34</v>
       </c>
     </row>
     <row r="261">
@@ -11235,10 +11255,10 @@
         <v>99.90000000000001</v>
       </c>
       <c r="D261" s="5" t="n">
-        <v>93.03</v>
+        <v>94.31</v>
       </c>
       <c r="E261" s="5" t="n">
-        <v>102.89</v>
+        <v>104.31</v>
       </c>
     </row>
     <row r="262">
@@ -11254,10 +11274,10 @@
         <v>82.47</v>
       </c>
       <c r="D262" s="5" t="n">
-        <v>92.37</v>
+        <v>93.64</v>
       </c>
       <c r="E262" s="5" t="n">
-        <v>84.68000000000001</v>
+        <v>85.84999999999999</v>
       </c>
     </row>
     <row r="263">
@@ -11273,10 +11293,10 @@
         <v>107.35</v>
       </c>
       <c r="D263" s="5" t="n">
-        <v>106.6</v>
+        <v>108.06</v>
       </c>
       <c r="E263" s="5" t="n">
-        <v>109.95</v>
+        <v>111.47</v>
       </c>
     </row>
     <row r="264">
@@ -11292,10 +11312,10 @@
         <v>162.22</v>
       </c>
       <c r="D264" s="5" t="n">
-        <v>125.69</v>
+        <v>127.42</v>
       </c>
       <c r="E264" s="5" t="n">
-        <v>165.74</v>
+        <v>168.02</v>
       </c>
     </row>
     <row r="265">
@@ -11311,10 +11331,10 @@
         <v>435.34</v>
       </c>
       <c r="D265" s="5" t="n">
-        <v>261.12</v>
+        <v>264.71</v>
       </c>
       <c r="E265" s="5" t="n">
-        <v>443.7</v>
+        <v>449.8</v>
       </c>
     </row>
     <row r="266">
@@ -11330,10 +11350,10 @@
         <v>107.33</v>
       </c>
       <c r="D266" s="5" t="n">
-        <v>98.38</v>
+        <v>99.73</v>
       </c>
       <c r="E266" s="5" t="n">
-        <v>108.91</v>
+        <v>110.41</v>
       </c>
     </row>
     <row r="267">
@@ -11349,10 +11369,10 @@
         <v>112.68</v>
       </c>
       <c r="D267" s="5" t="n">
-        <v>102.29</v>
+        <v>103.7</v>
       </c>
       <c r="E267" s="5" t="n">
-        <v>113.84</v>
+        <v>115.41</v>
       </c>
     </row>
     <row r="268">
@@ -11368,10 +11388,10 @@
         <v>66.42</v>
       </c>
       <c r="D268" s="5" t="n">
-        <v>71.66</v>
+        <v>72.65000000000001</v>
       </c>
       <c r="E268" s="5" t="n">
-        <v>66.81</v>
+        <v>67.73</v>
       </c>
     </row>
     <row r="269">
@@ -11387,10 +11407,10 @@
         <v>75.34999999999999</v>
       </c>
       <c r="D269" s="5" t="n">
-        <v>77.31999999999999</v>
+        <v>78.39</v>
       </c>
       <c r="E269" s="5" t="n">
-        <v>75.65000000000001</v>
+        <v>76.69</v>
       </c>
     </row>
     <row r="270">
@@ -11406,10 +11426,10 @@
         <v>83.58</v>
       </c>
       <c r="D270" s="5" t="n">
-        <v>77.08</v>
+        <v>78.14</v>
       </c>
       <c r="E270" s="5" t="n">
-        <v>83.73999999999999</v>
+        <v>84.90000000000001</v>
       </c>
     </row>
     <row r="271">
@@ -11425,10 +11445,10 @@
         <v>77.75</v>
       </c>
       <c r="D271" s="5" t="n">
-        <v>71.36</v>
+        <v>72.34</v>
       </c>
       <c r="E271" s="5" t="n">
-        <v>77.75</v>
+        <v>78.81999999999999</v>
       </c>
     </row>
     <row r="272">
@@ -11444,10 +11464,10 @@
         <v>45.49</v>
       </c>
       <c r="D272" s="5" t="n">
-        <v>67.22</v>
+        <v>67.83</v>
       </c>
       <c r="E272" s="5" t="n">
-        <v>45.49</v>
+        <v>45.91</v>
       </c>
     </row>
     <row r="273">
@@ -11463,10 +11483,10 @@
         <v>97.18000000000001</v>
       </c>
       <c r="D273" s="5" t="n">
-        <v>83.76000000000001</v>
+        <v>84.14</v>
       </c>
       <c r="E273" s="5" t="n">
-        <v>97.18000000000001</v>
+        <v>97.62</v>
       </c>
     </row>
     <row r="274">
@@ -11507,8 +11527,27 @@
         <v>60.42</v>
       </c>
     </row>
+    <row r="276">
+      <c r="A276" s="4" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="B276" s="5" t="n">
+        <v>65.76000000000001</v>
+      </c>
+      <c r="C276" s="5" t="n">
+        <v>63.17</v>
+      </c>
+      <c r="D276" s="5" t="n">
+        <v>65.76000000000001</v>
+      </c>
+      <c r="E276" s="5" t="n">
+        <v>63.17</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B275">
+  <conditionalFormatting sqref="B2:B276">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -11520,7 +11559,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C275">
+  <conditionalFormatting sqref="C2:C276">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -11532,7 +11571,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D275">
+  <conditionalFormatting sqref="D2:D276">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -11544,7 +11583,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E275">
+  <conditionalFormatting sqref="E2:E276">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>

--- a/outputs/NSW_historical_prices.xlsx
+++ b/outputs/NSW_historical_prices.xlsx
@@ -528,16 +528,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>91.93000000000001</v>
+        <v>76.3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>108.26</v>
+        <v>77.53</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>93.56999999999999</v>
+        <v>77.23</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>110.44</v>
+        <v>78.51000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>105.75</v>
+        <v>102.25</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>128.84</v>
+        <v>124.36</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>109.48</v>
+        <v>105.62</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>133.58</v>
+        <v>128.71</v>
       </c>
     </row>
     <row r="7">
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>103.05</v>
+        <v>102.03</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>125.85</v>
+        <v>124.26</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>107.93</v>
+        <v>106.63</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>131.91</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>118.07</v>
+        <v>116.55</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>138.86</v>
+        <v>135.72</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>129.98</v>
+        <v>127.83</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>152.75</v>
+        <v>148.62</v>
       </c>
     </row>
     <row r="9">
@@ -604,22 +604,22 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>97.45</v>
+        <v>97.2</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>115.09</v>
+        <v>114.63</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>114.63</v>
+        <v>114.1</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>135.38</v>
+        <v>134.56</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Data through: May 2026</t>
+          <t>Data through: Jun 2026</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F276"/>
+  <dimension ref="A1:F277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6273,6 +6273,26 @@
       </c>
       <c r="F276" s="7" t="inlineStr"/>
     </row>
+    <row r="277">
+      <c r="A277" s="4" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="B277" s="5" t="n">
+        <v>68.61</v>
+      </c>
+      <c r="C277" s="5" t="n">
+        <v>66.68000000000001</v>
+      </c>
+      <c r="D277" s="5" t="n">
+        <v>68.61</v>
+      </c>
+      <c r="E277" s="5" t="n">
+        <v>66.68000000000001</v>
+      </c>
+      <c r="F277" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6284,7 +6304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E276"/>
+  <dimension ref="A1:E277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11546,8 +11566,27 @@
         <v>63.17</v>
       </c>
     </row>
+    <row r="277">
+      <c r="A277" s="4" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="B277" s="5" t="n">
+        <v>68.61</v>
+      </c>
+      <c r="C277" s="5" t="n">
+        <v>66.68000000000001</v>
+      </c>
+      <c r="D277" s="5" t="n">
+        <v>68.61</v>
+      </c>
+      <c r="E277" s="5" t="n">
+        <v>66.68000000000001</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B276">
+  <conditionalFormatting sqref="B2:B277">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -11559,7 +11598,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C276">
+  <conditionalFormatting sqref="C2:C277">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -11571,7 +11610,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D276">
+  <conditionalFormatting sqref="D2:D277">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -11583,7 +11622,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E276">
+  <conditionalFormatting sqref="E2:E277">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>

--- a/outputs/NSW_historical_prices.xlsx
+++ b/outputs/NSW_historical_prices.xlsx
@@ -528,16 +528,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>76.3</v>
+        <v>74.84</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>77.53</v>
+        <v>75.72</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>77.23</v>
+        <v>75.54000000000001</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>78.51000000000001</v>
+        <v>76.44</v>
       </c>
     </row>
     <row r="6">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>102.25</v>
+        <v>100.26</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>124.36</v>
+        <v>121.45</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>105.62</v>
+        <v>103.35</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>128.71</v>
+        <v>125.44</v>
       </c>
     </row>
     <row r="7">
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>102.03</v>
+        <v>101.9</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>124.26</v>
+        <v>124.04</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>106.63</v>
+        <v>106.29</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>130</v>
+        <v>129.53</v>
       </c>
     </row>
     <row r="8">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>116.55</v>
+        <v>115.81</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>135.72</v>
+        <v>134.25</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>127.83</v>
+        <v>126.61</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>148.62</v>
+        <v>146.48</v>
       </c>
     </row>
     <row r="9">
@@ -604,22 +604,22 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>97.2</v>
+        <v>97.31999999999999</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>114.63</v>
+        <v>114.62</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>114.1</v>
+        <v>114.02</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>134.56</v>
+        <v>134.31</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Data through: Jun 2026</t>
+          <t>Data through: Jul 2026</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F277"/>
+  <dimension ref="A1:F278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6293,6 +6293,26 @@
       </c>
       <c r="F277" s="7" t="inlineStr"/>
     </row>
+    <row r="278">
+      <c r="A278" s="4" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="B278" s="5" t="n">
+        <v>79.43000000000001</v>
+      </c>
+      <c r="C278" s="5" t="n">
+        <v>85.61</v>
+      </c>
+      <c r="D278" s="5" t="n">
+        <v>79.43000000000001</v>
+      </c>
+      <c r="E278" s="5" t="n">
+        <v>85.61</v>
+      </c>
+      <c r="F278" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6304,7 +6324,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E277"/>
+  <dimension ref="A1:E278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11585,8 +11605,27 @@
         <v>66.68000000000001</v>
       </c>
     </row>
+    <row r="278">
+      <c r="A278" s="4" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="B278" s="5" t="n">
+        <v>79.43000000000001</v>
+      </c>
+      <c r="C278" s="5" t="n">
+        <v>85.61</v>
+      </c>
+      <c r="D278" s="5" t="n">
+        <v>79.43000000000001</v>
+      </c>
+      <c r="E278" s="5" t="n">
+        <v>85.61</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B277">
+  <conditionalFormatting sqref="B2:B278">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -11598,7 +11637,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C277">
+  <conditionalFormatting sqref="C2:C278">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -11610,7 +11649,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D277">
+  <conditionalFormatting sqref="D2:D278">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -11622,7 +11661,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E277">
+  <conditionalFormatting sqref="E2:E278">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>

--- a/outputs/NSW_historical_prices.xlsx
+++ b/outputs/NSW_historical_prices.xlsx
@@ -528,16 +528,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>74.84</v>
+        <v>73.3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>75.72</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>75.54000000000001</v>
+        <v>74.09</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>76.44</v>
+        <v>74.13</v>
       </c>
     </row>
     <row r="6">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>100.26</v>
+        <v>96.44</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>121.45</v>
+        <v>114.4</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>103.35</v>
+        <v>99.66</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>125.44</v>
+        <v>118.46</v>
       </c>
     </row>
     <row r="7">
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>101.9</v>
+        <v>101.61</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>124.04</v>
+        <v>123.47</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>106.29</v>
+        <v>106.36</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>129.53</v>
+        <v>129.43</v>
       </c>
     </row>
     <row r="8">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>115.81</v>
+        <v>116.19</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>134.25</v>
+        <v>134.55</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>126.61</v>
+        <v>127.5</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>146.48</v>
+        <v>147.39</v>
       </c>
     </row>
     <row r="9">
@@ -604,22 +604,22 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>97.31999999999999</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>114.62</v>
+        <v>114.84</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>114.02</v>
+        <v>114.84</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>134.31</v>
+        <v>135.15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Data through: Jul 2026</t>
+          <t>Data through: Aug 2026</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F278"/>
+  <dimension ref="A1:F279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -690,10 +690,10 @@
         <v>75.81999999999999</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>86.92</v>
+        <v>87.44</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>140.91</v>
+        <v>141.75</v>
       </c>
       <c r="F2" s="7" t="inlineStr"/>
     </row>
@@ -710,10 +710,10 @@
         <v>22.06</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>36.38</v>
+        <v>36.59</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>40.92</v>
+        <v>41.17</v>
       </c>
       <c r="F3" s="7" t="inlineStr"/>
     </row>
@@ -730,10 +730,10 @@
         <v>26.29</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>38.97</v>
+        <v>39.21</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>48.67</v>
+        <v>48.97</v>
       </c>
       <c r="F4" s="7" t="inlineStr"/>
     </row>
@@ -750,10 +750,10 @@
         <v>19.41</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>32.34</v>
+        <v>32.54</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>35.87</v>
+        <v>36.09</v>
       </c>
       <c r="F5" s="7" t="inlineStr"/>
     </row>
@@ -770,10 +770,10 @@
         <v>20.74</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>33.89</v>
+        <v>34.1</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>38.26</v>
+        <v>38.49</v>
       </c>
       <c r="F6" s="7" t="inlineStr"/>
     </row>
@@ -790,10 +790,10 @@
         <v>29.68</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>43.06</v>
+        <v>43.32</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>54.66</v>
+        <v>54.99</v>
       </c>
       <c r="F7" s="7" t="inlineStr"/>
     </row>
@@ -810,10 +810,10 @@
         <v>31.61</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>49.14</v>
+        <v>49.43</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>58.05</v>
+        <v>58.39</v>
       </c>
       <c r="F8" s="7" t="inlineStr"/>
     </row>
@@ -830,10 +830,10 @@
         <v>49.01</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>107.11</v>
+        <v>107.75</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>89.73</v>
+        <v>90.27</v>
       </c>
       <c r="F9" s="7" t="inlineStr"/>
     </row>
@@ -850,10 +850,10 @@
         <v>116.77</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>116.34</v>
+        <v>117.04</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>213.17</v>
+        <v>214.45</v>
       </c>
       <c r="F10" s="7" t="inlineStr"/>
     </row>
@@ -870,10 +870,10 @@
         <v>37.43</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>55.17</v>
+        <v>55.5</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>68.22</v>
+        <v>68.63</v>
       </c>
       <c r="F11" s="7" t="inlineStr"/>
     </row>
@@ -890,10 +890,10 @@
         <v>37.85</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>58.45</v>
+        <v>58.8</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>68.88</v>
+        <v>69.29000000000001</v>
       </c>
       <c r="F12" s="7" t="inlineStr"/>
     </row>
@@ -910,10 +910,10 @@
         <v>33.72</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>56.66</v>
+        <v>57</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>61.27</v>
+        <v>61.64</v>
       </c>
       <c r="F13" s="7" t="inlineStr"/>
     </row>
@@ -930,10 +930,10 @@
         <v>43.57</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>64.65000000000001</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>79.06</v>
+        <v>79.53</v>
       </c>
       <c r="F14" s="7" t="inlineStr"/>
     </row>
@@ -950,10 +950,10 @@
         <v>26.2</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>42.78</v>
+        <v>43.04</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>47.48</v>
+        <v>47.76</v>
       </c>
       <c r="F15" s="7" t="inlineStr"/>
     </row>
@@ -970,10 +970,10 @@
         <v>32.32</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>50.99</v>
+        <v>51.3</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>58.49</v>
+        <v>58.84</v>
       </c>
       <c r="F16" s="7" t="inlineStr"/>
     </row>
@@ -990,10 +990,10 @@
         <v>125.43</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>125.63</v>
+        <v>126.38</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>226.4</v>
+        <v>227.76</v>
       </c>
       <c r="F17" s="7" t="inlineStr"/>
     </row>
@@ -1010,10 +1010,10 @@
         <v>131.39</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>139.89</v>
+        <v>140.73</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>236.56</v>
+        <v>237.98</v>
       </c>
       <c r="F18" s="7" t="inlineStr"/>
     </row>
@@ -1030,10 +1030,10 @@
         <v>110.88</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>116.53</v>
+        <v>117.23</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>199.13</v>
+        <v>200.32</v>
       </c>
       <c r="F19" s="7" t="inlineStr"/>
     </row>
@@ -1050,10 +1050,10 @@
         <v>65.59999999999999</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>71.5</v>
+        <v>71.92</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>117.55</v>
+        <v>118.25</v>
       </c>
       <c r="F20" s="7" t="inlineStr"/>
     </row>
@@ -1070,10 +1070,10 @@
         <v>50.64</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>58.75</v>
+        <v>59.1</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>90.54000000000001</v>
+        <v>91.08</v>
       </c>
       <c r="F21" s="7" t="inlineStr"/>
     </row>
@@ -1090,10 +1090,10 @@
         <v>19.92</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>32.91</v>
+        <v>33.11</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>35.54</v>
+        <v>35.75</v>
       </c>
       <c r="F22" s="7" t="inlineStr"/>
     </row>
@@ -1110,10 +1110,10 @@
         <v>36.49</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>53.23</v>
+        <v>53.55</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>64.97</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="F23" s="7" t="inlineStr"/>
     </row>
@@ -1130,10 +1130,10 @@
         <v>27.74</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>43.35</v>
+        <v>43.61</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>49.29</v>
+        <v>49.58</v>
       </c>
       <c r="F24" s="7" t="inlineStr"/>
     </row>
@@ -1150,10 +1150,10 @@
         <v>32.42</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>46.73</v>
+        <v>47.01</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>57.49</v>
+        <v>57.84</v>
       </c>
       <c r="F25" s="7" t="inlineStr"/>
     </row>
@@ -1170,10 +1170,10 @@
         <v>27.73</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>42.95</v>
+        <v>43.21</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>49.01</v>
+        <v>49.31</v>
       </c>
       <c r="F26" s="7" t="inlineStr"/>
     </row>
@@ -1190,10 +1190,10 @@
         <v>36.96</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>50.15</v>
+        <v>50.45</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>65.11</v>
+        <v>65.5</v>
       </c>
       <c r="F27" s="7" t="inlineStr"/>
     </row>
@@ -1210,10 +1210,10 @@
         <v>36.19</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>50.27</v>
+        <v>50.57</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>63.54</v>
+        <v>63.93</v>
       </c>
       <c r="F28" s="7" t="inlineStr"/>
     </row>
@@ -1230,10 +1230,10 @@
         <v>86.17</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>83.06999999999999</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>151.04</v>
+        <v>151.95</v>
       </c>
       <c r="F29" s="7" t="inlineStr"/>
     </row>
@@ -1250,10 +1250,10 @@
         <v>104.05</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>100.6</v>
+        <v>101.2</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>182.07</v>
+        <v>183.16</v>
       </c>
       <c r="F30" s="7" t="inlineStr"/>
     </row>
@@ -1270,10 +1270,10 @@
         <v>127.53</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>124.99</v>
+        <v>125.73</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>222.77</v>
+        <v>224.11</v>
       </c>
       <c r="F31" s="7" t="inlineStr"/>
     </row>
@@ -1290,10 +1290,10 @@
         <v>33.82</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>46.75</v>
+        <v>47.03</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>58.91</v>
+        <v>59.26</v>
       </c>
       <c r="F32" s="7" t="inlineStr"/>
     </row>
@@ -1310,10 +1310,10 @@
         <v>122.66</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>111.94</v>
+        <v>112.61</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>213.05</v>
+        <v>214.32</v>
       </c>
       <c r="F33" s="7" t="inlineStr"/>
     </row>
@@ -1330,10 +1330,10 @@
         <v>27.46</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>39.11</v>
+        <v>39.34</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>47.56</v>
+        <v>47.84</v>
       </c>
       <c r="F34" s="7" t="inlineStr"/>
     </row>
@@ -1350,10 +1350,10 @@
         <v>23.63</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>35.51</v>
+        <v>35.72</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>40.71</v>
+        <v>40.96</v>
       </c>
       <c r="F35" s="7" t="inlineStr"/>
     </row>
@@ -1370,10 +1370,10 @@
         <v>32.23</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>43.62</v>
+        <v>43.88</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>55.24</v>
+        <v>55.57</v>
       </c>
       <c r="F36" s="7" t="inlineStr"/>
     </row>
@@ -1390,10 +1390,10 @@
         <v>38.39</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>53.65</v>
+        <v>53.98</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>65.45</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="F37" s="7" t="inlineStr"/>
     </row>
@@ -1410,10 +1410,10 @@
         <v>73.48999999999999</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>81.09999999999999</v>
+        <v>81.59</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>124.93</v>
+        <v>125.68</v>
       </c>
       <c r="F38" s="7" t="inlineStr"/>
     </row>
@@ -1430,10 +1430,10 @@
         <v>35.43</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>50.49</v>
+        <v>50.79</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>60.05</v>
+        <v>60.41</v>
       </c>
       <c r="F39" s="7" t="inlineStr"/>
     </row>
@@ -1450,10 +1450,10 @@
         <v>34.69</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>47.74</v>
+        <v>48.03</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>58.62</v>
+        <v>58.98</v>
       </c>
       <c r="F40" s="7" t="inlineStr"/>
     </row>
@@ -1470,10 +1470,10 @@
         <v>30.95</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>42.82</v>
+        <v>43.08</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>52.32</v>
+        <v>52.64</v>
       </c>
       <c r="F41" s="7" t="inlineStr"/>
     </row>
@@ -1490,10 +1490,10 @@
         <v>41.15</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>53.22</v>
+        <v>53.54</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>69.59</v>
+        <v>70.01000000000001</v>
       </c>
       <c r="F42" s="7" t="inlineStr"/>
     </row>
@@ -1510,10 +1510,10 @@
         <v>25.26</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>35.53</v>
+        <v>35.74</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>42.74</v>
+        <v>42.99</v>
       </c>
       <c r="F43" s="7" t="inlineStr"/>
     </row>
@@ -1530,10 +1530,10 @@
         <v>89.47</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>94.56999999999999</v>
+        <v>95.14</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>151.33</v>
+        <v>152.24</v>
       </c>
       <c r="F44" s="7" t="inlineStr"/>
     </row>
@@ -1550,10 +1550,10 @@
         <v>62.98</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>75.69</v>
+        <v>76.14</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>106.5</v>
+        <v>107.14</v>
       </c>
       <c r="F45" s="7" t="inlineStr"/>
     </row>
@@ -1570,10 +1570,10 @@
         <v>63.16</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>86.69</v>
+        <v>87.20999999999999</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>106.77</v>
+        <v>107.41</v>
       </c>
       <c r="F46" s="7" t="inlineStr"/>
     </row>
@@ -1590,10 +1590,10 @@
         <v>102.26</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>131.67</v>
+        <v>132.46</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>172.16</v>
+        <v>173.2</v>
       </c>
       <c r="F47" s="7" t="inlineStr"/>
     </row>
@@ -1610,10 +1610,10 @@
         <v>75.83</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>106.1</v>
+        <v>106.74</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>127.15</v>
+        <v>127.91</v>
       </c>
       <c r="F48" s="7" t="inlineStr"/>
     </row>
@@ -1630,10 +1630,10 @@
         <v>397.05</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>385.19</v>
+        <v>387.5</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>663.05</v>
+        <v>667.03</v>
       </c>
       <c r="F49" s="7" t="inlineStr"/>
     </row>
@@ -1650,10 +1650,10 @@
         <v>105.7</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>129.74</v>
+        <v>130.52</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>176.11</v>
+        <v>177.17</v>
       </c>
       <c r="F50" s="7" t="inlineStr"/>
     </row>
@@ -1670,10 +1670,10 @@
         <v>47.17</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>66.39</v>
+        <v>66.79000000000001</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>78.41</v>
+        <v>78.88</v>
       </c>
       <c r="F51" s="7" t="inlineStr"/>
     </row>
@@ -1690,10 +1690,10 @@
         <v>60.36</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>79.53</v>
+        <v>80</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>100.11</v>
+        <v>100.71</v>
       </c>
       <c r="F52" s="7" t="inlineStr"/>
     </row>
@@ -1710,10 +1710,10 @@
         <v>55.78</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>67.33</v>
+        <v>67.73</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>92.23</v>
+        <v>92.78</v>
       </c>
       <c r="F53" s="7" t="inlineStr"/>
     </row>
@@ -1730,10 +1730,10 @@
         <v>48.17</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>59.36</v>
+        <v>59.71</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>79.40000000000001</v>
+        <v>79.87</v>
       </c>
       <c r="F54" s="7" t="inlineStr"/>
     </row>
@@ -1750,10 +1750,10 @@
         <v>55.55</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>65.98999999999999</v>
+        <v>66.39</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>91.28</v>
+        <v>91.83</v>
       </c>
       <c r="F55" s="7" t="inlineStr"/>
     </row>
@@ -1770,10 +1770,10 @@
         <v>43.73</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>55.75</v>
+        <v>56.09</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>71.54000000000001</v>
+        <v>71.97</v>
       </c>
       <c r="F56" s="7" t="inlineStr"/>
     </row>
@@ -1790,10 +1790,10 @@
         <v>32.22</v>
       </c>
       <c r="D57" s="5" t="n">
-        <v>44.28</v>
+        <v>44.55</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>52.48</v>
+        <v>52.79</v>
       </c>
       <c r="F57" s="7" t="inlineStr"/>
     </row>
@@ -1810,10 +1810,10 @@
         <v>47.31</v>
       </c>
       <c r="D58" s="5" t="n">
-        <v>56.05</v>
+        <v>56.39</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>76.70999999999999</v>
+        <v>77.17</v>
       </c>
       <c r="F58" s="7" t="inlineStr"/>
     </row>
@@ -1830,10 +1830,10 @@
         <v>40.08</v>
       </c>
       <c r="D59" s="5" t="n">
-        <v>53.66</v>
+        <v>53.98</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>64.68000000000001</v>
+        <v>65.06</v>
       </c>
       <c r="F59" s="7" t="inlineStr"/>
     </row>
@@ -1850,10 +1850,10 @@
         <v>53.21</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>72.59</v>
+        <v>73.02</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>85.45</v>
+        <v>85.97</v>
       </c>
       <c r="F60" s="7" t="inlineStr"/>
     </row>
@@ -1870,10 +1870,10 @@
         <v>51.05</v>
       </c>
       <c r="D61" s="5" t="n">
-        <v>66.84</v>
+        <v>67.23999999999999</v>
       </c>
       <c r="E61" s="5" t="n">
-        <v>81.59</v>
+        <v>82.08</v>
       </c>
       <c r="F61" s="7" t="inlineStr"/>
     </row>
@@ -1890,10 +1890,10 @@
         <v>55.38</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>64.43000000000001</v>
+        <v>64.81999999999999</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>88.17</v>
+        <v>88.7</v>
       </c>
       <c r="F62" s="7" t="inlineStr"/>
     </row>
@@ -1910,10 +1910,10 @@
         <v>48.73</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>63.31</v>
+        <v>63.69</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>77.29000000000001</v>
+        <v>77.75</v>
       </c>
       <c r="F63" s="7" t="inlineStr"/>
     </row>
@@ -1930,10 +1930,10 @@
         <v>45.62</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>56.17</v>
+        <v>56.5</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>72.08</v>
+        <v>72.51000000000001</v>
       </c>
       <c r="F64" s="7" t="inlineStr"/>
     </row>
@@ -1950,10 +1950,10 @@
         <v>143.1</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>129.03</v>
+        <v>129.8</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>226.33</v>
+        <v>227.69</v>
       </c>
       <c r="F65" s="7" t="inlineStr"/>
     </row>
@@ -1970,10 +1970,10 @@
         <v>38.45</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>48.85</v>
+        <v>49.14</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>60.88</v>
+        <v>61.25</v>
       </c>
       <c r="F66" s="7" t="inlineStr"/>
     </row>
@@ -1990,10 +1990,10 @@
         <v>27.84</v>
       </c>
       <c r="D67" s="5" t="n">
-        <v>37.9</v>
+        <v>38.13</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>44.13</v>
+        <v>44.39</v>
       </c>
       <c r="F67" s="7" t="inlineStr"/>
     </row>
@@ -2010,10 +2010,10 @@
         <v>72.97</v>
       </c>
       <c r="D68" s="5" t="n">
-        <v>74.63</v>
+        <v>75.08</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>115.62</v>
+        <v>116.32</v>
       </c>
       <c r="F68" s="7" t="inlineStr"/>
     </row>
@@ -2030,10 +2030,10 @@
         <v>39.35</v>
       </c>
       <c r="D69" s="5" t="n">
-        <v>65.62</v>
+        <v>66.02</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>62.33</v>
+        <v>62.7</v>
       </c>
       <c r="F69" s="7" t="inlineStr"/>
     </row>
@@ -2050,10 +2050,10 @@
         <v>29.61</v>
       </c>
       <c r="D70" s="5" t="n">
-        <v>39.03</v>
+        <v>39.26</v>
       </c>
       <c r="E70" s="5" t="n">
-        <v>46.88</v>
+        <v>47.16</v>
       </c>
       <c r="F70" s="7" t="inlineStr"/>
     </row>
@@ -2070,10 +2070,10 @@
         <v>47.45</v>
       </c>
       <c r="D71" s="5" t="n">
-        <v>56.92</v>
+        <v>57.26</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>75.01000000000001</v>
+        <v>75.45999999999999</v>
       </c>
       <c r="F71" s="7" t="inlineStr"/>
     </row>
@@ -2090,10 +2090,10 @@
         <v>35.75</v>
       </c>
       <c r="D72" s="5" t="n">
-        <v>47.79</v>
+        <v>48.07</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>56.42</v>
+        <v>56.76</v>
       </c>
       <c r="F72" s="7" t="inlineStr"/>
     </row>
@@ -2110,10 +2110,10 @@
         <v>45.82</v>
       </c>
       <c r="D73" s="5" t="n">
-        <v>53.8</v>
+        <v>54.13</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>72.19</v>
+        <v>72.62</v>
       </c>
       <c r="F73" s="7" t="inlineStr"/>
     </row>
@@ -2130,10 +2130,10 @@
         <v>40.23</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>49.43</v>
+        <v>49.72</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>63.18</v>
+        <v>63.56</v>
       </c>
       <c r="F74" s="7" t="inlineStr"/>
     </row>
@@ -2150,10 +2150,10 @@
         <v>27.9</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>38.05</v>
+        <v>38.27</v>
       </c>
       <c r="E75" s="5" t="n">
-        <v>43.68</v>
+        <v>43.94</v>
       </c>
       <c r="F75" s="7" t="inlineStr"/>
     </row>
@@ -2170,10 +2170,10 @@
         <v>28.56</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>39.99</v>
+        <v>40.23</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>44.58</v>
+        <v>44.84</v>
       </c>
       <c r="F76" s="7" t="inlineStr"/>
     </row>
@@ -2190,10 +2190,10 @@
         <v>32.65</v>
       </c>
       <c r="D77" s="5" t="n">
-        <v>42.91</v>
+        <v>43.16</v>
       </c>
       <c r="E77" s="5" t="n">
-        <v>50.87</v>
+        <v>51.17</v>
       </c>
       <c r="F77" s="7" t="inlineStr"/>
     </row>
@@ -2210,10 +2210,10 @@
         <v>209.33</v>
       </c>
       <c r="D78" s="5" t="n">
-        <v>167.59</v>
+        <v>168.59</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>325.55</v>
+        <v>327.5</v>
       </c>
       <c r="F78" s="7" t="inlineStr"/>
     </row>
@@ -2230,10 +2230,10 @@
         <v>186.31</v>
       </c>
       <c r="D79" s="5" t="n">
-        <v>151.18</v>
+        <v>152.08</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>289.23</v>
+        <v>290.97</v>
       </c>
       <c r="F79" s="7" t="inlineStr"/>
     </row>
@@ -2250,10 +2250,10 @@
         <v>78.56</v>
       </c>
       <c r="D80" s="5" t="n">
-        <v>78.03</v>
+        <v>78.5</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>121.58</v>
+        <v>122.31</v>
       </c>
       <c r="F80" s="7" t="inlineStr"/>
     </row>
@@ -2270,10 +2270,10 @@
         <v>96.8</v>
       </c>
       <c r="D81" s="5" t="n">
-        <v>86</v>
+        <v>86.51000000000001</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>149.35</v>
+        <v>150.24</v>
       </c>
       <c r="F81" s="7" t="inlineStr"/>
     </row>
@@ -2290,10 +2290,10 @@
         <v>30.88</v>
       </c>
       <c r="D82" s="5" t="n">
-        <v>39.78</v>
+        <v>40.01</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>47.5</v>
+        <v>47.78</v>
       </c>
       <c r="F82" s="7" t="inlineStr"/>
     </row>
@@ -2310,10 +2310,10 @@
         <v>28.33</v>
       </c>
       <c r="D83" s="5" t="n">
-        <v>37.99</v>
+        <v>38.22</v>
       </c>
       <c r="E83" s="5" t="n">
-        <v>43.49</v>
+        <v>43.75</v>
       </c>
       <c r="F83" s="7" t="inlineStr"/>
     </row>
@@ -2330,10 +2330,10 @@
         <v>31.21</v>
       </c>
       <c r="D84" s="5" t="n">
-        <v>42.54</v>
+        <v>42.8</v>
       </c>
       <c r="E84" s="5" t="n">
-        <v>47.81</v>
+        <v>48.1</v>
       </c>
       <c r="F84" s="7" t="inlineStr"/>
     </row>
@@ -2350,10 +2350,10 @@
         <v>38.94</v>
       </c>
       <c r="D85" s="5" t="n">
-        <v>50.9</v>
+        <v>51.2</v>
       </c>
       <c r="E85" s="5" t="n">
-        <v>59.53</v>
+        <v>59.89</v>
       </c>
       <c r="F85" s="7" t="inlineStr"/>
     </row>
@@ -2370,10 +2370,10 @@
         <v>29.46</v>
       </c>
       <c r="D86" s="5" t="n">
-        <v>41.78</v>
+        <v>42.03</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>44.93</v>
+        <v>45.2</v>
       </c>
       <c r="F86" s="7" t="inlineStr"/>
     </row>
@@ -2390,10 +2390,10 @@
         <v>46.72</v>
       </c>
       <c r="D87" s="5" t="n">
-        <v>53.19</v>
+        <v>53.51</v>
       </c>
       <c r="E87" s="5" t="n">
-        <v>71.09</v>
+        <v>71.51000000000001</v>
       </c>
       <c r="F87" s="7" t="inlineStr"/>
     </row>
@@ -2410,10 +2410,10 @@
         <v>25.76</v>
       </c>
       <c r="D88" s="5" t="n">
-        <v>36.69</v>
+        <v>36.91</v>
       </c>
       <c r="E88" s="5" t="n">
-        <v>39.1</v>
+        <v>39.34</v>
       </c>
       <c r="F88" s="7" t="inlineStr"/>
     </row>
@@ -2430,10 +2430,10 @@
         <v>24.27</v>
       </c>
       <c r="D89" s="5" t="n">
-        <v>34.34</v>
+        <v>34.54</v>
       </c>
       <c r="E89" s="5" t="n">
-        <v>36.79</v>
+        <v>37.01</v>
       </c>
       <c r="F89" s="7" t="inlineStr"/>
     </row>
@@ -2450,10 +2450,10 @@
         <v>24.35</v>
       </c>
       <c r="D90" s="5" t="n">
-        <v>34.94</v>
+        <v>35.15</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>36.87</v>
+        <v>37.09</v>
       </c>
       <c r="F90" s="7" t="inlineStr"/>
     </row>
@@ -2470,10 +2470,10 @@
         <v>24.87</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>33.98</v>
+        <v>34.18</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>37.6</v>
+        <v>37.83</v>
       </c>
       <c r="F91" s="7" t="inlineStr"/>
     </row>
@@ -2490,10 +2490,10 @@
         <v>78.09</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>72.75</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>117.47</v>
+        <v>118.17</v>
       </c>
       <c r="F92" s="7" t="inlineStr"/>
     </row>
@@ -2510,10 +2510,10 @@
         <v>259.43</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>204.69</v>
+        <v>205.92</v>
       </c>
       <c r="E93" s="5" t="n">
-        <v>388.27</v>
+        <v>390.6</v>
       </c>
       <c r="F93" s="7" t="inlineStr"/>
     </row>
@@ -2530,10 +2530,10 @@
         <v>29.29</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>39.22</v>
+        <v>39.46</v>
       </c>
       <c r="E94" s="5" t="n">
-        <v>43.61</v>
+        <v>43.87</v>
       </c>
       <c r="F94" s="7" t="inlineStr"/>
     </row>
@@ -2550,10 +2550,10 @@
         <v>27.22</v>
       </c>
       <c r="D95" s="5" t="n">
-        <v>39.23</v>
+        <v>39.47</v>
       </c>
       <c r="E95" s="5" t="n">
-        <v>40.41</v>
+        <v>40.65</v>
       </c>
       <c r="F95" s="7" t="inlineStr"/>
     </row>
@@ -2570,10 +2570,10 @@
         <v>30.41</v>
       </c>
       <c r="D96" s="5" t="n">
-        <v>43.08</v>
+        <v>43.34</v>
       </c>
       <c r="E96" s="5" t="n">
-        <v>45</v>
+        <v>45.27</v>
       </c>
       <c r="F96" s="7" t="inlineStr"/>
     </row>
@@ -2590,10 +2590,10 @@
         <v>29.83</v>
       </c>
       <c r="D97" s="5" t="n">
-        <v>40.43</v>
+        <v>40.67</v>
       </c>
       <c r="E97" s="5" t="n">
-        <v>44.01</v>
+        <v>44.28</v>
       </c>
       <c r="F97" s="7" t="inlineStr"/>
     </row>
@@ -2610,10 +2610,10 @@
         <v>35.14</v>
       </c>
       <c r="D98" s="5" t="n">
-        <v>45.1</v>
+        <v>45.37</v>
       </c>
       <c r="E98" s="5" t="n">
-        <v>51.74</v>
+        <v>52.05</v>
       </c>
       <c r="F98" s="7" t="inlineStr"/>
     </row>
@@ -2630,10 +2630,10 @@
         <v>33.09</v>
       </c>
       <c r="D99" s="5" t="n">
-        <v>44.31</v>
+        <v>44.57</v>
       </c>
       <c r="E99" s="5" t="n">
-        <v>48.63</v>
+        <v>48.92</v>
       </c>
       <c r="F99" s="7" t="inlineStr"/>
     </row>
@@ -2650,10 +2650,10 @@
         <v>31.1</v>
       </c>
       <c r="D100" s="5" t="n">
-        <v>41.89</v>
+        <v>42.14</v>
       </c>
       <c r="E100" s="5" t="n">
-        <v>45.61</v>
+        <v>45.89</v>
       </c>
       <c r="F100" s="7" t="inlineStr"/>
     </row>
@@ -2670,10 +2670,10 @@
         <v>30.68</v>
       </c>
       <c r="D101" s="5" t="n">
-        <v>41.83</v>
+        <v>42.08</v>
       </c>
       <c r="E101" s="5" t="n">
-        <v>45</v>
+        <v>45.27</v>
       </c>
       <c r="F101" s="7" t="inlineStr"/>
     </row>
@@ -2690,10 +2690,10 @@
         <v>47.76</v>
       </c>
       <c r="D102" s="5" t="n">
-        <v>54.44</v>
+        <v>54.77</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>70.05</v>
+        <v>70.47</v>
       </c>
       <c r="F102" s="7" t="inlineStr"/>
     </row>
@@ -2710,10 +2710,10 @@
         <v>27.5</v>
       </c>
       <c r="D103" s="5" t="n">
-        <v>37.81</v>
+        <v>38.04</v>
       </c>
       <c r="E103" s="5" t="n">
-        <v>40.33</v>
+        <v>40.58</v>
       </c>
       <c r="F103" s="7" t="inlineStr"/>
     </row>
@@ -2730,10 +2730,10 @@
         <v>28.43</v>
       </c>
       <c r="D104" s="5" t="n">
-        <v>36.76</v>
+        <v>36.98</v>
       </c>
       <c r="E104" s="5" t="n">
-        <v>41.69</v>
+        <v>41.94</v>
       </c>
       <c r="F104" s="7" t="inlineStr"/>
     </row>
@@ -2750,10 +2750,10 @@
         <v>29.48</v>
       </c>
       <c r="D105" s="5" t="n">
-        <v>39.42</v>
+        <v>39.66</v>
       </c>
       <c r="E105" s="5" t="n">
-        <v>43.22</v>
+        <v>43.48</v>
       </c>
       <c r="F105" s="7" t="inlineStr"/>
     </row>
@@ -2770,10 +2770,10 @@
         <v>28.13</v>
       </c>
       <c r="D106" s="5" t="n">
-        <v>37.32</v>
+        <v>37.54</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>41.23</v>
+        <v>41.48</v>
       </c>
       <c r="F106" s="7" t="inlineStr"/>
     </row>
@@ -2790,10 +2790,10 @@
         <v>36.78</v>
       </c>
       <c r="D107" s="5" t="n">
-        <v>49.05</v>
+        <v>49.34</v>
       </c>
       <c r="E107" s="5" t="n">
-        <v>53.82</v>
+        <v>54.14</v>
       </c>
       <c r="F107" s="7" t="inlineStr"/>
     </row>
@@ -2810,10 +2810,10 @@
         <v>30.61</v>
       </c>
       <c r="D108" s="5" t="n">
-        <v>41.94</v>
+        <v>42.19</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>44.71</v>
+        <v>44.98</v>
       </c>
       <c r="F108" s="7" t="inlineStr"/>
     </row>
@@ -2830,10 +2830,10 @@
         <v>40.68</v>
       </c>
       <c r="D109" s="5" t="n">
-        <v>52.51</v>
+        <v>52.83</v>
       </c>
       <c r="E109" s="5" t="n">
-        <v>59.32</v>
+        <v>59.68</v>
       </c>
       <c r="F109" s="7" t="inlineStr"/>
     </row>
@@ -2850,10 +2850,10 @@
         <v>74.02</v>
       </c>
       <c r="D110" s="9" t="n">
-        <v>96.14</v>
+        <v>96.72</v>
       </c>
       <c r="E110" s="9" t="n">
-        <v>107.45</v>
+        <v>108.1</v>
       </c>
       <c r="F110" s="10" t="inlineStr">
         <is>
@@ -2874,10 +2874,10 @@
         <v>59.12</v>
       </c>
       <c r="D111" s="9" t="n">
-        <v>82.95</v>
+        <v>83.45</v>
       </c>
       <c r="E111" s="9" t="n">
-        <v>85.44</v>
+        <v>85.95</v>
       </c>
       <c r="F111" s="10" t="inlineStr">
         <is>
@@ -2898,10 +2898,10 @@
         <v>54.32</v>
       </c>
       <c r="D112" s="9" t="n">
-        <v>75.89</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="E112" s="9" t="n">
-        <v>78.15000000000001</v>
+        <v>78.62</v>
       </c>
       <c r="F112" s="10" t="inlineStr">
         <is>
@@ -2922,10 +2922,10 @@
         <v>60.96</v>
       </c>
       <c r="D113" s="9" t="n">
-        <v>82.04000000000001</v>
+        <v>82.53</v>
       </c>
       <c r="E113" s="9" t="n">
-        <v>87.63</v>
+        <v>88.15000000000001</v>
       </c>
       <c r="F113" s="10" t="inlineStr">
         <is>
@@ -2946,10 +2946,10 @@
         <v>62.23</v>
       </c>
       <c r="D114" s="9" t="n">
-        <v>81.69</v>
+        <v>82.18000000000001</v>
       </c>
       <c r="E114" s="9" t="n">
-        <v>89.38</v>
+        <v>89.91</v>
       </c>
       <c r="F114" s="10" t="inlineStr">
         <is>
@@ -2970,10 +2970,10 @@
         <v>50.48</v>
       </c>
       <c r="D115" s="9" t="n">
-        <v>71.48</v>
+        <v>71.91</v>
       </c>
       <c r="E115" s="9" t="n">
-        <v>72.44</v>
+        <v>72.87</v>
       </c>
       <c r="F115" s="10" t="inlineStr">
         <is>
@@ -2994,10 +2994,10 @@
         <v>53.13</v>
       </c>
       <c r="D116" s="9" t="n">
-        <v>72.47</v>
+        <v>72.91</v>
       </c>
       <c r="E116" s="9" t="n">
-        <v>76.16</v>
+        <v>76.61</v>
       </c>
       <c r="F116" s="10" t="inlineStr">
         <is>
@@ -3018,10 +3018,10 @@
         <v>54.42</v>
       </c>
       <c r="D117" s="9" t="n">
-        <v>74.62</v>
+        <v>75.06999999999999</v>
       </c>
       <c r="E117" s="9" t="n">
-        <v>77.92</v>
+        <v>78.39</v>
       </c>
       <c r="F117" s="10" t="inlineStr">
         <is>
@@ -3042,10 +3042,10 @@
         <v>54.87</v>
       </c>
       <c r="D118" s="9" t="n">
-        <v>75.09999999999999</v>
+        <v>75.55</v>
       </c>
       <c r="E118" s="9" t="n">
-        <v>78.47</v>
+        <v>78.94</v>
       </c>
       <c r="F118" s="10" t="inlineStr">
         <is>
@@ -3066,10 +3066,10 @@
         <v>57.39</v>
       </c>
       <c r="D119" s="9" t="n">
-        <v>77.17</v>
+        <v>77.64</v>
       </c>
       <c r="E119" s="9" t="n">
-        <v>81.97</v>
+        <v>82.47</v>
       </c>
       <c r="F119" s="10" t="inlineStr">
         <is>
@@ -3090,10 +3090,10 @@
         <v>59.18</v>
       </c>
       <c r="D120" s="9" t="n">
-        <v>78.56</v>
+        <v>79.03</v>
       </c>
       <c r="E120" s="9" t="n">
-        <v>84.42</v>
+        <v>84.93000000000001</v>
       </c>
       <c r="F120" s="10" t="inlineStr">
         <is>
@@ -3114,10 +3114,10 @@
         <v>59.67</v>
       </c>
       <c r="D121" s="9" t="n">
-        <v>80.5</v>
+        <v>80.98</v>
       </c>
       <c r="E121" s="9" t="n">
-        <v>85.02</v>
+        <v>85.53</v>
       </c>
       <c r="F121" s="10" t="inlineStr">
         <is>
@@ -3138,10 +3138,10 @@
         <v>60.88</v>
       </c>
       <c r="D122" s="9" t="n">
-        <v>82.03</v>
+        <v>82.52</v>
       </c>
       <c r="E122" s="9" t="n">
-        <v>86.39</v>
+        <v>86.91</v>
       </c>
       <c r="F122" s="10" t="inlineStr">
         <is>
@@ -3162,10 +3162,10 @@
         <v>56.37</v>
       </c>
       <c r="D123" s="9" t="n">
-        <v>76.7</v>
+        <v>77.16</v>
       </c>
       <c r="E123" s="9" t="n">
-        <v>79.67</v>
+        <v>80.14</v>
       </c>
       <c r="F123" s="10" t="inlineStr">
         <is>
@@ -3186,10 +3186,10 @@
         <v>54.35</v>
       </c>
       <c r="D124" s="9" t="n">
-        <v>74.2</v>
+        <v>74.64</v>
       </c>
       <c r="E124" s="9" t="n">
-        <v>76.5</v>
+        <v>76.95999999999999</v>
       </c>
       <c r="F124" s="10" t="inlineStr">
         <is>
@@ -3210,10 +3210,10 @@
         <v>52.4</v>
       </c>
       <c r="D125" s="9" t="n">
-        <v>72.31999999999999</v>
+        <v>72.75</v>
       </c>
       <c r="E125" s="9" t="n">
-        <v>73.58</v>
+        <v>74.02</v>
       </c>
       <c r="F125" s="10" t="inlineStr">
         <is>
@@ -3234,10 +3234,10 @@
         <v>51.68</v>
       </c>
       <c r="D126" s="9" t="n">
-        <v>70.73</v>
+        <v>71.16</v>
       </c>
       <c r="E126" s="9" t="n">
-        <v>72.40000000000001</v>
+        <v>72.83</v>
       </c>
       <c r="F126" s="10" t="inlineStr">
         <is>
@@ -3258,10 +3258,10 @@
         <v>70.8</v>
       </c>
       <c r="D127" s="9" t="n">
-        <v>82.5</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="E127" s="9" t="n">
-        <v>98.95</v>
+        <v>99.54000000000001</v>
       </c>
       <c r="F127" s="10" t="inlineStr">
         <is>
@@ -3282,10 +3282,10 @@
         <v>56.72</v>
       </c>
       <c r="D128" s="9" t="n">
-        <v>72.68000000000001</v>
+        <v>73.12</v>
       </c>
       <c r="E128" s="9" t="n">
-        <v>79.11</v>
+        <v>79.59</v>
       </c>
       <c r="F128" s="10" t="inlineStr">
         <is>
@@ -3306,10 +3306,10 @@
         <v>52.88</v>
       </c>
       <c r="D129" s="9" t="n">
-        <v>70.05</v>
+        <v>70.47</v>
       </c>
       <c r="E129" s="9" t="n">
-        <v>73.61</v>
+        <v>74.05</v>
       </c>
       <c r="F129" s="10" t="inlineStr">
         <is>
@@ -3330,10 +3330,10 @@
         <v>51.65</v>
       </c>
       <c r="D130" s="9" t="n">
-        <v>67.63</v>
+        <v>68.04000000000001</v>
       </c>
       <c r="E130" s="9" t="n">
-        <v>71.76000000000001</v>
+        <v>72.19</v>
       </c>
       <c r="F130" s="10" t="inlineStr">
         <is>
@@ -3354,10 +3354,10 @@
         <v>50.39</v>
       </c>
       <c r="D131" s="9" t="n">
-        <v>67.44</v>
+        <v>67.84</v>
       </c>
       <c r="E131" s="9" t="n">
-        <v>69.89</v>
+        <v>70.31</v>
       </c>
       <c r="F131" s="10" t="inlineStr">
         <is>
@@ -3378,10 +3378,10 @@
         <v>56.06</v>
       </c>
       <c r="D132" s="9" t="n">
-        <v>71.12</v>
+        <v>71.54000000000001</v>
       </c>
       <c r="E132" s="9" t="n">
-        <v>77.63</v>
+        <v>78.09</v>
       </c>
       <c r="F132" s="10" t="inlineStr">
         <is>
@@ -3402,10 +3402,10 @@
         <v>51.67</v>
       </c>
       <c r="D133" s="9" t="n">
-        <v>68.76000000000001</v>
+        <v>69.17</v>
       </c>
       <c r="E133" s="9" t="n">
-        <v>71.43000000000001</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="F133" s="10" t="inlineStr">
         <is>
@@ -3426,10 +3426,10 @@
         <v>44.55</v>
       </c>
       <c r="D134" s="5" t="n">
-        <v>56.9</v>
+        <v>57.24</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>61.5</v>
+        <v>61.87</v>
       </c>
       <c r="F134" s="7" t="inlineStr"/>
     </row>
@@ -3446,10 +3446,10 @@
         <v>40.13</v>
       </c>
       <c r="D135" s="5" t="n">
-        <v>49.75</v>
+        <v>50.05</v>
       </c>
       <c r="E135" s="5" t="n">
-        <v>55.32</v>
+        <v>55.65</v>
       </c>
       <c r="F135" s="7" t="inlineStr"/>
     </row>
@@ -3466,10 +3466,10 @@
         <v>44.84</v>
       </c>
       <c r="D136" s="5" t="n">
-        <v>55.02</v>
+        <v>55.35</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>61.72</v>
+        <v>62.1</v>
       </c>
       <c r="F136" s="7" t="inlineStr"/>
     </row>
@@ -3486,10 +3486,10 @@
         <v>34.1</v>
       </c>
       <c r="D137" s="5" t="n">
-        <v>43.49</v>
+        <v>43.75</v>
       </c>
       <c r="E137" s="5" t="n">
-        <v>46.91</v>
+        <v>47.19</v>
       </c>
       <c r="F137" s="7" t="inlineStr"/>
     </row>
@@ -3506,10 +3506,10 @@
         <v>41.02</v>
       </c>
       <c r="D138" s="5" t="n">
-        <v>46.35</v>
+        <v>46.62</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>56.4</v>
+        <v>56.73</v>
       </c>
       <c r="F138" s="7" t="inlineStr"/>
     </row>
@@ -3526,10 +3526,10 @@
         <v>35.12</v>
       </c>
       <c r="D139" s="5" t="n">
-        <v>42.11</v>
+        <v>42.36</v>
       </c>
       <c r="E139" s="5" t="n">
-        <v>48.25</v>
+        <v>48.54</v>
       </c>
       <c r="F139" s="7" t="inlineStr"/>
     </row>
@@ -3546,10 +3546,10 @@
         <v>47.17</v>
       </c>
       <c r="D140" s="5" t="n">
-        <v>50.74</v>
+        <v>51.04</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>64.77</v>
+        <v>65.16</v>
       </c>
       <c r="F140" s="7" t="inlineStr"/>
     </row>
@@ -3566,10 +3566,10 @@
         <v>38.88</v>
       </c>
       <c r="D141" s="5" t="n">
-        <v>45.91</v>
+        <v>46.19</v>
       </c>
       <c r="E141" s="5" t="n">
-        <v>53.35</v>
+        <v>53.67</v>
       </c>
       <c r="F141" s="7" t="inlineStr"/>
     </row>
@@ -3586,10 +3586,10 @@
         <v>35.83</v>
       </c>
       <c r="D142" s="5" t="n">
-        <v>42.22</v>
+        <v>42.48</v>
       </c>
       <c r="E142" s="5" t="n">
-        <v>49.14</v>
+        <v>49.43</v>
       </c>
       <c r="F142" s="7" t="inlineStr"/>
     </row>
@@ -3606,10 +3606,10 @@
         <v>42.98</v>
       </c>
       <c r="D143" s="5" t="n">
-        <v>49.03</v>
+        <v>49.33</v>
       </c>
       <c r="E143" s="5" t="n">
-        <v>58.8</v>
+        <v>59.15</v>
       </c>
       <c r="F143" s="7" t="inlineStr"/>
     </row>
@@ -3626,10 +3626,10 @@
         <v>41.54</v>
       </c>
       <c r="D144" s="5" t="n">
-        <v>48.71</v>
+        <v>49</v>
       </c>
       <c r="E144" s="5" t="n">
-        <v>56.7</v>
+        <v>57.04</v>
       </c>
       <c r="F144" s="7" t="inlineStr"/>
     </row>
@@ -3646,10 +3646,10 @@
         <v>40.75</v>
       </c>
       <c r="D145" s="5" t="n">
-        <v>49.14</v>
+        <v>49.44</v>
       </c>
       <c r="E145" s="5" t="n">
-        <v>55.49</v>
+        <v>55.82</v>
       </c>
       <c r="F145" s="7" t="inlineStr"/>
     </row>
@@ -3666,10 +3666,10 @@
         <v>43.87</v>
       </c>
       <c r="D146" s="5" t="n">
-        <v>53.24</v>
+        <v>53.56</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>59.66</v>
+        <v>60.02</v>
       </c>
       <c r="F146" s="7" t="inlineStr"/>
     </row>
@@ -3686,10 +3686,10 @@
         <v>40.45</v>
       </c>
       <c r="D147" s="5" t="n">
-        <v>49.91</v>
+        <v>50.21</v>
       </c>
       <c r="E147" s="5" t="n">
-        <v>54.94</v>
+        <v>55.27</v>
       </c>
       <c r="F147" s="7" t="inlineStr"/>
     </row>
@@ -3706,10 +3706,10 @@
         <v>76.97</v>
       </c>
       <c r="D148" s="5" t="n">
-        <v>78.67</v>
+        <v>79.14</v>
       </c>
       <c r="E148" s="5" t="n">
-        <v>104.4</v>
+        <v>105.03</v>
       </c>
       <c r="F148" s="7" t="inlineStr"/>
     </row>
@@ -3726,10 +3726,10 @@
         <v>41.94</v>
       </c>
       <c r="D149" s="5" t="n">
-        <v>49.77</v>
+        <v>50.07</v>
       </c>
       <c r="E149" s="5" t="n">
-        <v>56.81</v>
+        <v>57.15</v>
       </c>
       <c r="F149" s="7" t="inlineStr"/>
     </row>
@@ -3746,10 +3746,10 @@
         <v>62.06</v>
       </c>
       <c r="D150" s="5" t="n">
-        <v>62.12</v>
+        <v>62.5</v>
       </c>
       <c r="E150" s="5" t="n">
-        <v>83.95999999999999</v>
+        <v>84.45999999999999</v>
       </c>
       <c r="F150" s="7" t="inlineStr"/>
     </row>
@@ -3766,10 +3766,10 @@
         <v>50.61</v>
       </c>
       <c r="D151" s="5" t="n">
-        <v>60.21</v>
+        <v>60.57</v>
       </c>
       <c r="E151" s="5" t="n">
-        <v>68.38</v>
+        <v>68.79000000000001</v>
       </c>
       <c r="F151" s="7" t="inlineStr"/>
     </row>
@@ -3786,10 +3786,10 @@
         <v>60.64</v>
       </c>
       <c r="D152" s="5" t="n">
-        <v>61.13</v>
+        <v>61.49</v>
       </c>
       <c r="E152" s="5" t="n">
-        <v>81.98999999999999</v>
+        <v>82.48</v>
       </c>
       <c r="F152" s="7" t="inlineStr"/>
     </row>
@@ -3806,10 +3806,10 @@
         <v>45.94</v>
       </c>
       <c r="D153" s="5" t="n">
-        <v>52.51</v>
+        <v>52.82</v>
       </c>
       <c r="E153" s="5" t="n">
-        <v>62.15</v>
+        <v>62.53</v>
       </c>
       <c r="F153" s="7" t="inlineStr"/>
     </row>
@@ -3826,10 +3826,10 @@
         <v>49.96</v>
       </c>
       <c r="D154" s="5" t="n">
-        <v>60.46</v>
+        <v>60.82</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>67.64</v>
+        <v>68.04000000000001</v>
       </c>
       <c r="F154" s="7" t="inlineStr"/>
     </row>
@@ -3846,10 +3846,10 @@
         <v>78</v>
       </c>
       <c r="D155" s="5" t="n">
-        <v>89.26000000000001</v>
+        <v>89.8</v>
       </c>
       <c r="E155" s="5" t="n">
-        <v>105.44</v>
+        <v>106.08</v>
       </c>
       <c r="F155" s="7" t="inlineStr"/>
     </row>
@@ -3866,10 +3866,10 @@
         <v>81.53</v>
       </c>
       <c r="D156" s="5" t="n">
-        <v>90.23999999999999</v>
+        <v>90.78</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>110.06</v>
+        <v>110.72</v>
       </c>
       <c r="F156" s="7" t="inlineStr"/>
     </row>
@@ -3886,10 +3886,10 @@
         <v>121.82</v>
       </c>
       <c r="D157" s="5" t="n">
-        <v>131.68</v>
+        <v>132.47</v>
       </c>
       <c r="E157" s="5" t="n">
-        <v>164.2</v>
+        <v>165.19</v>
       </c>
       <c r="F157" s="7" t="inlineStr"/>
     </row>
@@ -3906,10 +3906,10 @@
         <v>86.11</v>
       </c>
       <c r="D158" s="5" t="n">
-        <v>88.86</v>
+        <v>89.39</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>115.8</v>
+        <v>116.49</v>
       </c>
       <c r="F158" s="7" t="inlineStr"/>
     </row>
@@ -3926,10 +3926,10 @@
         <v>58.75</v>
       </c>
       <c r="D159" s="5" t="n">
-        <v>64.53</v>
+        <v>64.92</v>
       </c>
       <c r="E159" s="5" t="n">
-        <v>78.81999999999999</v>
+        <v>79.29000000000001</v>
       </c>
       <c r="F159" s="7" t="inlineStr"/>
     </row>
@@ -3946,10 +3946,10 @@
         <v>50.15</v>
       </c>
       <c r="D160" s="5" t="n">
-        <v>60.07</v>
+        <v>60.43</v>
       </c>
       <c r="E160" s="5" t="n">
-        <v>67.13</v>
+        <v>67.53</v>
       </c>
       <c r="F160" s="7" t="inlineStr"/>
     </row>
@@ -3966,10 +3966,10 @@
         <v>60.61</v>
       </c>
       <c r="D161" s="5" t="n">
-        <v>73.8</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="E161" s="5" t="n">
-        <v>80.98</v>
+        <v>81.47</v>
       </c>
       <c r="F161" s="7" t="inlineStr"/>
     </row>
@@ -3986,10 +3986,10 @@
         <v>114.97</v>
       </c>
       <c r="D162" s="5" t="n">
-        <v>110.88</v>
+        <v>111.55</v>
       </c>
       <c r="E162" s="5" t="n">
-        <v>153.35</v>
+        <v>154.27</v>
       </c>
       <c r="F162" s="7" t="inlineStr"/>
     </row>
@@ -4006,10 +4006,10 @@
         <v>59.62</v>
       </c>
       <c r="D163" s="5" t="n">
-        <v>68.61</v>
+        <v>69.02</v>
       </c>
       <c r="E163" s="5" t="n">
-        <v>79.38</v>
+        <v>79.86</v>
       </c>
       <c r="F163" s="7" t="inlineStr"/>
     </row>
@@ -4026,10 +4026,10 @@
         <v>106.24</v>
       </c>
       <c r="D164" s="5" t="n">
-        <v>109.93</v>
+        <v>110.59</v>
       </c>
       <c r="E164" s="5" t="n">
-        <v>141.24</v>
+        <v>142.09</v>
       </c>
       <c r="F164" s="7" t="inlineStr"/>
     </row>
@@ -4046,10 +4046,10 @@
         <v>279.63</v>
       </c>
       <c r="D165" s="5" t="n">
-        <v>237.07</v>
+        <v>238.49</v>
       </c>
       <c r="E165" s="5" t="n">
-        <v>371.19</v>
+        <v>373.42</v>
       </c>
       <c r="F165" s="7" t="inlineStr"/>
     </row>
@@ -4066,10 +4066,10 @@
         <v>110.22</v>
       </c>
       <c r="D166" s="5" t="n">
-        <v>122.88</v>
+        <v>123.62</v>
       </c>
       <c r="E166" s="5" t="n">
-        <v>146.09</v>
+        <v>146.96</v>
       </c>
       <c r="F166" s="7" t="inlineStr"/>
     </row>
@@ -4086,10 +4086,10 @@
         <v>115.63</v>
       </c>
       <c r="D167" s="5" t="n">
-        <v>141.01</v>
+        <v>141.86</v>
       </c>
       <c r="E167" s="5" t="n">
-        <v>153.16</v>
+        <v>154.08</v>
       </c>
       <c r="F167" s="7" t="inlineStr"/>
     </row>
@@ -4106,10 +4106,10 @@
         <v>96.5</v>
       </c>
       <c r="D168" s="5" t="n">
-        <v>118.7</v>
+        <v>119.41</v>
       </c>
       <c r="E168" s="5" t="n">
-        <v>127.74</v>
+        <v>128.5</v>
       </c>
       <c r="F168" s="7" t="inlineStr"/>
     </row>
@@ -4126,10 +4126,10 @@
         <v>90.03</v>
       </c>
       <c r="D169" s="5" t="n">
-        <v>112.26</v>
+        <v>112.93</v>
       </c>
       <c r="E169" s="5" t="n">
-        <v>119.1</v>
+        <v>119.81</v>
       </c>
       <c r="F169" s="7" t="inlineStr"/>
     </row>
@@ -4146,10 +4146,10 @@
         <v>102.1</v>
       </c>
       <c r="D170" s="5" t="n">
-        <v>120.31</v>
+        <v>121.03</v>
       </c>
       <c r="E170" s="5" t="n">
-        <v>134.79</v>
+        <v>135.6</v>
       </c>
       <c r="F170" s="7" t="inlineStr"/>
     </row>
@@ -4166,10 +4166,10 @@
         <v>112.14</v>
       </c>
       <c r="D171" s="5" t="n">
-        <v>134.58</v>
+        <v>135.39</v>
       </c>
       <c r="E171" s="5" t="n">
-        <v>147.74</v>
+        <v>148.63</v>
       </c>
       <c r="F171" s="7" t="inlineStr"/>
     </row>
@@ -4186,10 +4186,10 @@
         <v>91.84999999999999</v>
       </c>
       <c r="D172" s="5" t="n">
-        <v>114.7</v>
+        <v>115.39</v>
       </c>
       <c r="E172" s="5" t="n">
-        <v>120.76</v>
+        <v>121.49</v>
       </c>
       <c r="F172" s="7" t="inlineStr"/>
     </row>
@@ -4206,10 +4206,10 @@
         <v>90.03</v>
       </c>
       <c r="D173" s="5" t="n">
-        <v>107.81</v>
+        <v>108.46</v>
       </c>
       <c r="E173" s="5" t="n">
-        <v>118.11</v>
+        <v>118.82</v>
       </c>
       <c r="F173" s="7" t="inlineStr"/>
     </row>
@@ -4226,10 +4226,10 @@
         <v>87.13</v>
       </c>
       <c r="D174" s="5" t="n">
-        <v>103.12</v>
+        <v>103.74</v>
       </c>
       <c r="E174" s="5" t="n">
-        <v>114.05</v>
+        <v>114.73</v>
       </c>
       <c r="F174" s="7" t="inlineStr"/>
     </row>
@@ -4246,10 +4246,10 @@
         <v>87.25</v>
       </c>
       <c r="D175" s="5" t="n">
-        <v>99.98999999999999</v>
+        <v>100.59</v>
       </c>
       <c r="E175" s="5" t="n">
-        <v>113.95</v>
+        <v>114.63</v>
       </c>
       <c r="F175" s="7" t="inlineStr"/>
     </row>
@@ -4266,10 +4266,10 @@
         <v>83.73999999999999</v>
       </c>
       <c r="D176" s="5" t="n">
-        <v>99.14</v>
+        <v>99.73</v>
       </c>
       <c r="E176" s="5" t="n">
-        <v>109.21</v>
+        <v>109.86</v>
       </c>
       <c r="F176" s="7" t="inlineStr"/>
     </row>
@@ -4286,10 +4286,10 @@
         <v>80.61</v>
       </c>
       <c r="D177" s="5" t="n">
-        <v>94.79000000000001</v>
+        <v>95.36</v>
       </c>
       <c r="E177" s="5" t="n">
-        <v>104.97</v>
+        <v>105.6</v>
       </c>
       <c r="F177" s="7" t="inlineStr"/>
     </row>
@@ -4306,10 +4306,10 @@
         <v>69.84999999999999</v>
       </c>
       <c r="D178" s="5" t="n">
-        <v>86.75</v>
+        <v>87.27</v>
       </c>
       <c r="E178" s="5" t="n">
-        <v>90.83</v>
+        <v>91.37</v>
       </c>
       <c r="F178" s="7" t="inlineStr"/>
     </row>
@@ -4326,10 +4326,10 @@
         <v>85.54000000000001</v>
       </c>
       <c r="D179" s="5" t="n">
-        <v>97.58</v>
+        <v>98.16</v>
       </c>
       <c r="E179" s="5" t="n">
-        <v>111.1</v>
+        <v>111.77</v>
       </c>
       <c r="F179" s="7" t="inlineStr"/>
     </row>
@@ -4346,10 +4346,10 @@
         <v>88.81999999999999</v>
       </c>
       <c r="D180" s="5" t="n">
-        <v>100.24</v>
+        <v>100.84</v>
       </c>
       <c r="E180" s="5" t="n">
-        <v>115.22</v>
+        <v>115.91</v>
       </c>
       <c r="F180" s="7" t="inlineStr"/>
     </row>
@@ -4366,10 +4366,10 @@
         <v>130.79</v>
       </c>
       <c r="D181" s="5" t="n">
-        <v>130.53</v>
+        <v>131.31</v>
       </c>
       <c r="E181" s="5" t="n">
-        <v>169.47</v>
+        <v>170.48</v>
       </c>
       <c r="F181" s="7" t="inlineStr"/>
     </row>
@@ -4386,10 +4386,10 @@
         <v>84.93000000000001</v>
       </c>
       <c r="D182" s="5" t="n">
-        <v>97.02</v>
+        <v>97.61</v>
       </c>
       <c r="E182" s="5" t="n">
-        <v>109.89</v>
+        <v>110.54</v>
       </c>
       <c r="F182" s="7" t="inlineStr"/>
     </row>
@@ -4406,10 +4406,10 @@
         <v>108.46</v>
       </c>
       <c r="D183" s="5" t="n">
-        <v>120.18</v>
+        <v>120.9</v>
       </c>
       <c r="E183" s="5" t="n">
-        <v>140.13</v>
+        <v>140.97</v>
       </c>
       <c r="F183" s="7" t="inlineStr"/>
     </row>
@@ -4426,10 +4426,10 @@
         <v>107.82</v>
       </c>
       <c r="D184" s="5" t="n">
-        <v>120.45</v>
+        <v>121.17</v>
       </c>
       <c r="E184" s="5" t="n">
-        <v>139.1</v>
+        <v>139.93</v>
       </c>
       <c r="F184" s="7" t="inlineStr"/>
     </row>
@@ -4446,10 +4446,10 @@
         <v>101.79</v>
       </c>
       <c r="D185" s="5" t="n">
-        <v>113.66</v>
+        <v>114.34</v>
       </c>
       <c r="E185" s="5" t="n">
-        <v>131.09</v>
+        <v>131.88</v>
       </c>
       <c r="F185" s="7" t="inlineStr"/>
     </row>
@@ -4466,10 +4466,10 @@
         <v>99.8</v>
       </c>
       <c r="D186" s="5" t="n">
-        <v>110.62</v>
+        <v>111.28</v>
       </c>
       <c r="E186" s="5" t="n">
-        <v>128.31</v>
+        <v>129.08</v>
       </c>
       <c r="F186" s="7" t="inlineStr"/>
     </row>
@@ -4486,10 +4486,10 @@
         <v>97.98</v>
       </c>
       <c r="D187" s="5" t="n">
-        <v>107.22</v>
+        <v>107.86</v>
       </c>
       <c r="E187" s="5" t="n">
-        <v>125.75</v>
+        <v>126.51</v>
       </c>
       <c r="F187" s="7" t="inlineStr"/>
     </row>
@@ -4506,10 +4506,10 @@
         <v>157.41</v>
       </c>
       <c r="D188" s="5" t="n">
-        <v>150.75</v>
+        <v>151.65</v>
       </c>
       <c r="E188" s="5" t="n">
-        <v>202.04</v>
+        <v>203.25</v>
       </c>
       <c r="F188" s="7" t="inlineStr"/>
     </row>
@@ -4526,10 +4526,10 @@
         <v>102.7</v>
       </c>
       <c r="D189" s="5" t="n">
-        <v>114.52</v>
+        <v>115.21</v>
       </c>
       <c r="E189" s="5" t="n">
-        <v>131.82</v>
+        <v>132.61</v>
       </c>
       <c r="F189" s="7" t="inlineStr"/>
     </row>
@@ -4546,10 +4546,10 @@
         <v>99.31</v>
       </c>
       <c r="D190" s="5" t="n">
-        <v>112.84</v>
+        <v>113.52</v>
       </c>
       <c r="E190" s="5" t="n">
-        <v>127.47</v>
+        <v>128.24</v>
       </c>
       <c r="F190" s="7" t="inlineStr"/>
     </row>
@@ -4566,10 +4566,10 @@
         <v>87.88</v>
       </c>
       <c r="D191" s="5" t="n">
-        <v>100.53</v>
+        <v>101.13</v>
       </c>
       <c r="E191" s="5" t="n">
-        <v>112.58</v>
+        <v>113.26</v>
       </c>
       <c r="F191" s="7" t="inlineStr"/>
     </row>
@@ -4586,10 +4586,10 @@
         <v>90.98</v>
       </c>
       <c r="D192" s="5" t="n">
-        <v>101.16</v>
+        <v>101.77</v>
       </c>
       <c r="E192" s="5" t="n">
-        <v>116.32</v>
+        <v>117.02</v>
       </c>
       <c r="F192" s="7" t="inlineStr"/>
     </row>
@@ -4606,10 +4606,10 @@
         <v>107.65</v>
       </c>
       <c r="D193" s="5" t="n">
-        <v>116.49</v>
+        <v>117.19</v>
       </c>
       <c r="E193" s="5" t="n">
-        <v>137.37</v>
+        <v>138.19</v>
       </c>
       <c r="F193" s="7" t="inlineStr"/>
     </row>
@@ -4626,10 +4626,10 @@
         <v>80.73999999999999</v>
       </c>
       <c r="D194" s="5" t="n">
-        <v>91.15000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="E194" s="5" t="n">
-        <v>102.83</v>
+        <v>103.45</v>
       </c>
       <c r="F194" s="7" t="inlineStr"/>
     </row>
@@ -4646,10 +4646,10 @@
         <v>98.62</v>
       </c>
       <c r="D195" s="5" t="n">
-        <v>106.84</v>
+        <v>107.48</v>
       </c>
       <c r="E195" s="5" t="n">
-        <v>125.37</v>
+        <v>126.12</v>
       </c>
       <c r="F195" s="7" t="inlineStr"/>
     </row>
@@ -4666,10 +4666,10 @@
         <v>110.15</v>
       </c>
       <c r="D196" s="5" t="n">
-        <v>121.33</v>
+        <v>122.06</v>
       </c>
       <c r="E196" s="5" t="n">
-        <v>139.77</v>
+        <v>140.6</v>
       </c>
       <c r="F196" s="7" t="inlineStr"/>
     </row>
@@ -4686,10 +4686,10 @@
         <v>111.43</v>
       </c>
       <c r="D197" s="5" t="n">
-        <v>128.84</v>
+        <v>129.61</v>
       </c>
       <c r="E197" s="5" t="n">
-        <v>141.07</v>
+        <v>141.91</v>
       </c>
       <c r="F197" s="7" t="inlineStr"/>
     </row>
@@ -4706,10 +4706,10 @@
         <v>72.06</v>
       </c>
       <c r="D198" s="5" t="n">
-        <v>88.29000000000001</v>
+        <v>88.81999999999999</v>
       </c>
       <c r="E198" s="5" t="n">
-        <v>91.02</v>
+        <v>91.56</v>
       </c>
       <c r="F198" s="7" t="inlineStr"/>
     </row>
@@ -4726,10 +4726,10 @@
         <v>54.5</v>
       </c>
       <c r="D199" s="5" t="n">
-        <v>65.65000000000001</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="E199" s="5" t="n">
-        <v>68.68000000000001</v>
+        <v>69.09</v>
       </c>
       <c r="F199" s="7" t="inlineStr"/>
     </row>
@@ -4746,10 +4746,10 @@
         <v>185.41</v>
       </c>
       <c r="D200" s="5" t="n">
-        <v>191.69</v>
+        <v>192.84</v>
       </c>
       <c r="E200" s="5" t="n">
-        <v>233.37</v>
+        <v>234.77</v>
       </c>
       <c r="F200" s="7" t="inlineStr"/>
     </row>
@@ -4766,10 +4766,10 @@
         <v>59.42</v>
       </c>
       <c r="D201" s="5" t="n">
-        <v>72.28</v>
+        <v>72.72</v>
       </c>
       <c r="E201" s="5" t="n">
-        <v>74.7</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="F201" s="7" t="inlineStr"/>
     </row>
@@ -4786,10 +4786,10 @@
         <v>51.4</v>
       </c>
       <c r="D202" s="5" t="n">
-        <v>57.96</v>
+        <v>58.3</v>
       </c>
       <c r="E202" s="5" t="n">
-        <v>64.54000000000001</v>
+        <v>64.92</v>
       </c>
       <c r="F202" s="7" t="inlineStr"/>
     </row>
@@ -4806,10 +4806,10 @@
         <v>45.3</v>
       </c>
       <c r="D203" s="5" t="n">
-        <v>51.01</v>
+        <v>51.32</v>
       </c>
       <c r="E203" s="5" t="n">
-        <v>57.24</v>
+        <v>57.59</v>
       </c>
       <c r="F203" s="7" t="inlineStr"/>
     </row>
@@ -4826,10 +4826,10 @@
         <v>48.48</v>
       </c>
       <c r="D204" s="5" t="n">
-        <v>53.36</v>
+        <v>53.68</v>
       </c>
       <c r="E204" s="5" t="n">
-        <v>61.66</v>
+        <v>62.03</v>
       </c>
       <c r="F204" s="7" t="inlineStr"/>
     </row>
@@ -4846,10 +4846,10 @@
         <v>60.43</v>
       </c>
       <c r="D205" s="5" t="n">
-        <v>61.57</v>
+        <v>61.93</v>
       </c>
       <c r="E205" s="5" t="n">
-        <v>77.36</v>
+        <v>77.83</v>
       </c>
       <c r="F205" s="7" t="inlineStr"/>
     </row>
@@ -4866,10 +4866,10 @@
         <v>56.33</v>
       </c>
       <c r="D206" s="5" t="n">
-        <v>61.11</v>
+        <v>61.48</v>
       </c>
       <c r="E206" s="5" t="n">
-        <v>71.73999999999999</v>
+        <v>72.17</v>
       </c>
       <c r="F206" s="7" t="inlineStr"/>
     </row>
@@ -4886,10 +4886,10 @@
         <v>60.22</v>
       </c>
       <c r="D207" s="5" t="n">
-        <v>63.18</v>
+        <v>63.56</v>
       </c>
       <c r="E207" s="5" t="n">
-        <v>76.31</v>
+        <v>76.76000000000001</v>
       </c>
       <c r="F207" s="7" t="inlineStr"/>
     </row>
@@ -4906,10 +4906,10 @@
         <v>44.24</v>
       </c>
       <c r="D208" s="5" t="n">
-        <v>51.68</v>
+        <v>51.99</v>
       </c>
       <c r="E208" s="5" t="n">
-        <v>55.77</v>
+        <v>56.11</v>
       </c>
       <c r="F208" s="7" t="inlineStr"/>
     </row>
@@ -4926,10 +4926,10 @@
         <v>71.72</v>
       </c>
       <c r="D209" s="5" t="n">
-        <v>72.73999999999999</v>
+        <v>73.17</v>
       </c>
       <c r="E209" s="5" t="n">
-        <v>90.14</v>
+        <v>90.69</v>
       </c>
       <c r="F209" s="7" t="inlineStr"/>
     </row>
@@ -4946,10 +4946,10 @@
         <v>82.45</v>
       </c>
       <c r="D210" s="5" t="n">
-        <v>78.31</v>
+        <v>78.78</v>
       </c>
       <c r="E210" s="5" t="n">
-        <v>103.32</v>
+        <v>103.94</v>
       </c>
       <c r="F210" s="7" t="inlineStr"/>
     </row>
@@ -4966,10 +4966,10 @@
         <v>106.96</v>
       </c>
       <c r="D211" s="5" t="n">
-        <v>89.18000000000001</v>
+        <v>89.72</v>
       </c>
       <c r="E211" s="5" t="n">
-        <v>133.63</v>
+        <v>134.44</v>
       </c>
       <c r="F211" s="7" t="inlineStr"/>
     </row>
@@ -4986,10 +4986,10 @@
         <v>42.87</v>
       </c>
       <c r="D212" s="5" t="n">
-        <v>48.43</v>
+        <v>48.72</v>
       </c>
       <c r="E212" s="5" t="n">
-        <v>53.46</v>
+        <v>53.78</v>
       </c>
       <c r="F212" s="7" t="inlineStr"/>
     </row>
@@ -5006,10 +5006,10 @@
         <v>36.12</v>
       </c>
       <c r="D213" s="5" t="n">
-        <v>43.72</v>
+        <v>43.98</v>
       </c>
       <c r="E213" s="5" t="n">
-        <v>44.95</v>
+        <v>45.22</v>
       </c>
       <c r="F213" s="7" t="inlineStr"/>
     </row>
@@ -5026,10 +5026,10 @@
         <v>40.97</v>
       </c>
       <c r="D214" s="5" t="n">
-        <v>48.41</v>
+        <v>48.7</v>
       </c>
       <c r="E214" s="5" t="n">
-        <v>50.89</v>
+        <v>51.2</v>
       </c>
       <c r="F214" s="7" t="inlineStr"/>
     </row>
@@ -5046,10 +5046,10 @@
         <v>68.79000000000001</v>
       </c>
       <c r="D215" s="5" t="n">
-        <v>69.04000000000001</v>
+        <v>69.45</v>
       </c>
       <c r="E215" s="5" t="n">
-        <v>85.23999999999999</v>
+        <v>85.75</v>
       </c>
       <c r="F215" s="7" t="inlineStr"/>
     </row>
@@ -5066,10 +5066,10 @@
         <v>183.33</v>
       </c>
       <c r="D216" s="5" t="n">
-        <v>145.36</v>
+        <v>146.23</v>
       </c>
       <c r="E216" s="5" t="n">
-        <v>226.63</v>
+        <v>227.99</v>
       </c>
       <c r="F216" s="7" t="inlineStr"/>
     </row>
@@ -5086,10 +5086,10 @@
         <v>255.16</v>
       </c>
       <c r="D217" s="5" t="n">
-        <v>197.36</v>
+        <v>198.54</v>
       </c>
       <c r="E217" s="5" t="n">
-        <v>314.66</v>
+        <v>316.54</v>
       </c>
       <c r="F217" s="7" t="inlineStr"/>
     </row>
@@ -5106,10 +5106,10 @@
         <v>173.79</v>
       </c>
       <c r="D218" s="5" t="n">
-        <v>152.49</v>
+        <v>153.41</v>
       </c>
       <c r="E218" s="5" t="n">
-        <v>213.71</v>
+        <v>214.99</v>
       </c>
       <c r="F218" s="7" t="inlineStr"/>
     </row>
@@ -5126,10 +5126,10 @@
         <v>66.06999999999999</v>
       </c>
       <c r="D219" s="5" t="n">
-        <v>73.76000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="E219" s="5" t="n">
-        <v>81.02</v>
+        <v>81.5</v>
       </c>
       <c r="F219" s="7" t="inlineStr"/>
     </row>
@@ -5146,10 +5146,10 @@
         <v>47.75</v>
       </c>
       <c r="D220" s="5" t="n">
-        <v>59.79</v>
+        <v>60.15</v>
       </c>
       <c r="E220" s="5" t="n">
-        <v>58.39</v>
+        <v>58.74</v>
       </c>
       <c r="F220" s="7" t="inlineStr"/>
     </row>
@@ -5166,10 +5166,10 @@
         <v>59.06</v>
       </c>
       <c r="D221" s="5" t="n">
-        <v>69.55</v>
+        <v>69.97</v>
       </c>
       <c r="E221" s="5" t="n">
-        <v>71.91</v>
+        <v>72.34</v>
       </c>
       <c r="F221" s="7" t="inlineStr"/>
     </row>
@@ -5186,10 +5186,10 @@
         <v>72.52</v>
       </c>
       <c r="D222" s="5" t="n">
-        <v>78.13</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="E222" s="5" t="n">
-        <v>87.93000000000001</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="F222" s="7" t="inlineStr"/>
     </row>
@@ -5206,10 +5206,10 @@
         <v>69.08</v>
       </c>
       <c r="D223" s="5" t="n">
-        <v>82.06</v>
+        <v>82.55</v>
       </c>
       <c r="E223" s="5" t="n">
-        <v>83.41</v>
+        <v>83.91</v>
       </c>
       <c r="F223" s="7" t="inlineStr"/>
     </row>
@@ -5226,10 +5226,10 @@
         <v>81.23999999999999</v>
       </c>
       <c r="D224" s="5" t="n">
-        <v>92.51000000000001</v>
+        <v>93.06</v>
       </c>
       <c r="E224" s="5" t="n">
-        <v>97.39</v>
+        <v>97.97</v>
       </c>
       <c r="F224" s="7" t="inlineStr"/>
     </row>
@@ -5246,10 +5246,10 @@
         <v>92.36</v>
       </c>
       <c r="D225" s="5" t="n">
-        <v>98.83</v>
+        <v>99.42</v>
       </c>
       <c r="E225" s="5" t="n">
-        <v>109.93</v>
+        <v>110.59</v>
       </c>
       <c r="F225" s="7" t="inlineStr"/>
     </row>
@@ -5266,10 +5266,10 @@
         <v>104.67</v>
       </c>
       <c r="D226" s="5" t="n">
-        <v>118.99</v>
+        <v>119.7</v>
       </c>
       <c r="E226" s="5" t="n">
-        <v>123.71</v>
+        <v>124.45</v>
       </c>
       <c r="F226" s="7" t="inlineStr"/>
     </row>
@@ -5286,10 +5286,10 @@
         <v>204.07</v>
       </c>
       <c r="D227" s="5" t="n">
-        <v>219.55</v>
+        <v>220.86</v>
       </c>
       <c r="E227" s="5" t="n">
-        <v>239.75</v>
+        <v>241.19</v>
       </c>
       <c r="F227" s="7" t="inlineStr"/>
     </row>
@@ -5306,10 +5306,10 @@
         <v>385.21</v>
       </c>
       <c r="D228" s="5" t="n">
-        <v>374.3</v>
+        <v>376.55</v>
       </c>
       <c r="E228" s="5" t="n">
-        <v>449.9</v>
+        <v>452.6</v>
       </c>
       <c r="F228" s="7" t="inlineStr"/>
     </row>
@@ -5326,10 +5326,10 @@
         <v>441.06</v>
       </c>
       <c r="D229" s="5" t="n">
-        <v>462.16</v>
+        <v>464.93</v>
       </c>
       <c r="E229" s="5" t="n">
-        <v>512.11</v>
+        <v>515.1799999999999</v>
       </c>
       <c r="F229" s="7" t="inlineStr"/>
     </row>
@@ -5346,10 +5346,10 @@
         <v>425.89</v>
       </c>
       <c r="D230" s="5" t="n">
-        <v>428.34</v>
+        <v>430.91</v>
       </c>
       <c r="E230" s="5" t="n">
-        <v>491.49</v>
+        <v>494.43</v>
       </c>
       <c r="F230" s="7" t="inlineStr"/>
     </row>
@@ -5366,10 +5366,10 @@
         <v>156.59</v>
       </c>
       <c r="D231" s="5" t="n">
-        <v>170.13</v>
+        <v>171.15</v>
       </c>
       <c r="E231" s="5" t="n">
-        <v>179.61</v>
+        <v>180.69</v>
       </c>
       <c r="F231" s="7" t="inlineStr"/>
     </row>
@@ -5386,10 +5386,10 @@
         <v>157.38</v>
       </c>
       <c r="D232" s="5" t="n">
-        <v>175.43</v>
+        <v>176.48</v>
       </c>
       <c r="E232" s="5" t="n">
-        <v>179.43</v>
+        <v>180.51</v>
       </c>
       <c r="F232" s="7" t="inlineStr"/>
     </row>
@@ -5406,10 +5406,10 @@
         <v>155.91</v>
       </c>
       <c r="D233" s="5" t="n">
-        <v>171.84</v>
+        <v>172.87</v>
       </c>
       <c r="E233" s="5" t="n">
-        <v>176.67</v>
+        <v>177.73</v>
       </c>
       <c r="F233" s="7" t="inlineStr"/>
     </row>
@@ -5426,10 +5426,10 @@
         <v>106.68</v>
       </c>
       <c r="D234" s="5" t="n">
-        <v>127.15</v>
+        <v>127.92</v>
       </c>
       <c r="E234" s="5" t="n">
-        <v>120.15</v>
+        <v>120.87</v>
       </c>
       <c r="F234" s="7" t="inlineStr"/>
     </row>
@@ -5446,10 +5446,10 @@
         <v>72.58</v>
       </c>
       <c r="D235" s="5" t="n">
-        <v>92.51000000000001</v>
+        <v>93.06</v>
       </c>
       <c r="E235" s="5" t="n">
-        <v>81.25</v>
+        <v>81.73999999999999</v>
       </c>
       <c r="F235" s="7" t="inlineStr"/>
     </row>
@@ -5466,10 +5466,10 @@
         <v>95.95</v>
       </c>
       <c r="D236" s="5" t="n">
-        <v>105.19</v>
+        <v>105.82</v>
       </c>
       <c r="E236" s="5" t="n">
-        <v>106.93</v>
+        <v>107.57</v>
       </c>
       <c r="F236" s="7" t="inlineStr"/>
     </row>
@@ -5486,10 +5486,10 @@
         <v>96.16</v>
       </c>
       <c r="D237" s="5" t="n">
-        <v>99.98999999999999</v>
+        <v>100.59</v>
       </c>
       <c r="E237" s="5" t="n">
-        <v>106.68</v>
+        <v>107.32</v>
       </c>
       <c r="F237" s="7" t="inlineStr"/>
     </row>
@@ -5506,10 +5506,10 @@
         <v>134.91</v>
       </c>
       <c r="D238" s="5" t="n">
-        <v>128.13</v>
+        <v>128.9</v>
       </c>
       <c r="E238" s="5" t="n">
-        <v>149</v>
+        <v>149.9</v>
       </c>
       <c r="F238" s="7" t="inlineStr"/>
     </row>
@@ -5526,10 +5526,10 @@
         <v>116.44</v>
       </c>
       <c r="D239" s="5" t="n">
-        <v>122.07</v>
+        <v>122.8</v>
       </c>
       <c r="E239" s="5" t="n">
-        <v>128.24</v>
+        <v>129.01</v>
       </c>
       <c r="F239" s="7" t="inlineStr"/>
     </row>
@@ -5546,10 +5546,10 @@
         <v>230.59</v>
       </c>
       <c r="D240" s="5" t="n">
-        <v>213.04</v>
+        <v>214.32</v>
       </c>
       <c r="E240" s="5" t="n">
-        <v>253.23</v>
+        <v>254.75</v>
       </c>
       <c r="F240" s="7" t="inlineStr"/>
     </row>
@@ -5566,10 +5566,10 @@
         <v>123.7</v>
       </c>
       <c r="D241" s="5" t="n">
-        <v>115.2</v>
+        <v>115.89</v>
       </c>
       <c r="E241" s="5" t="n">
-        <v>135.46</v>
+        <v>136.27</v>
       </c>
       <c r="F241" s="7" t="inlineStr"/>
     </row>
@@ -5586,10 +5586,10 @@
         <v>93.78</v>
       </c>
       <c r="D242" s="5" t="n">
-        <v>91.8</v>
+        <v>92.34999999999999</v>
       </c>
       <c r="E242" s="5" t="n">
-        <v>102.3</v>
+        <v>102.92</v>
       </c>
       <c r="F242" s="7" t="inlineStr"/>
     </row>
@@ -5606,10 +5606,10 @@
         <v>104.72</v>
       </c>
       <c r="D243" s="5" t="n">
-        <v>101.4</v>
+        <v>102.01</v>
       </c>
       <c r="E243" s="5" t="n">
-        <v>113.8</v>
+        <v>114.49</v>
       </c>
       <c r="F243" s="7" t="inlineStr"/>
     </row>
@@ -5626,10 +5626,10 @@
         <v>70.17</v>
       </c>
       <c r="D244" s="5" t="n">
-        <v>69.87</v>
+        <v>70.29000000000001</v>
       </c>
       <c r="E244" s="5" t="n">
-        <v>75.97</v>
+        <v>76.42</v>
       </c>
       <c r="F244" s="7" t="inlineStr"/>
     </row>
@@ -5646,10 +5646,10 @@
         <v>41.9</v>
       </c>
       <c r="D245" s="5" t="n">
-        <v>45.46</v>
+        <v>45.73</v>
       </c>
       <c r="E245" s="5" t="n">
-        <v>45.27</v>
+        <v>45.54</v>
       </c>
       <c r="F245" s="7" t="inlineStr"/>
     </row>
@@ -5666,10 +5666,10 @@
         <v>94.34999999999999</v>
       </c>
       <c r="D246" s="5" t="n">
-        <v>94.17</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="E246" s="5" t="n">
-        <v>101.72</v>
+        <v>102.33</v>
       </c>
       <c r="F246" s="7" t="inlineStr"/>
     </row>
@@ -5686,10 +5686,10 @@
         <v>81.66</v>
       </c>
       <c r="D247" s="5" t="n">
-        <v>73.44</v>
+        <v>73.88</v>
       </c>
       <c r="E247" s="5" t="n">
-        <v>87.84999999999999</v>
+        <v>88.38</v>
       </c>
       <c r="F247" s="7" t="inlineStr"/>
     </row>
@@ -5706,10 +5706,10 @@
         <v>80.48</v>
       </c>
       <c r="D248" s="5" t="n">
-        <v>87.06</v>
+        <v>87.58</v>
       </c>
       <c r="E248" s="5" t="n">
-        <v>86.31999999999999</v>
+        <v>86.83</v>
       </c>
       <c r="F248" s="7" t="inlineStr"/>
     </row>
@@ -5726,10 +5726,10 @@
         <v>160.9</v>
       </c>
       <c r="D249" s="5" t="n">
-        <v>119.39</v>
+        <v>120.1</v>
       </c>
       <c r="E249" s="5" t="n">
-        <v>172.04</v>
+        <v>173.07</v>
       </c>
       <c r="F249" s="7" t="inlineStr"/>
     </row>
@@ -5746,10 +5746,10 @@
         <v>70.48999999999999</v>
       </c>
       <c r="D250" s="5" t="n">
-        <v>75.12</v>
+        <v>75.56999999999999</v>
       </c>
       <c r="E250" s="5" t="n">
-        <v>75.14</v>
+        <v>75.59</v>
       </c>
       <c r="F250" s="7" t="inlineStr"/>
     </row>
@@ -5766,10 +5766,10 @@
         <v>86.27</v>
       </c>
       <c r="D251" s="5" t="n">
-        <v>95.42</v>
+        <v>95.98999999999999</v>
       </c>
       <c r="E251" s="5" t="n">
-        <v>91.64</v>
+        <v>92.19</v>
       </c>
       <c r="F251" s="7" t="inlineStr"/>
     </row>
@@ -5786,10 +5786,10 @@
         <v>430.06</v>
       </c>
       <c r="D252" s="5" t="n">
-        <v>289.57</v>
+        <v>291.31</v>
       </c>
       <c r="E252" s="5" t="n">
-        <v>455.23</v>
+        <v>457.96</v>
       </c>
       <c r="F252" s="7" t="inlineStr"/>
     </row>
@@ -5806,10 +5806,10 @@
         <v>173.97</v>
       </c>
       <c r="D253" s="5" t="n">
-        <v>161.13</v>
+        <v>162.1</v>
       </c>
       <c r="E253" s="5" t="n">
-        <v>183.52</v>
+        <v>184.62</v>
       </c>
       <c r="F253" s="7" t="inlineStr"/>
     </row>
@@ -5826,10 +5826,10 @@
         <v>155.59</v>
       </c>
       <c r="D254" s="5" t="n">
-        <v>134.05</v>
+        <v>134.85</v>
       </c>
       <c r="E254" s="5" t="n">
-        <v>164.01</v>
+        <v>164.99</v>
       </c>
       <c r="F254" s="7" t="inlineStr"/>
     </row>
@@ -5846,10 +5846,10 @@
         <v>253.4</v>
       </c>
       <c r="D255" s="5" t="n">
-        <v>183.76</v>
+        <v>184.86</v>
       </c>
       <c r="E255" s="5" t="n">
-        <v>266.92</v>
+        <v>268.52</v>
       </c>
       <c r="F255" s="7" t="inlineStr"/>
     </row>
@@ -5866,10 +5866,10 @@
         <v>49.3</v>
       </c>
       <c r="D256" s="5" t="n">
-        <v>61.07</v>
+        <v>61.44</v>
       </c>
       <c r="E256" s="5" t="n">
-        <v>51.89</v>
+        <v>52.2</v>
       </c>
       <c r="F256" s="7" t="inlineStr"/>
     </row>
@@ -5886,10 +5886,10 @@
         <v>81.59</v>
       </c>
       <c r="D257" s="5" t="n">
-        <v>81.43000000000001</v>
+        <v>81.92</v>
       </c>
       <c r="E257" s="5" t="n">
-        <v>85.81999999999999</v>
+        <v>86.34</v>
       </c>
       <c r="F257" s="7" t="inlineStr"/>
     </row>
@@ -5906,10 +5906,10 @@
         <v>359.37</v>
       </c>
       <c r="D258" s="5" t="n">
-        <v>230.93</v>
+        <v>232.31</v>
       </c>
       <c r="E258" s="5" t="n">
-        <v>377.77</v>
+        <v>380.04</v>
       </c>
       <c r="F258" s="7" t="inlineStr"/>
     </row>
@@ -5926,10 +5926,10 @@
         <v>173.92</v>
       </c>
       <c r="D259" s="5" t="n">
-        <v>141.54</v>
+        <v>142.38</v>
       </c>
       <c r="E259" s="5" t="n">
-        <v>182.7</v>
+        <v>183.8</v>
       </c>
       <c r="F259" s="7" t="inlineStr"/>
     </row>
@@ -5946,10 +5946,10 @@
         <v>93.90000000000001</v>
       </c>
       <c r="D260" s="5" t="n">
-        <v>87.28</v>
+        <v>87.81</v>
       </c>
       <c r="E260" s="5" t="n">
-        <v>98.34</v>
+        <v>98.93000000000001</v>
       </c>
       <c r="F260" s="7" t="inlineStr"/>
     </row>
@@ -5966,10 +5966,10 @@
         <v>99.90000000000001</v>
       </c>
       <c r="D261" s="5" t="n">
-        <v>94.31</v>
+        <v>94.88</v>
       </c>
       <c r="E261" s="5" t="n">
-        <v>104.31</v>
+        <v>104.93</v>
       </c>
       <c r="F261" s="7" t="inlineStr"/>
     </row>
@@ -5986,10 +5986,10 @@
         <v>82.47</v>
       </c>
       <c r="D262" s="5" t="n">
-        <v>93.64</v>
+        <v>94.2</v>
       </c>
       <c r="E262" s="5" t="n">
-        <v>85.84999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="F262" s="7" t="inlineStr"/>
     </row>
@@ -6006,10 +6006,10 @@
         <v>107.35</v>
       </c>
       <c r="D263" s="5" t="n">
-        <v>108.06</v>
+        <v>108.71</v>
       </c>
       <c r="E263" s="5" t="n">
-        <v>111.47</v>
+        <v>112.14</v>
       </c>
       <c r="F263" s="7" t="inlineStr"/>
     </row>
@@ -6026,10 +6026,10 @@
         <v>162.22</v>
       </c>
       <c r="D264" s="5" t="n">
-        <v>127.42</v>
+        <v>128.19</v>
       </c>
       <c r="E264" s="5" t="n">
-        <v>168.02</v>
+        <v>169.03</v>
       </c>
       <c r="F264" s="7" t="inlineStr"/>
     </row>
@@ -6046,10 +6046,10 @@
         <v>435.34</v>
       </c>
       <c r="D265" s="5" t="n">
-        <v>264.71</v>
+        <v>266.3</v>
       </c>
       <c r="E265" s="5" t="n">
-        <v>449.8</v>
+        <v>452.5</v>
       </c>
       <c r="F265" s="7" t="inlineStr"/>
     </row>
@@ -6066,10 +6066,10 @@
         <v>107.33</v>
       </c>
       <c r="D266" s="5" t="n">
-        <v>99.73</v>
+        <v>100.33</v>
       </c>
       <c r="E266" s="5" t="n">
-        <v>110.41</v>
+        <v>111.07</v>
       </c>
       <c r="F266" s="7" t="inlineStr"/>
     </row>
@@ -6086,10 +6086,10 @@
         <v>112.68</v>
       </c>
       <c r="D267" s="5" t="n">
-        <v>103.7</v>
+        <v>104.32</v>
       </c>
       <c r="E267" s="5" t="n">
-        <v>115.41</v>
+        <v>116.1</v>
       </c>
       <c r="F267" s="7" t="inlineStr"/>
     </row>
@@ -6106,10 +6106,10 @@
         <v>66.42</v>
       </c>
       <c r="D268" s="5" t="n">
-        <v>72.65000000000001</v>
+        <v>73.08</v>
       </c>
       <c r="E268" s="5" t="n">
-        <v>67.73</v>
+        <v>68.14</v>
       </c>
       <c r="F268" s="7" t="inlineStr"/>
     </row>
@@ -6126,10 +6126,10 @@
         <v>75.34999999999999</v>
       </c>
       <c r="D269" s="5" t="n">
-        <v>78.39</v>
+        <v>78.86</v>
       </c>
       <c r="E269" s="5" t="n">
-        <v>76.69</v>
+        <v>77.15000000000001</v>
       </c>
       <c r="F269" s="7" t="inlineStr"/>
     </row>
@@ -6146,10 +6146,10 @@
         <v>83.58</v>
       </c>
       <c r="D270" s="5" t="n">
-        <v>78.14</v>
+        <v>78.61</v>
       </c>
       <c r="E270" s="5" t="n">
-        <v>84.90000000000001</v>
+        <v>85.41</v>
       </c>
       <c r="F270" s="7" t="inlineStr"/>
     </row>
@@ -6166,10 +6166,10 @@
         <v>77.75</v>
       </c>
       <c r="D271" s="5" t="n">
-        <v>72.34</v>
+        <v>72.78</v>
       </c>
       <c r="E271" s="5" t="n">
-        <v>78.81999999999999</v>
+        <v>79.29000000000001</v>
       </c>
       <c r="F271" s="7" t="inlineStr"/>
     </row>
@@ -6186,10 +6186,10 @@
         <v>45.49</v>
       </c>
       <c r="D272" s="5" t="n">
-        <v>67.83</v>
+        <v>68.23999999999999</v>
       </c>
       <c r="E272" s="5" t="n">
-        <v>45.91</v>
+        <v>46.18</v>
       </c>
       <c r="F272" s="7" t="inlineStr"/>
     </row>
@@ -6206,10 +6206,10 @@
         <v>97.18000000000001</v>
       </c>
       <c r="D273" s="5" t="n">
-        <v>84.14</v>
+        <v>84.65000000000001</v>
       </c>
       <c r="E273" s="5" t="n">
-        <v>97.62</v>
+        <v>98.20999999999999</v>
       </c>
       <c r="F273" s="7" t="inlineStr"/>
     </row>
@@ -6226,10 +6226,10 @@
         <v>74.36</v>
       </c>
       <c r="D274" s="5" t="n">
-        <v>71.2</v>
+        <v>71.63</v>
       </c>
       <c r="E274" s="5" t="n">
-        <v>74.36</v>
+        <v>74.81</v>
       </c>
       <c r="F274" s="7" t="inlineStr"/>
     </row>
@@ -6246,10 +6246,10 @@
         <v>60.42</v>
       </c>
       <c r="D275" s="5" t="n">
-        <v>64.27</v>
+        <v>64.53</v>
       </c>
       <c r="E275" s="5" t="n">
-        <v>60.42</v>
+        <v>60.66</v>
       </c>
       <c r="F275" s="7" t="inlineStr"/>
     </row>
@@ -6266,10 +6266,10 @@
         <v>63.17</v>
       </c>
       <c r="D276" s="5" t="n">
-        <v>65.76000000000001</v>
+        <v>65.89</v>
       </c>
       <c r="E276" s="5" t="n">
-        <v>63.17</v>
+        <v>63.3</v>
       </c>
       <c r="F276" s="7" t="inlineStr"/>
     </row>
@@ -6312,6 +6312,26 @@
         <v>85.61</v>
       </c>
       <c r="F278" s="7" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="4" t="inlineStr">
+        <is>
+          <t>Aug 2026</t>
+        </is>
+      </c>
+      <c r="B279" s="5" t="n">
+        <v>82.81</v>
+      </c>
+      <c r="C279" s="5" t="n">
+        <v>84.17</v>
+      </c>
+      <c r="D279" s="5" t="n">
+        <v>82.81</v>
+      </c>
+      <c r="E279" s="5" t="n">
+        <v>84.17</v>
+      </c>
+      <c r="F279" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6324,7 +6344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E278"/>
+  <dimension ref="A1:E279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6374,10 +6394,10 @@
         <v>75.81999999999999</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>86.92</v>
+        <v>87.44</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>140.91</v>
+        <v>141.75</v>
       </c>
     </row>
     <row r="3">
@@ -6393,10 +6413,10 @@
         <v>22.06</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>36.38</v>
+        <v>36.59</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>40.92</v>
+        <v>41.17</v>
       </c>
     </row>
     <row r="4">
@@ -6412,10 +6432,10 @@
         <v>26.29</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>38.97</v>
+        <v>39.21</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>48.67</v>
+        <v>48.97</v>
       </c>
     </row>
     <row r="5">
@@ -6431,10 +6451,10 @@
         <v>19.41</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>32.34</v>
+        <v>32.54</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>35.87</v>
+        <v>36.09</v>
       </c>
     </row>
     <row r="6">
@@ -6450,10 +6470,10 @@
         <v>20.74</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>33.89</v>
+        <v>34.1</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>38.26</v>
+        <v>38.49</v>
       </c>
     </row>
     <row r="7">
@@ -6469,10 +6489,10 @@
         <v>29.68</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>43.06</v>
+        <v>43.32</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>54.66</v>
+        <v>54.99</v>
       </c>
     </row>
     <row r="8">
@@ -6488,10 +6508,10 @@
         <v>31.61</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>49.14</v>
+        <v>49.43</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>58.05</v>
+        <v>58.39</v>
       </c>
     </row>
     <row r="9">
@@ -6507,10 +6527,10 @@
         <v>49.01</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>107.11</v>
+        <v>107.75</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>89.73</v>
+        <v>90.27</v>
       </c>
     </row>
     <row r="10">
@@ -6526,10 +6546,10 @@
         <v>116.77</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>116.34</v>
+        <v>117.04</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>213.17</v>
+        <v>214.45</v>
       </c>
     </row>
     <row r="11">
@@ -6545,10 +6565,10 @@
         <v>37.43</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>55.17</v>
+        <v>55.5</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>68.22</v>
+        <v>68.63</v>
       </c>
     </row>
     <row r="12">
@@ -6564,10 +6584,10 @@
         <v>37.85</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>58.45</v>
+        <v>58.8</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>68.88</v>
+        <v>69.29000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -6583,10 +6603,10 @@
         <v>33.72</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>56.66</v>
+        <v>57</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>61.27</v>
+        <v>61.64</v>
       </c>
     </row>
     <row r="14">
@@ -6602,10 +6622,10 @@
         <v>43.57</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>64.65000000000001</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>79.06</v>
+        <v>79.53</v>
       </c>
     </row>
     <row r="15">
@@ -6621,10 +6641,10 @@
         <v>26.2</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>42.78</v>
+        <v>43.04</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>47.48</v>
+        <v>47.76</v>
       </c>
     </row>
     <row r="16">
@@ -6640,10 +6660,10 @@
         <v>32.32</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>50.99</v>
+        <v>51.3</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>58.49</v>
+        <v>58.84</v>
       </c>
     </row>
     <row r="17">
@@ -6659,10 +6679,10 @@
         <v>125.43</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>125.63</v>
+        <v>126.38</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>226.4</v>
+        <v>227.76</v>
       </c>
     </row>
     <row r="18">
@@ -6678,10 +6698,10 @@
         <v>131.39</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>139.89</v>
+        <v>140.73</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>236.56</v>
+        <v>237.98</v>
       </c>
     </row>
     <row r="19">
@@ -6697,10 +6717,10 @@
         <v>110.88</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>116.53</v>
+        <v>117.23</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>199.13</v>
+        <v>200.32</v>
       </c>
     </row>
     <row r="20">
@@ -6716,10 +6736,10 @@
         <v>65.59999999999999</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>71.5</v>
+        <v>71.92</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>117.55</v>
+        <v>118.25</v>
       </c>
     </row>
     <row r="21">
@@ -6735,10 +6755,10 @@
         <v>50.64</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>58.75</v>
+        <v>59.1</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>90.54000000000001</v>
+        <v>91.08</v>
       </c>
     </row>
     <row r="22">
@@ -6754,10 +6774,10 @@
         <v>19.92</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>32.91</v>
+        <v>33.11</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>35.54</v>
+        <v>35.75</v>
       </c>
     </row>
     <row r="23">
@@ -6773,10 +6793,10 @@
         <v>36.49</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>53.23</v>
+        <v>53.55</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>64.97</v>
+        <v>65.34999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -6792,10 +6812,10 @@
         <v>27.74</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>43.35</v>
+        <v>43.61</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>49.29</v>
+        <v>49.58</v>
       </c>
     </row>
     <row r="25">
@@ -6811,10 +6831,10 @@
         <v>32.42</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>46.73</v>
+        <v>47.01</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>57.49</v>
+        <v>57.84</v>
       </c>
     </row>
     <row r="26">
@@ -6830,10 +6850,10 @@
         <v>27.73</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>42.95</v>
+        <v>43.21</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>49.01</v>
+        <v>49.31</v>
       </c>
     </row>
     <row r="27">
@@ -6849,10 +6869,10 @@
         <v>36.96</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>50.15</v>
+        <v>50.45</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>65.11</v>
+        <v>65.5</v>
       </c>
     </row>
     <row r="28">
@@ -6868,10 +6888,10 @@
         <v>36.19</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>50.27</v>
+        <v>50.57</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>63.54</v>
+        <v>63.93</v>
       </c>
     </row>
     <row r="29">
@@ -6887,10 +6907,10 @@
         <v>86.17</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>83.06999999999999</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>151.04</v>
+        <v>151.95</v>
       </c>
     </row>
     <row r="30">
@@ -6906,10 +6926,10 @@
         <v>104.05</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>100.6</v>
+        <v>101.2</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>182.07</v>
+        <v>183.16</v>
       </c>
     </row>
     <row r="31">
@@ -6925,10 +6945,10 @@
         <v>127.53</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>124.99</v>
+        <v>125.73</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>222.77</v>
+        <v>224.11</v>
       </c>
     </row>
     <row r="32">
@@ -6944,10 +6964,10 @@
         <v>33.82</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>46.75</v>
+        <v>47.03</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>58.91</v>
+        <v>59.26</v>
       </c>
     </row>
     <row r="33">
@@ -6963,10 +6983,10 @@
         <v>122.66</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>111.94</v>
+        <v>112.61</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>213.05</v>
+        <v>214.32</v>
       </c>
     </row>
     <row r="34">
@@ -6982,10 +7002,10 @@
         <v>27.46</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>39.11</v>
+        <v>39.34</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>47.56</v>
+        <v>47.84</v>
       </c>
     </row>
     <row r="35">
@@ -7001,10 +7021,10 @@
         <v>23.63</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>35.51</v>
+        <v>35.72</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>40.71</v>
+        <v>40.96</v>
       </c>
     </row>
     <row r="36">
@@ -7020,10 +7040,10 @@
         <v>32.23</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>43.62</v>
+        <v>43.88</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>55.24</v>
+        <v>55.57</v>
       </c>
     </row>
     <row r="37">
@@ -7039,10 +7059,10 @@
         <v>38.39</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>53.65</v>
+        <v>53.98</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>65.45</v>
+        <v>65.84999999999999</v>
       </c>
     </row>
     <row r="38">
@@ -7058,10 +7078,10 @@
         <v>73.48999999999999</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>81.09999999999999</v>
+        <v>81.59</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>124.93</v>
+        <v>125.68</v>
       </c>
     </row>
     <row r="39">
@@ -7077,10 +7097,10 @@
         <v>35.43</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>50.49</v>
+        <v>50.79</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>60.05</v>
+        <v>60.41</v>
       </c>
     </row>
     <row r="40">
@@ -7096,10 +7116,10 @@
         <v>34.69</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>47.74</v>
+        <v>48.03</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>58.62</v>
+        <v>58.98</v>
       </c>
     </row>
     <row r="41">
@@ -7115,10 +7135,10 @@
         <v>30.95</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>42.82</v>
+        <v>43.08</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>52.32</v>
+        <v>52.64</v>
       </c>
     </row>
     <row r="42">
@@ -7134,10 +7154,10 @@
         <v>41.15</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>53.22</v>
+        <v>53.54</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>69.59</v>
+        <v>70.01000000000001</v>
       </c>
     </row>
     <row r="43">
@@ -7153,10 +7173,10 @@
         <v>25.26</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>35.53</v>
+        <v>35.74</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>42.74</v>
+        <v>42.99</v>
       </c>
     </row>
     <row r="44">
@@ -7172,10 +7192,10 @@
         <v>89.47</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>94.56999999999999</v>
+        <v>95.14</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>151.33</v>
+        <v>152.24</v>
       </c>
     </row>
     <row r="45">
@@ -7191,10 +7211,10 @@
         <v>62.98</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>75.69</v>
+        <v>76.14</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>106.5</v>
+        <v>107.14</v>
       </c>
     </row>
     <row r="46">
@@ -7210,10 +7230,10 @@
         <v>63.16</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>86.69</v>
+        <v>87.20999999999999</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>106.77</v>
+        <v>107.41</v>
       </c>
     </row>
     <row r="47">
@@ -7229,10 +7249,10 @@
         <v>102.26</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>131.67</v>
+        <v>132.46</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>172.16</v>
+        <v>173.2</v>
       </c>
     </row>
     <row r="48">
@@ -7248,10 +7268,10 @@
         <v>75.83</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>106.1</v>
+        <v>106.74</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>127.15</v>
+        <v>127.91</v>
       </c>
     </row>
     <row r="49">
@@ -7267,10 +7287,10 @@
         <v>397.05</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>385.19</v>
+        <v>387.5</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>663.05</v>
+        <v>667.03</v>
       </c>
     </row>
     <row r="50">
@@ -7286,10 +7306,10 @@
         <v>105.7</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>129.74</v>
+        <v>130.52</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>176.11</v>
+        <v>177.17</v>
       </c>
     </row>
     <row r="51">
@@ -7305,10 +7325,10 @@
         <v>47.17</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>66.39</v>
+        <v>66.79000000000001</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>78.41</v>
+        <v>78.88</v>
       </c>
     </row>
     <row r="52">
@@ -7324,10 +7344,10 @@
         <v>60.36</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>79.53</v>
+        <v>80</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>100.11</v>
+        <v>100.71</v>
       </c>
     </row>
     <row r="53">
@@ -7343,10 +7363,10 @@
         <v>55.78</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>67.33</v>
+        <v>67.73</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>92.23</v>
+        <v>92.78</v>
       </c>
     </row>
     <row r="54">
@@ -7362,10 +7382,10 @@
         <v>48.17</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>59.36</v>
+        <v>59.71</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>79.40000000000001</v>
+        <v>79.87</v>
       </c>
     </row>
     <row r="55">
@@ -7381,10 +7401,10 @@
         <v>55.55</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>65.98999999999999</v>
+        <v>66.39</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>91.28</v>
+        <v>91.83</v>
       </c>
     </row>
     <row r="56">
@@ -7400,10 +7420,10 @@
         <v>43.73</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>55.75</v>
+        <v>56.09</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>71.54000000000001</v>
+        <v>71.97</v>
       </c>
     </row>
     <row r="57">
@@ -7419,10 +7439,10 @@
         <v>32.22</v>
       </c>
       <c r="D57" s="5" t="n">
-        <v>44.28</v>
+        <v>44.55</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>52.48</v>
+        <v>52.79</v>
       </c>
     </row>
     <row r="58">
@@ -7438,10 +7458,10 @@
         <v>47.31</v>
       </c>
       <c r="D58" s="5" t="n">
-        <v>56.05</v>
+        <v>56.39</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>76.70999999999999</v>
+        <v>77.17</v>
       </c>
     </row>
     <row r="59">
@@ -7457,10 +7477,10 @@
         <v>40.08</v>
       </c>
       <c r="D59" s="5" t="n">
-        <v>53.66</v>
+        <v>53.98</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>64.68000000000001</v>
+        <v>65.06</v>
       </c>
     </row>
     <row r="60">
@@ -7476,10 +7496,10 @@
         <v>53.21</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>72.59</v>
+        <v>73.02</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>85.45</v>
+        <v>85.97</v>
       </c>
     </row>
     <row r="61">
@@ -7495,10 +7515,10 @@
         <v>51.05</v>
       </c>
       <c r="D61" s="5" t="n">
-        <v>66.84</v>
+        <v>67.23999999999999</v>
       </c>
       <c r="E61" s="5" t="n">
-        <v>81.59</v>
+        <v>82.08</v>
       </c>
     </row>
     <row r="62">
@@ -7514,10 +7534,10 @@
         <v>55.38</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>64.43000000000001</v>
+        <v>64.81999999999999</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>88.17</v>
+        <v>88.7</v>
       </c>
     </row>
     <row r="63">
@@ -7533,10 +7553,10 @@
         <v>48.73</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>63.31</v>
+        <v>63.69</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>77.29000000000001</v>
+        <v>77.75</v>
       </c>
     </row>
     <row r="64">
@@ -7552,10 +7572,10 @@
         <v>45.62</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>56.17</v>
+        <v>56.5</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>72.08</v>
+        <v>72.51000000000001</v>
       </c>
     </row>
     <row r="65">
@@ -7571,10 +7591,10 @@
         <v>143.1</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>129.03</v>
+        <v>129.8</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>226.33</v>
+        <v>227.69</v>
       </c>
     </row>
     <row r="66">
@@ -7590,10 +7610,10 @@
         <v>38.45</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>48.85</v>
+        <v>49.14</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>60.88</v>
+        <v>61.25</v>
       </c>
     </row>
     <row r="67">
@@ -7609,10 +7629,10 @@
         <v>27.84</v>
       </c>
       <c r="D67" s="5" t="n">
-        <v>37.9</v>
+        <v>38.13</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>44.13</v>
+        <v>44.39</v>
       </c>
     </row>
     <row r="68">
@@ -7628,10 +7648,10 @@
         <v>72.97</v>
       </c>
       <c r="D68" s="5" t="n">
-        <v>74.63</v>
+        <v>75.08</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>115.62</v>
+        <v>116.32</v>
       </c>
     </row>
     <row r="69">
@@ -7647,10 +7667,10 @@
         <v>39.35</v>
       </c>
       <c r="D69" s="5" t="n">
-        <v>65.62</v>
+        <v>66.02</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>62.33</v>
+        <v>62.7</v>
       </c>
     </row>
     <row r="70">
@@ -7666,10 +7686,10 @@
         <v>29.61</v>
       </c>
       <c r="D70" s="5" t="n">
-        <v>39.03</v>
+        <v>39.26</v>
       </c>
       <c r="E70" s="5" t="n">
-        <v>46.88</v>
+        <v>47.16</v>
       </c>
     </row>
     <row r="71">
@@ -7685,10 +7705,10 @@
         <v>47.45</v>
       </c>
       <c r="D71" s="5" t="n">
-        <v>56.92</v>
+        <v>57.26</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>75.01000000000001</v>
+        <v>75.45999999999999</v>
       </c>
     </row>
     <row r="72">
@@ -7704,10 +7724,10 @@
         <v>35.75</v>
       </c>
       <c r="D72" s="5" t="n">
-        <v>47.79</v>
+        <v>48.07</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>56.42</v>
+        <v>56.76</v>
       </c>
     </row>
     <row r="73">
@@ -7723,10 +7743,10 @@
         <v>45.82</v>
       </c>
       <c r="D73" s="5" t="n">
-        <v>53.8</v>
+        <v>54.13</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>72.19</v>
+        <v>72.62</v>
       </c>
     </row>
     <row r="74">
@@ -7742,10 +7762,10 @@
         <v>40.23</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>49.43</v>
+        <v>49.72</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>63.18</v>
+        <v>63.56</v>
       </c>
     </row>
     <row r="75">
@@ -7761,10 +7781,10 @@
         <v>27.9</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>38.05</v>
+        <v>38.27</v>
       </c>
       <c r="E75" s="5" t="n">
-        <v>43.68</v>
+        <v>43.94</v>
       </c>
     </row>
     <row r="76">
@@ -7780,10 +7800,10 @@
         <v>28.56</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>39.99</v>
+        <v>40.23</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>44.58</v>
+        <v>44.84</v>
       </c>
     </row>
     <row r="77">
@@ -7799,10 +7819,10 @@
         <v>32.65</v>
       </c>
       <c r="D77" s="5" t="n">
-        <v>42.91</v>
+        <v>43.16</v>
       </c>
       <c r="E77" s="5" t="n">
-        <v>50.87</v>
+        <v>51.17</v>
       </c>
     </row>
     <row r="78">
@@ -7818,10 +7838,10 @@
         <v>209.33</v>
       </c>
       <c r="D78" s="5" t="n">
-        <v>167.59</v>
+        <v>168.59</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>325.55</v>
+        <v>327.5</v>
       </c>
     </row>
     <row r="79">
@@ -7837,10 +7857,10 @@
         <v>186.31</v>
       </c>
       <c r="D79" s="5" t="n">
-        <v>151.18</v>
+        <v>152.08</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>289.23</v>
+        <v>290.97</v>
       </c>
     </row>
     <row r="80">
@@ -7856,10 +7876,10 @@
         <v>78.56</v>
       </c>
       <c r="D80" s="5" t="n">
-        <v>78.03</v>
+        <v>78.5</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>121.58</v>
+        <v>122.31</v>
       </c>
     </row>
     <row r="81">
@@ -7875,10 +7895,10 @@
         <v>96.8</v>
       </c>
       <c r="D81" s="5" t="n">
-        <v>86</v>
+        <v>86.51000000000001</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>149.35</v>
+        <v>150.24</v>
       </c>
     </row>
     <row r="82">
@@ -7894,10 +7914,10 @@
         <v>30.88</v>
       </c>
       <c r="D82" s="5" t="n">
-        <v>39.78</v>
+        <v>40.01</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>47.5</v>
+        <v>47.78</v>
       </c>
     </row>
     <row r="83">
@@ -7913,10 +7933,10 @@
         <v>28.33</v>
       </c>
       <c r="D83" s="5" t="n">
-        <v>37.99</v>
+        <v>38.22</v>
       </c>
       <c r="E83" s="5" t="n">
-        <v>43.49</v>
+        <v>43.75</v>
       </c>
     </row>
     <row r="84">
@@ -7932,10 +7952,10 @@
         <v>31.21</v>
       </c>
       <c r="D84" s="5" t="n">
-        <v>42.54</v>
+        <v>42.8</v>
       </c>
       <c r="E84" s="5" t="n">
-        <v>47.81</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="85">
@@ -7951,10 +7971,10 @@
         <v>38.94</v>
       </c>
       <c r="D85" s="5" t="n">
-        <v>50.9</v>
+        <v>51.2</v>
       </c>
       <c r="E85" s="5" t="n">
-        <v>59.53</v>
+        <v>59.89</v>
       </c>
     </row>
     <row r="86">
@@ -7970,10 +7990,10 @@
         <v>29.46</v>
       </c>
       <c r="D86" s="5" t="n">
-        <v>41.78</v>
+        <v>42.03</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>44.93</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="87">
@@ -7989,10 +8009,10 @@
         <v>46.72</v>
       </c>
       <c r="D87" s="5" t="n">
-        <v>53.19</v>
+        <v>53.51</v>
       </c>
       <c r="E87" s="5" t="n">
-        <v>71.09</v>
+        <v>71.51000000000001</v>
       </c>
     </row>
     <row r="88">
@@ -8008,10 +8028,10 @@
         <v>25.76</v>
       </c>
       <c r="D88" s="5" t="n">
-        <v>36.69</v>
+        <v>36.91</v>
       </c>
       <c r="E88" s="5" t="n">
-        <v>39.1</v>
+        <v>39.34</v>
       </c>
     </row>
     <row r="89">
@@ -8027,10 +8047,10 @@
         <v>24.27</v>
       </c>
       <c r="D89" s="5" t="n">
-        <v>34.34</v>
+        <v>34.54</v>
       </c>
       <c r="E89" s="5" t="n">
-        <v>36.79</v>
+        <v>37.01</v>
       </c>
     </row>
     <row r="90">
@@ -8046,10 +8066,10 @@
         <v>24.35</v>
       </c>
       <c r="D90" s="5" t="n">
-        <v>34.94</v>
+        <v>35.15</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>36.87</v>
+        <v>37.09</v>
       </c>
     </row>
     <row r="91">
@@ -8065,10 +8085,10 @@
         <v>24.87</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>33.98</v>
+        <v>34.18</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>37.6</v>
+        <v>37.83</v>
       </c>
     </row>
     <row r="92">
@@ -8084,10 +8104,10 @@
         <v>78.09</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>72.75</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>117.47</v>
+        <v>118.17</v>
       </c>
     </row>
     <row r="93">
@@ -8103,10 +8123,10 @@
         <v>259.43</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>204.69</v>
+        <v>205.92</v>
       </c>
       <c r="E93" s="5" t="n">
-        <v>388.27</v>
+        <v>390.6</v>
       </c>
     </row>
     <row r="94">
@@ -8122,10 +8142,10 @@
         <v>29.29</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>39.22</v>
+        <v>39.46</v>
       </c>
       <c r="E94" s="5" t="n">
-        <v>43.61</v>
+        <v>43.87</v>
       </c>
     </row>
     <row r="95">
@@ -8141,10 +8161,10 @@
         <v>27.22</v>
       </c>
       <c r="D95" s="5" t="n">
-        <v>39.23</v>
+        <v>39.47</v>
       </c>
       <c r="E95" s="5" t="n">
-        <v>40.41</v>
+        <v>40.65</v>
       </c>
     </row>
     <row r="96">
@@ -8160,10 +8180,10 @@
         <v>30.41</v>
       </c>
       <c r="D96" s="5" t="n">
-        <v>43.08</v>
+        <v>43.34</v>
       </c>
       <c r="E96" s="5" t="n">
-        <v>45</v>
+        <v>45.27</v>
       </c>
     </row>
     <row r="97">
@@ -8179,10 +8199,10 @@
         <v>29.83</v>
       </c>
       <c r="D97" s="5" t="n">
-        <v>40.43</v>
+        <v>40.67</v>
       </c>
       <c r="E97" s="5" t="n">
-        <v>44.01</v>
+        <v>44.28</v>
       </c>
     </row>
     <row r="98">
@@ -8198,10 +8218,10 @@
         <v>35.14</v>
       </c>
       <c r="D98" s="5" t="n">
-        <v>45.1</v>
+        <v>45.37</v>
       </c>
       <c r="E98" s="5" t="n">
-        <v>51.74</v>
+        <v>52.05</v>
       </c>
     </row>
     <row r="99">
@@ -8217,10 +8237,10 @@
         <v>33.09</v>
       </c>
       <c r="D99" s="5" t="n">
-        <v>44.31</v>
+        <v>44.57</v>
       </c>
       <c r="E99" s="5" t="n">
-        <v>48.63</v>
+        <v>48.92</v>
       </c>
     </row>
     <row r="100">
@@ -8236,10 +8256,10 @@
         <v>31.1</v>
       </c>
       <c r="D100" s="5" t="n">
-        <v>41.89</v>
+        <v>42.14</v>
       </c>
       <c r="E100" s="5" t="n">
-        <v>45.61</v>
+        <v>45.89</v>
       </c>
     </row>
     <row r="101">
@@ -8255,10 +8275,10 @@
         <v>30.68</v>
       </c>
       <c r="D101" s="5" t="n">
-        <v>41.83</v>
+        <v>42.08</v>
       </c>
       <c r="E101" s="5" t="n">
-        <v>45</v>
+        <v>45.27</v>
       </c>
     </row>
     <row r="102">
@@ -8274,10 +8294,10 @@
         <v>47.76</v>
       </c>
       <c r="D102" s="5" t="n">
-        <v>54.44</v>
+        <v>54.77</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>70.05</v>
+        <v>70.47</v>
       </c>
     </row>
     <row r="103">
@@ -8293,10 +8313,10 @@
         <v>27.5</v>
       </c>
       <c r="D103" s="5" t="n">
-        <v>37.81</v>
+        <v>38.04</v>
       </c>
       <c r="E103" s="5" t="n">
-        <v>40.33</v>
+        <v>40.58</v>
       </c>
     </row>
     <row r="104">
@@ -8312,10 +8332,10 @@
         <v>28.43</v>
       </c>
       <c r="D104" s="5" t="n">
-        <v>36.76</v>
+        <v>36.98</v>
       </c>
       <c r="E104" s="5" t="n">
-        <v>41.69</v>
+        <v>41.94</v>
       </c>
     </row>
     <row r="105">
@@ -8331,10 +8351,10 @@
         <v>29.48</v>
       </c>
       <c r="D105" s="5" t="n">
-        <v>39.42</v>
+        <v>39.66</v>
       </c>
       <c r="E105" s="5" t="n">
-        <v>43.22</v>
+        <v>43.48</v>
       </c>
     </row>
     <row r="106">
@@ -8350,10 +8370,10 @@
         <v>28.13</v>
       </c>
       <c r="D106" s="5" t="n">
-        <v>37.32</v>
+        <v>37.54</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>41.23</v>
+        <v>41.48</v>
       </c>
     </row>
     <row r="107">
@@ -8369,10 +8389,10 @@
         <v>36.78</v>
       </c>
       <c r="D107" s="5" t="n">
-        <v>49.05</v>
+        <v>49.34</v>
       </c>
       <c r="E107" s="5" t="n">
-        <v>53.82</v>
+        <v>54.14</v>
       </c>
     </row>
     <row r="108">
@@ -8388,10 +8408,10 @@
         <v>30.61</v>
       </c>
       <c r="D108" s="5" t="n">
-        <v>41.94</v>
+        <v>42.19</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>44.71</v>
+        <v>44.98</v>
       </c>
     </row>
     <row r="109">
@@ -8407,10 +8427,10 @@
         <v>40.68</v>
       </c>
       <c r="D109" s="5" t="n">
-        <v>52.51</v>
+        <v>52.83</v>
       </c>
       <c r="E109" s="5" t="n">
-        <v>59.32</v>
+        <v>59.68</v>
       </c>
     </row>
     <row r="110">
@@ -8426,10 +8446,10 @@
         <v>74.02</v>
       </c>
       <c r="D110" s="5" t="n">
-        <v>96.14</v>
+        <v>96.72</v>
       </c>
       <c r="E110" s="5" t="n">
-        <v>107.45</v>
+        <v>108.1</v>
       </c>
     </row>
     <row r="111">
@@ -8445,10 +8465,10 @@
         <v>59.12</v>
       </c>
       <c r="D111" s="5" t="n">
-        <v>82.95</v>
+        <v>83.45</v>
       </c>
       <c r="E111" s="5" t="n">
-        <v>85.44</v>
+        <v>85.95</v>
       </c>
     </row>
     <row r="112">
@@ -8464,10 +8484,10 @@
         <v>54.32</v>
       </c>
       <c r="D112" s="5" t="n">
-        <v>75.89</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="E112" s="5" t="n">
-        <v>78.15000000000001</v>
+        <v>78.62</v>
       </c>
     </row>
     <row r="113">
@@ -8483,10 +8503,10 @@
         <v>60.96</v>
       </c>
       <c r="D113" s="5" t="n">
-        <v>82.04000000000001</v>
+        <v>82.53</v>
       </c>
       <c r="E113" s="5" t="n">
-        <v>87.63</v>
+        <v>88.15000000000001</v>
       </c>
     </row>
     <row r="114">
@@ -8502,10 +8522,10 @@
         <v>62.23</v>
       </c>
       <c r="D114" s="5" t="n">
-        <v>81.69</v>
+        <v>82.18000000000001</v>
       </c>
       <c r="E114" s="5" t="n">
-        <v>89.38</v>
+        <v>89.91</v>
       </c>
     </row>
     <row r="115">
@@ -8521,10 +8541,10 @@
         <v>50.48</v>
       </c>
       <c r="D115" s="5" t="n">
-        <v>71.48</v>
+        <v>71.91</v>
       </c>
       <c r="E115" s="5" t="n">
-        <v>72.44</v>
+        <v>72.87</v>
       </c>
     </row>
     <row r="116">
@@ -8540,10 +8560,10 @@
         <v>53.13</v>
       </c>
       <c r="D116" s="5" t="n">
-        <v>72.47</v>
+        <v>72.91</v>
       </c>
       <c r="E116" s="5" t="n">
-        <v>76.16</v>
+        <v>76.61</v>
       </c>
     </row>
     <row r="117">
@@ -8559,10 +8579,10 @@
         <v>54.42</v>
       </c>
       <c r="D117" s="5" t="n">
-        <v>74.62</v>
+        <v>75.06999999999999</v>
       </c>
       <c r="E117" s="5" t="n">
-        <v>77.92</v>
+        <v>78.39</v>
       </c>
     </row>
     <row r="118">
@@ -8578,10 +8598,10 @@
         <v>54.87</v>
       </c>
       <c r="D118" s="5" t="n">
-        <v>75.09999999999999</v>
+        <v>75.55</v>
       </c>
       <c r="E118" s="5" t="n">
-        <v>78.47</v>
+        <v>78.94</v>
       </c>
     </row>
     <row r="119">
@@ -8597,10 +8617,10 @@
         <v>57.39</v>
       </c>
       <c r="D119" s="5" t="n">
-        <v>77.17</v>
+        <v>77.64</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>81.97</v>
+        <v>82.47</v>
       </c>
     </row>
     <row r="120">
@@ -8616,10 +8636,10 @@
         <v>59.18</v>
       </c>
       <c r="D120" s="5" t="n">
-        <v>78.56</v>
+        <v>79.03</v>
       </c>
       <c r="E120" s="5" t="n">
-        <v>84.42</v>
+        <v>84.93000000000001</v>
       </c>
     </row>
     <row r="121">
@@ -8635,10 +8655,10 @@
         <v>59.67</v>
       </c>
       <c r="D121" s="5" t="n">
-        <v>80.5</v>
+        <v>80.98</v>
       </c>
       <c r="E121" s="5" t="n">
-        <v>85.02</v>
+        <v>85.53</v>
       </c>
     </row>
     <row r="122">
@@ -8654,10 +8674,10 @@
         <v>60.88</v>
       </c>
       <c r="D122" s="5" t="n">
-        <v>82.03</v>
+        <v>82.52</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>86.39</v>
+        <v>86.91</v>
       </c>
     </row>
     <row r="123">
@@ -8673,10 +8693,10 @@
         <v>56.37</v>
       </c>
       <c r="D123" s="5" t="n">
-        <v>76.7</v>
+        <v>77.16</v>
       </c>
       <c r="E123" s="5" t="n">
-        <v>79.67</v>
+        <v>80.14</v>
       </c>
     </row>
     <row r="124">
@@ -8692,10 +8712,10 @@
         <v>54.35</v>
       </c>
       <c r="D124" s="5" t="n">
-        <v>74.2</v>
+        <v>74.64</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>76.5</v>
+        <v>76.95999999999999</v>
       </c>
     </row>
     <row r="125">
@@ -8711,10 +8731,10 @@
         <v>52.4</v>
       </c>
       <c r="D125" s="5" t="n">
-        <v>72.31999999999999</v>
+        <v>72.75</v>
       </c>
       <c r="E125" s="5" t="n">
-        <v>73.58</v>
+        <v>74.02</v>
       </c>
     </row>
     <row r="126">
@@ -8730,10 +8750,10 @@
         <v>51.68</v>
       </c>
       <c r="D126" s="5" t="n">
-        <v>70.73</v>
+        <v>71.16</v>
       </c>
       <c r="E126" s="5" t="n">
-        <v>72.40000000000001</v>
+        <v>72.83</v>
       </c>
     </row>
     <row r="127">
@@ -8749,10 +8769,10 @@
         <v>70.8</v>
       </c>
       <c r="D127" s="5" t="n">
-        <v>82.5</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="E127" s="5" t="n">
-        <v>98.95</v>
+        <v>99.54000000000001</v>
       </c>
     </row>
     <row r="128">
@@ -8768,10 +8788,10 @@
         <v>56.72</v>
       </c>
       <c r="D128" s="5" t="n">
-        <v>72.68000000000001</v>
+        <v>73.12</v>
       </c>
       <c r="E128" s="5" t="n">
-        <v>79.11</v>
+        <v>79.59</v>
       </c>
     </row>
     <row r="129">
@@ -8787,10 +8807,10 @@
         <v>52.88</v>
       </c>
       <c r="D129" s="5" t="n">
-        <v>70.05</v>
+        <v>70.47</v>
       </c>
       <c r="E129" s="5" t="n">
-        <v>73.61</v>
+        <v>74.05</v>
       </c>
     </row>
     <row r="130">
@@ -8806,10 +8826,10 @@
         <v>51.65</v>
       </c>
       <c r="D130" s="5" t="n">
-        <v>67.63</v>
+        <v>68.04000000000001</v>
       </c>
       <c r="E130" s="5" t="n">
-        <v>71.76000000000001</v>
+        <v>72.19</v>
       </c>
     </row>
     <row r="131">
@@ -8825,10 +8845,10 @@
         <v>50.39</v>
       </c>
       <c r="D131" s="5" t="n">
-        <v>67.44</v>
+        <v>67.84</v>
       </c>
       <c r="E131" s="5" t="n">
-        <v>69.89</v>
+        <v>70.31</v>
       </c>
     </row>
     <row r="132">
@@ -8844,10 +8864,10 @@
         <v>56.06</v>
       </c>
       <c r="D132" s="5" t="n">
-        <v>71.12</v>
+        <v>71.54000000000001</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>77.63</v>
+        <v>78.09</v>
       </c>
     </row>
     <row r="133">
@@ -8863,10 +8883,10 @@
         <v>51.67</v>
       </c>
       <c r="D133" s="5" t="n">
-        <v>68.76000000000001</v>
+        <v>69.17</v>
       </c>
       <c r="E133" s="5" t="n">
-        <v>71.43000000000001</v>
+        <v>71.84999999999999</v>
       </c>
     </row>
     <row r="134">
@@ -8882,10 +8902,10 @@
         <v>44.55</v>
       </c>
       <c r="D134" s="5" t="n">
-        <v>56.9</v>
+        <v>57.24</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>61.5</v>
+        <v>61.87</v>
       </c>
     </row>
     <row r="135">
@@ -8901,10 +8921,10 @@
         <v>40.13</v>
       </c>
       <c r="D135" s="5" t="n">
-        <v>49.75</v>
+        <v>50.05</v>
       </c>
       <c r="E135" s="5" t="n">
-        <v>55.32</v>
+        <v>55.65</v>
       </c>
     </row>
     <row r="136">
@@ -8920,10 +8940,10 @@
         <v>44.84</v>
       </c>
       <c r="D136" s="5" t="n">
-        <v>55.02</v>
+        <v>55.35</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>61.72</v>
+        <v>62.1</v>
       </c>
     </row>
     <row r="137">
@@ -8939,10 +8959,10 @@
         <v>34.1</v>
       </c>
       <c r="D137" s="5" t="n">
-        <v>43.49</v>
+        <v>43.75</v>
       </c>
       <c r="E137" s="5" t="n">
-        <v>46.91</v>
+        <v>47.19</v>
       </c>
     </row>
     <row r="138">
@@ -8958,10 +8978,10 @@
         <v>41.02</v>
       </c>
       <c r="D138" s="5" t="n">
-        <v>46.35</v>
+        <v>46.62</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>56.4</v>
+        <v>56.73</v>
       </c>
     </row>
     <row r="139">
@@ -8977,10 +8997,10 @@
         <v>35.12</v>
       </c>
       <c r="D139" s="5" t="n">
-        <v>42.11</v>
+        <v>42.36</v>
       </c>
       <c r="E139" s="5" t="n">
-        <v>48.25</v>
+        <v>48.54</v>
       </c>
     </row>
     <row r="140">
@@ -8996,10 +9016,10 @@
         <v>47.17</v>
       </c>
       <c r="D140" s="5" t="n">
-        <v>50.74</v>
+        <v>51.04</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>64.77</v>
+        <v>65.16</v>
       </c>
     </row>
     <row r="141">
@@ -9015,10 +9035,10 @@
         <v>38.88</v>
       </c>
       <c r="D141" s="5" t="n">
-        <v>45.91</v>
+        <v>46.19</v>
       </c>
       <c r="E141" s="5" t="n">
-        <v>53.35</v>
+        <v>53.67</v>
       </c>
     </row>
     <row r="142">
@@ -9034,10 +9054,10 @@
         <v>35.83</v>
       </c>
       <c r="D142" s="5" t="n">
-        <v>42.22</v>
+        <v>42.48</v>
       </c>
       <c r="E142" s="5" t="n">
-        <v>49.14</v>
+        <v>49.43</v>
       </c>
     </row>
     <row r="143">
@@ -9053,10 +9073,10 @@
         <v>42.98</v>
       </c>
       <c r="D143" s="5" t="n">
-        <v>49.03</v>
+        <v>49.33</v>
       </c>
       <c r="E143" s="5" t="n">
-        <v>58.8</v>
+        <v>59.15</v>
       </c>
     </row>
     <row r="144">
@@ -9072,10 +9092,10 @@
         <v>41.54</v>
       </c>
       <c r="D144" s="5" t="n">
-        <v>48.71</v>
+        <v>49</v>
       </c>
       <c r="E144" s="5" t="n">
-        <v>56.7</v>
+        <v>57.04</v>
       </c>
     </row>
     <row r="145">
@@ -9091,10 +9111,10 @@
         <v>40.75</v>
       </c>
       <c r="D145" s="5" t="n">
-        <v>49.14</v>
+        <v>49.44</v>
       </c>
       <c r="E145" s="5" t="n">
-        <v>55.49</v>
+        <v>55.82</v>
       </c>
     </row>
     <row r="146">
@@ -9110,10 +9130,10 @@
         <v>43.87</v>
       </c>
       <c r="D146" s="5" t="n">
-        <v>53.24</v>
+        <v>53.56</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>59.66</v>
+        <v>60.02</v>
       </c>
     </row>
     <row r="147">
@@ -9129,10 +9149,10 @@
         <v>40.45</v>
       </c>
       <c r="D147" s="5" t="n">
-        <v>49.91</v>
+        <v>50.21</v>
       </c>
       <c r="E147" s="5" t="n">
-        <v>54.94</v>
+        <v>55.27</v>
       </c>
     </row>
     <row r="148">
@@ -9148,10 +9168,10 @@
         <v>76.97</v>
       </c>
       <c r="D148" s="5" t="n">
-        <v>78.67</v>
+        <v>79.14</v>
       </c>
       <c r="E148" s="5" t="n">
-        <v>104.4</v>
+        <v>105.03</v>
       </c>
     </row>
     <row r="149">
@@ -9167,10 +9187,10 @@
         <v>41.94</v>
       </c>
       <c r="D149" s="5" t="n">
-        <v>49.77</v>
+        <v>50.07</v>
       </c>
       <c r="E149" s="5" t="n">
-        <v>56.81</v>
+        <v>57.15</v>
       </c>
     </row>
     <row r="150">
@@ -9186,10 +9206,10 @@
         <v>62.06</v>
       </c>
       <c r="D150" s="5" t="n">
-        <v>62.12</v>
+        <v>62.5</v>
       </c>
       <c r="E150" s="5" t="n">
-        <v>83.95999999999999</v>
+        <v>84.45999999999999</v>
       </c>
     </row>
     <row r="151">
@@ -9205,10 +9225,10 @@
         <v>50.61</v>
       </c>
       <c r="D151" s="5" t="n">
-        <v>60.21</v>
+        <v>60.57</v>
       </c>
       <c r="E151" s="5" t="n">
-        <v>68.38</v>
+        <v>68.79000000000001</v>
       </c>
     </row>
     <row r="152">
@@ -9224,10 +9244,10 @@
         <v>60.64</v>
       </c>
       <c r="D152" s="5" t="n">
-        <v>61.13</v>
+        <v>61.49</v>
       </c>
       <c r="E152" s="5" t="n">
-        <v>81.98999999999999</v>
+        <v>82.48</v>
       </c>
     </row>
     <row r="153">
@@ -9243,10 +9263,10 @@
         <v>45.94</v>
       </c>
       <c r="D153" s="5" t="n">
-        <v>52.51</v>
+        <v>52.82</v>
       </c>
       <c r="E153" s="5" t="n">
-        <v>62.15</v>
+        <v>62.53</v>
       </c>
     </row>
     <row r="154">
@@ -9262,10 +9282,10 @@
         <v>49.96</v>
       </c>
       <c r="D154" s="5" t="n">
-        <v>60.46</v>
+        <v>60.82</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>67.64</v>
+        <v>68.04000000000001</v>
       </c>
     </row>
     <row r="155">
@@ -9281,10 +9301,10 @@
         <v>78</v>
       </c>
       <c r="D155" s="5" t="n">
-        <v>89.26000000000001</v>
+        <v>89.8</v>
       </c>
       <c r="E155" s="5" t="n">
-        <v>105.44</v>
+        <v>106.08</v>
       </c>
     </row>
     <row r="156">
@@ -9300,10 +9320,10 @@
         <v>81.53</v>
       </c>
       <c r="D156" s="5" t="n">
-        <v>90.23999999999999</v>
+        <v>90.78</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>110.06</v>
+        <v>110.72</v>
       </c>
     </row>
     <row r="157">
@@ -9319,10 +9339,10 @@
         <v>121.82</v>
       </c>
       <c r="D157" s="5" t="n">
-        <v>131.68</v>
+        <v>132.47</v>
       </c>
       <c r="E157" s="5" t="n">
-        <v>164.2</v>
+        <v>165.19</v>
       </c>
     </row>
     <row r="158">
@@ -9338,10 +9358,10 @@
         <v>86.11</v>
       </c>
       <c r="D158" s="5" t="n">
-        <v>88.86</v>
+        <v>89.39</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>115.8</v>
+        <v>116.49</v>
       </c>
     </row>
     <row r="159">
@@ -9357,10 +9377,10 @@
         <v>58.75</v>
       </c>
       <c r="D159" s="5" t="n">
-        <v>64.53</v>
+        <v>64.92</v>
       </c>
       <c r="E159" s="5" t="n">
-        <v>78.81999999999999</v>
+        <v>79.29000000000001</v>
       </c>
     </row>
     <row r="160">
@@ -9376,10 +9396,10 @@
         <v>50.15</v>
       </c>
       <c r="D160" s="5" t="n">
-        <v>60.07</v>
+        <v>60.43</v>
       </c>
       <c r="E160" s="5" t="n">
-        <v>67.13</v>
+        <v>67.53</v>
       </c>
     </row>
     <row r="161">
@@ -9395,10 +9415,10 @@
         <v>60.61</v>
       </c>
       <c r="D161" s="5" t="n">
-        <v>73.8</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="E161" s="5" t="n">
-        <v>80.98</v>
+        <v>81.47</v>
       </c>
     </row>
     <row r="162">
@@ -9414,10 +9434,10 @@
         <v>114.97</v>
       </c>
       <c r="D162" s="5" t="n">
-        <v>110.88</v>
+        <v>111.55</v>
       </c>
       <c r="E162" s="5" t="n">
-        <v>153.35</v>
+        <v>154.27</v>
       </c>
     </row>
     <row r="163">
@@ -9433,10 +9453,10 @@
         <v>59.62</v>
       </c>
       <c r="D163" s="5" t="n">
-        <v>68.61</v>
+        <v>69.02</v>
       </c>
       <c r="E163" s="5" t="n">
-        <v>79.38</v>
+        <v>79.86</v>
       </c>
     </row>
     <row r="164">
@@ -9452,10 +9472,10 @@
         <v>106.24</v>
       </c>
       <c r="D164" s="5" t="n">
-        <v>109.93</v>
+        <v>110.59</v>
       </c>
       <c r="E164" s="5" t="n">
-        <v>141.24</v>
+        <v>142.09</v>
       </c>
     </row>
     <row r="165">
@@ -9471,10 +9491,10 @@
         <v>279.63</v>
       </c>
       <c r="D165" s="5" t="n">
-        <v>237.07</v>
+        <v>238.49</v>
       </c>
       <c r="E165" s="5" t="n">
-        <v>371.19</v>
+        <v>373.42</v>
       </c>
     </row>
     <row r="166">
@@ -9490,10 +9510,10 @@
         <v>110.22</v>
       </c>
       <c r="D166" s="5" t="n">
-        <v>122.88</v>
+        <v>123.62</v>
       </c>
       <c r="E166" s="5" t="n">
-        <v>146.09</v>
+        <v>146.96</v>
       </c>
     </row>
     <row r="167">
@@ -9509,10 +9529,10 @@
         <v>115.63</v>
       </c>
       <c r="D167" s="5" t="n">
-        <v>141.01</v>
+        <v>141.86</v>
       </c>
       <c r="E167" s="5" t="n">
-        <v>153.16</v>
+        <v>154.08</v>
       </c>
     </row>
     <row r="168">
@@ -9528,10 +9548,10 @@
         <v>96.5</v>
       </c>
       <c r="D168" s="5" t="n">
-        <v>118.7</v>
+        <v>119.41</v>
       </c>
       <c r="E168" s="5" t="n">
-        <v>127.74</v>
+        <v>128.5</v>
       </c>
     </row>
     <row r="169">
@@ -9547,10 +9567,10 @@
         <v>90.03</v>
       </c>
       <c r="D169" s="5" t="n">
-        <v>112.26</v>
+        <v>112.93</v>
       </c>
       <c r="E169" s="5" t="n">
-        <v>119.1</v>
+        <v>119.81</v>
       </c>
     </row>
     <row r="170">
@@ -9566,10 +9586,10 @@
         <v>102.1</v>
       </c>
       <c r="D170" s="5" t="n">
-        <v>120.31</v>
+        <v>121.03</v>
       </c>
       <c r="E170" s="5" t="n">
-        <v>134.79</v>
+        <v>135.6</v>
       </c>
     </row>
     <row r="171">
@@ -9585,10 +9605,10 @@
         <v>112.14</v>
       </c>
       <c r="D171" s="5" t="n">
-        <v>134.58</v>
+        <v>135.39</v>
       </c>
       <c r="E171" s="5" t="n">
-        <v>147.74</v>
+        <v>148.63</v>
       </c>
     </row>
     <row r="172">
@@ -9604,10 +9624,10 @@
         <v>91.84999999999999</v>
       </c>
       <c r="D172" s="5" t="n">
-        <v>114.7</v>
+        <v>115.39</v>
       </c>
       <c r="E172" s="5" t="n">
-        <v>120.76</v>
+        <v>121.49</v>
       </c>
     </row>
     <row r="173">
@@ -9623,10 +9643,10 @@
         <v>90.03</v>
       </c>
       <c r="D173" s="5" t="n">
-        <v>107.81</v>
+        <v>108.46</v>
       </c>
       <c r="E173" s="5" t="n">
-        <v>118.11</v>
+        <v>118.82</v>
       </c>
     </row>
     <row r="174">
@@ -9642,10 +9662,10 @@
         <v>87.13</v>
       </c>
       <c r="D174" s="5" t="n">
-        <v>103.12</v>
+        <v>103.74</v>
       </c>
       <c r="E174" s="5" t="n">
-        <v>114.05</v>
+        <v>114.73</v>
       </c>
     </row>
     <row r="175">
@@ -9661,10 +9681,10 @@
         <v>87.25</v>
       </c>
       <c r="D175" s="5" t="n">
-        <v>99.98999999999999</v>
+        <v>100.59</v>
       </c>
       <c r="E175" s="5" t="n">
-        <v>113.95</v>
+        <v>114.63</v>
       </c>
     </row>
     <row r="176">
@@ -9680,10 +9700,10 @@
         <v>83.73999999999999</v>
       </c>
       <c r="D176" s="5" t="n">
-        <v>99.14</v>
+        <v>99.73</v>
       </c>
       <c r="E176" s="5" t="n">
-        <v>109.21</v>
+        <v>109.86</v>
       </c>
     </row>
     <row r="177">
@@ -9699,10 +9719,10 @@
         <v>80.61</v>
       </c>
       <c r="D177" s="5" t="n">
-        <v>94.79000000000001</v>
+        <v>95.36</v>
       </c>
       <c r="E177" s="5" t="n">
-        <v>104.97</v>
+        <v>105.6</v>
       </c>
     </row>
     <row r="178">
@@ -9718,10 +9738,10 @@
         <v>69.84999999999999</v>
       </c>
       <c r="D178" s="5" t="n">
-        <v>86.75</v>
+        <v>87.27</v>
       </c>
       <c r="E178" s="5" t="n">
-        <v>90.83</v>
+        <v>91.37</v>
       </c>
     </row>
     <row r="179">
@@ -9737,10 +9757,10 @@
         <v>85.54000000000001</v>
       </c>
       <c r="D179" s="5" t="n">
-        <v>97.58</v>
+        <v>98.16</v>
       </c>
       <c r="E179" s="5" t="n">
-        <v>111.1</v>
+        <v>111.77</v>
       </c>
     </row>
     <row r="180">
@@ -9756,10 +9776,10 @@
         <v>88.81999999999999</v>
       </c>
       <c r="D180" s="5" t="n">
-        <v>100.24</v>
+        <v>100.84</v>
       </c>
       <c r="E180" s="5" t="n">
-        <v>115.22</v>
+        <v>115.91</v>
       </c>
     </row>
     <row r="181">
@@ -9775,10 +9795,10 @@
         <v>130.79</v>
       </c>
       <c r="D181" s="5" t="n">
-        <v>130.53</v>
+        <v>131.31</v>
       </c>
       <c r="E181" s="5" t="n">
-        <v>169.47</v>
+        <v>170.48</v>
       </c>
     </row>
     <row r="182">
@@ -9794,10 +9814,10 @@
         <v>84.93000000000001</v>
       </c>
       <c r="D182" s="5" t="n">
-        <v>97.02</v>
+        <v>97.61</v>
       </c>
       <c r="E182" s="5" t="n">
-        <v>109.89</v>
+        <v>110.54</v>
       </c>
     </row>
     <row r="183">
@@ -9813,10 +9833,10 @@
         <v>108.46</v>
       </c>
       <c r="D183" s="5" t="n">
-        <v>120.18</v>
+        <v>120.9</v>
       </c>
       <c r="E183" s="5" t="n">
-        <v>140.13</v>
+        <v>140.97</v>
       </c>
     </row>
     <row r="184">
@@ -9832,10 +9852,10 @@
         <v>107.82</v>
       </c>
       <c r="D184" s="5" t="n">
-        <v>120.45</v>
+        <v>121.17</v>
       </c>
       <c r="E184" s="5" t="n">
-        <v>139.1</v>
+        <v>139.93</v>
       </c>
     </row>
     <row r="185">
@@ -9851,10 +9871,10 @@
         <v>101.79</v>
       </c>
       <c r="D185" s="5" t="n">
-        <v>113.66</v>
+        <v>114.34</v>
       </c>
       <c r="E185" s="5" t="n">
-        <v>131.09</v>
+        <v>131.88</v>
       </c>
     </row>
     <row r="186">
@@ -9870,10 +9890,10 @@
         <v>99.8</v>
       </c>
       <c r="D186" s="5" t="n">
-        <v>110.62</v>
+        <v>111.28</v>
       </c>
       <c r="E186" s="5" t="n">
-        <v>128.31</v>
+        <v>129.08</v>
       </c>
     </row>
     <row r="187">
@@ -9889,10 +9909,10 @@
         <v>97.98</v>
       </c>
       <c r="D187" s="5" t="n">
-        <v>107.22</v>
+        <v>107.86</v>
       </c>
       <c r="E187" s="5" t="n">
-        <v>125.75</v>
+        <v>126.51</v>
       </c>
     </row>
     <row r="188">
@@ -9908,10 +9928,10 @@
         <v>157.41</v>
       </c>
       <c r="D188" s="5" t="n">
-        <v>150.75</v>
+        <v>151.65</v>
       </c>
       <c r="E188" s="5" t="n">
-        <v>202.04</v>
+        <v>203.25</v>
       </c>
     </row>
     <row r="189">
@@ -9927,10 +9947,10 @@
         <v>102.7</v>
       </c>
       <c r="D189" s="5" t="n">
-        <v>114.52</v>
+        <v>115.21</v>
       </c>
       <c r="E189" s="5" t="n">
-        <v>131.82</v>
+        <v>132.61</v>
       </c>
     </row>
     <row r="190">
@@ -9946,10 +9966,10 @@
         <v>99.31</v>
       </c>
       <c r="D190" s="5" t="n">
-        <v>112.84</v>
+        <v>113.52</v>
       </c>
       <c r="E190" s="5" t="n">
-        <v>127.47</v>
+        <v>128.24</v>
       </c>
     </row>
     <row r="191">
@@ -9965,10 +9985,10 @@
         <v>87.88</v>
       </c>
       <c r="D191" s="5" t="n">
-        <v>100.53</v>
+        <v>101.13</v>
       </c>
       <c r="E191" s="5" t="n">
-        <v>112.58</v>
+        <v>113.26</v>
       </c>
     </row>
     <row r="192">
@@ -9984,10 +10004,10 @@
         <v>90.98</v>
       </c>
       <c r="D192" s="5" t="n">
-        <v>101.16</v>
+        <v>101.77</v>
       </c>
       <c r="E192" s="5" t="n">
-        <v>116.32</v>
+        <v>117.02</v>
       </c>
     </row>
     <row r="193">
@@ -10003,10 +10023,10 @@
         <v>107.65</v>
       </c>
       <c r="D193" s="5" t="n">
-        <v>116.49</v>
+        <v>117.19</v>
       </c>
       <c r="E193" s="5" t="n">
-        <v>137.37</v>
+        <v>138.19</v>
       </c>
     </row>
     <row r="194">
@@ -10022,10 +10042,10 @@
         <v>80.73999999999999</v>
       </c>
       <c r="D194" s="5" t="n">
-        <v>91.15000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="E194" s="5" t="n">
-        <v>102.83</v>
+        <v>103.45</v>
       </c>
     </row>
     <row r="195">
@@ -10041,10 +10061,10 @@
         <v>98.62</v>
       </c>
       <c r="D195" s="5" t="n">
-        <v>106.84</v>
+        <v>107.48</v>
       </c>
       <c r="E195" s="5" t="n">
-        <v>125.37</v>
+        <v>126.12</v>
       </c>
     </row>
     <row r="196">
@@ -10060,10 +10080,10 @@
         <v>110.15</v>
       </c>
       <c r="D196" s="5" t="n">
-        <v>121.33</v>
+        <v>122.06</v>
       </c>
       <c r="E196" s="5" t="n">
-        <v>139.77</v>
+        <v>140.6</v>
       </c>
     </row>
     <row r="197">
@@ -10079,10 +10099,10 @@
         <v>111.43</v>
       </c>
       <c r="D197" s="5" t="n">
-        <v>128.84</v>
+        <v>129.61</v>
       </c>
       <c r="E197" s="5" t="n">
-        <v>141.07</v>
+        <v>141.91</v>
       </c>
     </row>
     <row r="198">
@@ -10098,10 +10118,10 @@
         <v>72.06</v>
       </c>
       <c r="D198" s="5" t="n">
-        <v>88.29000000000001</v>
+        <v>88.81999999999999</v>
       </c>
       <c r="E198" s="5" t="n">
-        <v>91.02</v>
+        <v>91.56</v>
       </c>
     </row>
     <row r="199">
@@ -10117,10 +10137,10 @@
         <v>54.5</v>
       </c>
       <c r="D199" s="5" t="n">
-        <v>65.65000000000001</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="E199" s="5" t="n">
-        <v>68.68000000000001</v>
+        <v>69.09</v>
       </c>
     </row>
     <row r="200">
@@ -10136,10 +10156,10 @@
         <v>185.41</v>
       </c>
       <c r="D200" s="5" t="n">
-        <v>191.69</v>
+        <v>192.84</v>
       </c>
       <c r="E200" s="5" t="n">
-        <v>233.37</v>
+        <v>234.77</v>
       </c>
     </row>
     <row r="201">
@@ -10155,10 +10175,10 @@
         <v>59.42</v>
       </c>
       <c r="D201" s="5" t="n">
-        <v>72.28</v>
+        <v>72.72</v>
       </c>
       <c r="E201" s="5" t="n">
-        <v>74.7</v>
+        <v>75.15000000000001</v>
       </c>
     </row>
     <row r="202">
@@ -10174,10 +10194,10 @@
         <v>51.4</v>
       </c>
       <c r="D202" s="5" t="n">
-        <v>57.96</v>
+        <v>58.3</v>
       </c>
       <c r="E202" s="5" t="n">
-        <v>64.54000000000001</v>
+        <v>64.92</v>
       </c>
     </row>
     <row r="203">
@@ -10193,10 +10213,10 @@
         <v>45.3</v>
       </c>
       <c r="D203" s="5" t="n">
-        <v>51.01</v>
+        <v>51.32</v>
       </c>
       <c r="E203" s="5" t="n">
-        <v>57.24</v>
+        <v>57.59</v>
       </c>
     </row>
     <row r="204">
@@ -10212,10 +10232,10 @@
         <v>48.48</v>
       </c>
       <c r="D204" s="5" t="n">
-        <v>53.36</v>
+        <v>53.68</v>
       </c>
       <c r="E204" s="5" t="n">
-        <v>61.66</v>
+        <v>62.03</v>
       </c>
     </row>
     <row r="205">
@@ -10231,10 +10251,10 @@
         <v>60.43</v>
       </c>
       <c r="D205" s="5" t="n">
-        <v>61.57</v>
+        <v>61.93</v>
       </c>
       <c r="E205" s="5" t="n">
-        <v>77.36</v>
+        <v>77.83</v>
       </c>
     </row>
     <row r="206">
@@ -10250,10 +10270,10 @@
         <v>56.33</v>
       </c>
       <c r="D206" s="5" t="n">
-        <v>61.11</v>
+        <v>61.48</v>
       </c>
       <c r="E206" s="5" t="n">
-        <v>71.73999999999999</v>
+        <v>72.17</v>
       </c>
     </row>
     <row r="207">
@@ -10269,10 +10289,10 @@
         <v>60.22</v>
       </c>
       <c r="D207" s="5" t="n">
-        <v>63.18</v>
+        <v>63.56</v>
       </c>
       <c r="E207" s="5" t="n">
-        <v>76.31</v>
+        <v>76.76000000000001</v>
       </c>
     </row>
     <row r="208">
@@ -10288,10 +10308,10 @@
         <v>44.24</v>
       </c>
       <c r="D208" s="5" t="n">
-        <v>51.68</v>
+        <v>51.99</v>
       </c>
       <c r="E208" s="5" t="n">
-        <v>55.77</v>
+        <v>56.11</v>
       </c>
     </row>
     <row r="209">
@@ -10307,10 +10327,10 @@
         <v>71.72</v>
       </c>
       <c r="D209" s="5" t="n">
-        <v>72.73999999999999</v>
+        <v>73.17</v>
       </c>
       <c r="E209" s="5" t="n">
-        <v>90.14</v>
+        <v>90.69</v>
       </c>
     </row>
     <row r="210">
@@ -10326,10 +10346,10 @@
         <v>82.45</v>
       </c>
       <c r="D210" s="5" t="n">
-        <v>78.31</v>
+        <v>78.78</v>
       </c>
       <c r="E210" s="5" t="n">
-        <v>103.32</v>
+        <v>103.94</v>
       </c>
     </row>
     <row r="211">
@@ -10345,10 +10365,10 @@
         <v>106.96</v>
       </c>
       <c r="D211" s="5" t="n">
-        <v>89.18000000000001</v>
+        <v>89.72</v>
       </c>
       <c r="E211" s="5" t="n">
-        <v>133.63</v>
+        <v>134.44</v>
       </c>
     </row>
     <row r="212">
@@ -10364,10 +10384,10 @@
         <v>42.87</v>
       </c>
       <c r="D212" s="5" t="n">
-        <v>48.43</v>
+        <v>48.72</v>
       </c>
       <c r="E212" s="5" t="n">
-        <v>53.46</v>
+        <v>53.78</v>
       </c>
     </row>
     <row r="213">
@@ -10383,10 +10403,10 @@
         <v>36.12</v>
       </c>
       <c r="D213" s="5" t="n">
-        <v>43.72</v>
+        <v>43.98</v>
       </c>
       <c r="E213" s="5" t="n">
-        <v>44.95</v>
+        <v>45.22</v>
       </c>
     </row>
     <row r="214">
@@ -10402,10 +10422,10 @@
         <v>40.97</v>
       </c>
       <c r="D214" s="5" t="n">
-        <v>48.41</v>
+        <v>48.7</v>
       </c>
       <c r="E214" s="5" t="n">
-        <v>50.89</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="215">
@@ -10421,10 +10441,10 @@
         <v>68.79000000000001</v>
       </c>
       <c r="D215" s="5" t="n">
-        <v>69.04000000000001</v>
+        <v>69.45</v>
       </c>
       <c r="E215" s="5" t="n">
-        <v>85.23999999999999</v>
+        <v>85.75</v>
       </c>
     </row>
     <row r="216">
@@ -10440,10 +10460,10 @@
         <v>183.33</v>
       </c>
       <c r="D216" s="5" t="n">
-        <v>145.36</v>
+        <v>146.23</v>
       </c>
       <c r="E216" s="5" t="n">
-        <v>226.63</v>
+        <v>227.99</v>
       </c>
     </row>
     <row r="217">
@@ -10459,10 +10479,10 @@
         <v>255.16</v>
       </c>
       <c r="D217" s="5" t="n">
-        <v>197.36</v>
+        <v>198.54</v>
       </c>
       <c r="E217" s="5" t="n">
-        <v>314.66</v>
+        <v>316.54</v>
       </c>
     </row>
     <row r="218">
@@ -10478,10 +10498,10 @@
         <v>173.79</v>
       </c>
       <c r="D218" s="5" t="n">
-        <v>152.49</v>
+        <v>153.41</v>
       </c>
       <c r="E218" s="5" t="n">
-        <v>213.71</v>
+        <v>214.99</v>
       </c>
     </row>
     <row r="219">
@@ -10497,10 +10517,10 @@
         <v>66.06999999999999</v>
       </c>
       <c r="D219" s="5" t="n">
-        <v>73.76000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="E219" s="5" t="n">
-        <v>81.02</v>
+        <v>81.5</v>
       </c>
     </row>
     <row r="220">
@@ -10516,10 +10536,10 @@
         <v>47.75</v>
       </c>
       <c r="D220" s="5" t="n">
-        <v>59.79</v>
+        <v>60.15</v>
       </c>
       <c r="E220" s="5" t="n">
-        <v>58.39</v>
+        <v>58.74</v>
       </c>
     </row>
     <row r="221">
@@ -10535,10 +10555,10 @@
         <v>59.06</v>
       </c>
       <c r="D221" s="5" t="n">
-        <v>69.55</v>
+        <v>69.97</v>
       </c>
       <c r="E221" s="5" t="n">
-        <v>71.91</v>
+        <v>72.34</v>
       </c>
     </row>
     <row r="222">
@@ -10554,10 +10574,10 @@
         <v>72.52</v>
       </c>
       <c r="D222" s="5" t="n">
-        <v>78.13</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="E222" s="5" t="n">
-        <v>87.93000000000001</v>
+        <v>88.45999999999999</v>
       </c>
     </row>
     <row r="223">
@@ -10573,10 +10593,10 @@
         <v>69.08</v>
       </c>
       <c r="D223" s="5" t="n">
-        <v>82.06</v>
+        <v>82.55</v>
       </c>
       <c r="E223" s="5" t="n">
-        <v>83.41</v>
+        <v>83.91</v>
       </c>
     </row>
     <row r="224">
@@ -10592,10 +10612,10 @@
         <v>81.23999999999999</v>
       </c>
       <c r="D224" s="5" t="n">
-        <v>92.51000000000001</v>
+        <v>93.06</v>
       </c>
       <c r="E224" s="5" t="n">
-        <v>97.39</v>
+        <v>97.97</v>
       </c>
     </row>
     <row r="225">
@@ -10611,10 +10631,10 @@
         <v>92.36</v>
       </c>
       <c r="D225" s="5" t="n">
-        <v>98.83</v>
+        <v>99.42</v>
       </c>
       <c r="E225" s="5" t="n">
-        <v>109.93</v>
+        <v>110.59</v>
       </c>
     </row>
     <row r="226">
@@ -10630,10 +10650,10 @@
         <v>104.67</v>
       </c>
       <c r="D226" s="5" t="n">
-        <v>118.99</v>
+        <v>119.7</v>
       </c>
       <c r="E226" s="5" t="n">
-        <v>123.71</v>
+        <v>124.45</v>
       </c>
     </row>
     <row r="227">
@@ -10649,10 +10669,10 @@
         <v>204.07</v>
       </c>
       <c r="D227" s="5" t="n">
-        <v>219.55</v>
+        <v>220.86</v>
       </c>
       <c r="E227" s="5" t="n">
-        <v>239.75</v>
+        <v>241.19</v>
       </c>
     </row>
     <row r="228">
@@ -10668,10 +10688,10 @@
         <v>385.21</v>
       </c>
       <c r="D228" s="5" t="n">
-        <v>374.3</v>
+        <v>376.55</v>
       </c>
       <c r="E228" s="5" t="n">
-        <v>449.9</v>
+        <v>452.6</v>
       </c>
     </row>
     <row r="229">
@@ -10687,10 +10707,10 @@
         <v>441.06</v>
       </c>
       <c r="D229" s="5" t="n">
-        <v>462.16</v>
+        <v>464.93</v>
       </c>
       <c r="E229" s="5" t="n">
-        <v>512.11</v>
+        <v>515.1799999999999</v>
       </c>
     </row>
     <row r="230">
@@ -10706,10 +10726,10 @@
         <v>425.89</v>
       </c>
       <c r="D230" s="5" t="n">
-        <v>428.34</v>
+        <v>430.91</v>
       </c>
       <c r="E230" s="5" t="n">
-        <v>491.49</v>
+        <v>494.43</v>
       </c>
     </row>
     <row r="231">
@@ -10725,10 +10745,10 @@
         <v>156.59</v>
       </c>
       <c r="D231" s="5" t="n">
-        <v>170.13</v>
+        <v>171.15</v>
       </c>
       <c r="E231" s="5" t="n">
-        <v>179.61</v>
+        <v>180.69</v>
       </c>
     </row>
     <row r="232">
@@ -10744,10 +10764,10 @@
         <v>157.38</v>
       </c>
       <c r="D232" s="5" t="n">
-        <v>175.43</v>
+        <v>176.48</v>
       </c>
       <c r="E232" s="5" t="n">
-        <v>179.43</v>
+        <v>180.51</v>
       </c>
     </row>
     <row r="233">
@@ -10763,10 +10783,10 @@
         <v>155.91</v>
       </c>
       <c r="D233" s="5" t="n">
-        <v>171.84</v>
+        <v>172.87</v>
       </c>
       <c r="E233" s="5" t="n">
-        <v>176.67</v>
+        <v>177.73</v>
       </c>
     </row>
     <row r="234">
@@ -10782,10 +10802,10 @@
         <v>106.68</v>
       </c>
       <c r="D234" s="5" t="n">
-        <v>127.15</v>
+        <v>127.92</v>
       </c>
       <c r="E234" s="5" t="n">
-        <v>120.15</v>
+        <v>120.87</v>
       </c>
     </row>
     <row r="235">
@@ -10801,10 +10821,10 @@
         <v>72.58</v>
       </c>
       <c r="D235" s="5" t="n">
-        <v>92.51000000000001</v>
+        <v>93.06</v>
       </c>
       <c r="E235" s="5" t="n">
-        <v>81.25</v>
+        <v>81.73999999999999</v>
       </c>
     </row>
     <row r="236">
@@ -10820,10 +10840,10 @@
         <v>95.95</v>
       </c>
       <c r="D236" s="5" t="n">
-        <v>105.19</v>
+        <v>105.82</v>
       </c>
       <c r="E236" s="5" t="n">
-        <v>106.93</v>
+        <v>107.57</v>
       </c>
     </row>
     <row r="237">
@@ -10839,10 +10859,10 @@
         <v>96.16</v>
       </c>
       <c r="D237" s="5" t="n">
-        <v>99.98999999999999</v>
+        <v>100.59</v>
       </c>
       <c r="E237" s="5" t="n">
-        <v>106.68</v>
+        <v>107.32</v>
       </c>
     </row>
     <row r="238">
@@ -10858,10 +10878,10 @@
         <v>134.91</v>
       </c>
       <c r="D238" s="5" t="n">
-        <v>128.13</v>
+        <v>128.9</v>
       </c>
       <c r="E238" s="5" t="n">
-        <v>149</v>
+        <v>149.9</v>
       </c>
     </row>
     <row r="239">
@@ -10877,10 +10897,10 @@
         <v>116.44</v>
       </c>
       <c r="D239" s="5" t="n">
-        <v>122.07</v>
+        <v>122.8</v>
       </c>
       <c r="E239" s="5" t="n">
-        <v>128.24</v>
+        <v>129.01</v>
       </c>
     </row>
     <row r="240">
@@ -10896,10 +10916,10 @@
         <v>230.59</v>
       </c>
       <c r="D240" s="5" t="n">
-        <v>213.04</v>
+        <v>214.32</v>
       </c>
       <c r="E240" s="5" t="n">
-        <v>253.23</v>
+        <v>254.75</v>
       </c>
     </row>
     <row r="241">
@@ -10915,10 +10935,10 @@
         <v>123.7</v>
       </c>
       <c r="D241" s="5" t="n">
-        <v>115.2</v>
+        <v>115.89</v>
       </c>
       <c r="E241" s="5" t="n">
-        <v>135.46</v>
+        <v>136.27</v>
       </c>
     </row>
     <row r="242">
@@ -10934,10 +10954,10 @@
         <v>93.78</v>
       </c>
       <c r="D242" s="5" t="n">
-        <v>91.8</v>
+        <v>92.34999999999999</v>
       </c>
       <c r="E242" s="5" t="n">
-        <v>102.3</v>
+        <v>102.92</v>
       </c>
     </row>
     <row r="243">
@@ -10953,10 +10973,10 @@
         <v>104.72</v>
       </c>
       <c r="D243" s="5" t="n">
-        <v>101.4</v>
+        <v>102.01</v>
       </c>
       <c r="E243" s="5" t="n">
-        <v>113.8</v>
+        <v>114.49</v>
       </c>
     </row>
     <row r="244">
@@ -10972,10 +10992,10 @@
         <v>70.17</v>
       </c>
       <c r="D244" s="5" t="n">
-        <v>69.87</v>
+        <v>70.29000000000001</v>
       </c>
       <c r="E244" s="5" t="n">
-        <v>75.97</v>
+        <v>76.42</v>
       </c>
     </row>
     <row r="245">
@@ -10991,10 +11011,10 @@
         <v>41.9</v>
       </c>
       <c r="D245" s="5" t="n">
-        <v>45.46</v>
+        <v>45.73</v>
       </c>
       <c r="E245" s="5" t="n">
-        <v>45.27</v>
+        <v>45.54</v>
       </c>
     </row>
     <row r="246">
@@ -11010,10 +11030,10 @@
         <v>94.34999999999999</v>
       </c>
       <c r="D246" s="5" t="n">
-        <v>94.17</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="E246" s="5" t="n">
-        <v>101.72</v>
+        <v>102.33</v>
       </c>
     </row>
     <row r="247">
@@ -11029,10 +11049,10 @@
         <v>81.66</v>
       </c>
       <c r="D247" s="5" t="n">
-        <v>73.44</v>
+        <v>73.88</v>
       </c>
       <c r="E247" s="5" t="n">
-        <v>87.84999999999999</v>
+        <v>88.38</v>
       </c>
     </row>
     <row r="248">
@@ -11048,10 +11068,10 @@
         <v>80.48</v>
       </c>
       <c r="D248" s="5" t="n">
-        <v>87.06</v>
+        <v>87.58</v>
       </c>
       <c r="E248" s="5" t="n">
-        <v>86.31999999999999</v>
+        <v>86.83</v>
       </c>
     </row>
     <row r="249">
@@ -11067,10 +11087,10 @@
         <v>160.9</v>
       </c>
       <c r="D249" s="5" t="n">
-        <v>119.39</v>
+        <v>120.1</v>
       </c>
       <c r="E249" s="5" t="n">
-        <v>172.04</v>
+        <v>173.07</v>
       </c>
     </row>
     <row r="250">
@@ -11086,10 +11106,10 @@
         <v>70.48999999999999</v>
       </c>
       <c r="D250" s="5" t="n">
-        <v>75.12</v>
+        <v>75.56999999999999</v>
       </c>
       <c r="E250" s="5" t="n">
-        <v>75.14</v>
+        <v>75.59</v>
       </c>
     </row>
     <row r="251">
@@ -11105,10 +11125,10 @@
         <v>86.27</v>
       </c>
       <c r="D251" s="5" t="n">
-        <v>95.42</v>
+        <v>95.98999999999999</v>
       </c>
       <c r="E251" s="5" t="n">
-        <v>91.64</v>
+        <v>92.19</v>
       </c>
     </row>
     <row r="252">
@@ -11124,10 +11144,10 @@
         <v>430.06</v>
       </c>
       <c r="D252" s="5" t="n">
-        <v>289.57</v>
+        <v>291.31</v>
       </c>
       <c r="E252" s="5" t="n">
-        <v>455.23</v>
+        <v>457.96</v>
       </c>
     </row>
     <row r="253">
@@ -11143,10 +11163,10 @@
         <v>173.97</v>
       </c>
       <c r="D253" s="5" t="n">
-        <v>161.13</v>
+        <v>162.1</v>
       </c>
       <c r="E253" s="5" t="n">
-        <v>183.52</v>
+        <v>184.62</v>
       </c>
     </row>
     <row r="254">
@@ -11162,10 +11182,10 @@
         <v>155.59</v>
       </c>
       <c r="D254" s="5" t="n">
-        <v>134.05</v>
+        <v>134.85</v>
       </c>
       <c r="E254" s="5" t="n">
-        <v>164.01</v>
+        <v>164.99</v>
       </c>
     </row>
     <row r="255">
@@ -11181,10 +11201,10 @@
         <v>253.4</v>
       </c>
       <c r="D255" s="5" t="n">
-        <v>183.76</v>
+        <v>184.86</v>
       </c>
       <c r="E255" s="5" t="n">
-        <v>266.92</v>
+        <v>268.52</v>
       </c>
     </row>
     <row r="256">
@@ -11200,10 +11220,10 @@
         <v>49.3</v>
       </c>
       <c r="D256" s="5" t="n">
-        <v>61.07</v>
+        <v>61.44</v>
       </c>
       <c r="E256" s="5" t="n">
-        <v>51.89</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="257">
@@ -11219,10 +11239,10 @@
         <v>81.59</v>
       </c>
       <c r="D257" s="5" t="n">
-        <v>81.43000000000001</v>
+        <v>81.92</v>
       </c>
       <c r="E257" s="5" t="n">
-        <v>85.81999999999999</v>
+        <v>86.34</v>
       </c>
     </row>
     <row r="258">
@@ -11238,10 +11258,10 @@
         <v>359.37</v>
       </c>
       <c r="D258" s="5" t="n">
-        <v>230.93</v>
+        <v>232.31</v>
       </c>
       <c r="E258" s="5" t="n">
-        <v>377.77</v>
+        <v>380.04</v>
       </c>
     </row>
     <row r="259">
@@ -11257,10 +11277,10 @@
         <v>173.92</v>
       </c>
       <c r="D259" s="5" t="n">
-        <v>141.54</v>
+        <v>142.38</v>
       </c>
       <c r="E259" s="5" t="n">
-        <v>182.7</v>
+        <v>183.8</v>
       </c>
     </row>
     <row r="260">
@@ -11276,10 +11296,10 @@
         <v>93.90000000000001</v>
       </c>
       <c r="D260" s="5" t="n">
-        <v>87.28</v>
+        <v>87.81</v>
       </c>
       <c r="E260" s="5" t="n">
-        <v>98.34</v>
+        <v>98.93000000000001</v>
       </c>
     </row>
     <row r="261">
@@ -11295,10 +11315,10 @@
         <v>99.90000000000001</v>
       </c>
       <c r="D261" s="5" t="n">
-        <v>94.31</v>
+        <v>94.88</v>
       </c>
       <c r="E261" s="5" t="n">
-        <v>104.31</v>
+        <v>104.93</v>
       </c>
     </row>
     <row r="262">
@@ -11314,10 +11334,10 @@
         <v>82.47</v>
       </c>
       <c r="D262" s="5" t="n">
-        <v>93.64</v>
+        <v>94.2</v>
       </c>
       <c r="E262" s="5" t="n">
-        <v>85.84999999999999</v>
+        <v>86.36</v>
       </c>
     </row>
     <row r="263">
@@ -11333,10 +11353,10 @@
         <v>107.35</v>
       </c>
       <c r="D263" s="5" t="n">
-        <v>108.06</v>
+        <v>108.71</v>
       </c>
       <c r="E263" s="5" t="n">
-        <v>111.47</v>
+        <v>112.14</v>
       </c>
     </row>
     <row r="264">
@@ -11352,10 +11372,10 @@
         <v>162.22</v>
       </c>
       <c r="D264" s="5" t="n">
-        <v>127.42</v>
+        <v>128.19</v>
       </c>
       <c r="E264" s="5" t="n">
-        <v>168.02</v>
+        <v>169.03</v>
       </c>
     </row>
     <row r="265">
@@ -11371,10 +11391,10 @@
         <v>435.34</v>
       </c>
       <c r="D265" s="5" t="n">
-        <v>264.71</v>
+        <v>266.3</v>
       </c>
       <c r="E265" s="5" t="n">
-        <v>449.8</v>
+        <v>452.5</v>
       </c>
     </row>
     <row r="266">
@@ -11390,10 +11410,10 @@
         <v>107.33</v>
       </c>
       <c r="D266" s="5" t="n">
-        <v>99.73</v>
+        <v>100.33</v>
       </c>
       <c r="E266" s="5" t="n">
-        <v>110.41</v>
+        <v>111.07</v>
       </c>
     </row>
     <row r="267">
@@ -11409,10 +11429,10 @@
         <v>112.68</v>
       </c>
       <c r="D267" s="5" t="n">
-        <v>103.7</v>
+        <v>104.32</v>
       </c>
       <c r="E267" s="5" t="n">
-        <v>115.41</v>
+        <v>116.1</v>
       </c>
     </row>
     <row r="268">
@@ -11428,10 +11448,10 @@
         <v>66.42</v>
       </c>
       <c r="D268" s="5" t="n">
-        <v>72.65000000000001</v>
+        <v>73.08</v>
       </c>
       <c r="E268" s="5" t="n">
-        <v>67.73</v>
+        <v>68.14</v>
       </c>
     </row>
     <row r="269">
@@ -11447,10 +11467,10 @@
         <v>75.34999999999999</v>
       </c>
       <c r="D269" s="5" t="n">
-        <v>78.39</v>
+        <v>78.86</v>
       </c>
       <c r="E269" s="5" t="n">
-        <v>76.69</v>
+        <v>77.15000000000001</v>
       </c>
     </row>
     <row r="270">
@@ -11466,10 +11486,10 @@
         <v>83.58</v>
       </c>
       <c r="D270" s="5" t="n">
-        <v>78.14</v>
+        <v>78.61</v>
       </c>
       <c r="E270" s="5" t="n">
-        <v>84.90000000000001</v>
+        <v>85.41</v>
       </c>
     </row>
     <row r="271">
@@ -11485,10 +11505,10 @@
         <v>77.75</v>
       </c>
       <c r="D271" s="5" t="n">
-        <v>72.34</v>
+        <v>72.78</v>
       </c>
       <c r="E271" s="5" t="n">
-        <v>78.81999999999999</v>
+        <v>79.29000000000001</v>
       </c>
     </row>
     <row r="272">
@@ -11504,10 +11524,10 @@
         <v>45.49</v>
       </c>
       <c r="D272" s="5" t="n">
-        <v>67.83</v>
+        <v>68.23999999999999</v>
       </c>
       <c r="E272" s="5" t="n">
-        <v>45.91</v>
+        <v>46.18</v>
       </c>
     </row>
     <row r="273">
@@ -11523,10 +11543,10 @@
         <v>97.18000000000001</v>
       </c>
       <c r="D273" s="5" t="n">
-        <v>84.14</v>
+        <v>84.65000000000001</v>
       </c>
       <c r="E273" s="5" t="n">
-        <v>97.62</v>
+        <v>98.20999999999999</v>
       </c>
     </row>
     <row r="274">
@@ -11542,10 +11562,10 @@
         <v>74.36</v>
       </c>
       <c r="D274" s="5" t="n">
-        <v>71.2</v>
+        <v>71.63</v>
       </c>
       <c r="E274" s="5" t="n">
-        <v>74.36</v>
+        <v>74.81</v>
       </c>
     </row>
     <row r="275">
@@ -11561,10 +11581,10 @@
         <v>60.42</v>
       </c>
       <c r="D275" s="5" t="n">
-        <v>64.27</v>
+        <v>64.53</v>
       </c>
       <c r="E275" s="5" t="n">
-        <v>60.42</v>
+        <v>60.66</v>
       </c>
     </row>
     <row r="276">
@@ -11580,10 +11600,10 @@
         <v>63.17</v>
       </c>
       <c r="D276" s="5" t="n">
-        <v>65.76000000000001</v>
+        <v>65.89</v>
       </c>
       <c r="E276" s="5" t="n">
-        <v>63.17</v>
+        <v>63.3</v>
       </c>
     </row>
     <row r="277">
@@ -11624,8 +11644,27 @@
         <v>85.61</v>
       </c>
     </row>
+    <row r="279">
+      <c r="A279" s="4" t="inlineStr">
+        <is>
+          <t>Aug 2026</t>
+        </is>
+      </c>
+      <c r="B279" s="5" t="n">
+        <v>82.81</v>
+      </c>
+      <c r="C279" s="5" t="n">
+        <v>84.17</v>
+      </c>
+      <c r="D279" s="5" t="n">
+        <v>82.81</v>
+      </c>
+      <c r="E279" s="5" t="n">
+        <v>84.17</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B278">
+  <conditionalFormatting sqref="B2:B279">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -11637,7 +11676,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C278">
+  <conditionalFormatting sqref="C2:C279">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -11649,7 +11688,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D278">
+  <conditionalFormatting sqref="D2:D279">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -11661,7 +11700,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E278">
+  <conditionalFormatting sqref="E2:E279">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
